--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annashen/Desktop/code/ME663-project/postprocess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDEB569-0AC7-D946-A84F-369FC6D8110E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05523EA5-9B93-A840-9090-CBFD9100858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="2420" windowWidth="33460" windowHeight="16880" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
+    <workbookView xWindow="1100" yWindow="700" windowWidth="25940" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -157,7 +158,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,12 +187,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -238,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -246,31 +241,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -369,29 +349,29 @@
     <tableColumn id="2" xr3:uid="{00DE4CFB-CE63-774C-9203-441FF3361859}" name="conv_scheme"/>
     <tableColumn id="17" xr3:uid="{47055424-3AAA-D24A-BA60-63AE4C6D6F5B}" name="RE"/>
     <tableColumn id="4" xr3:uid="{495CF2F5-C4F9-8F4D-AA38-DF0B3BD005AB}" name="N"/>
-    <tableColumn id="5" xr3:uid="{766BC887-C47B-5B4D-856A-DB7D9716FC41}" name="DX" dataDxfId="9">
+    <tableColumn id="5" xr3:uid="{766BC887-C47B-5B4D-856A-DB7D9716FC41}" name="DX" dataDxfId="19">
       <calculatedColumnFormula>1/Table52[[#This Row],[N]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{41134D54-A4BA-874E-976C-009F5555A5F2}" name="DT_MAX" dataDxfId="8">
+    <tableColumn id="6" xr3:uid="{41134D54-A4BA-874E-976C-009F5555A5F2}" name="DT_MAX" dataDxfId="18">
       <calculatedColumnFormula>Table52[[#This Row],[DX]]/1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{273D8EE8-DE95-664F-9350-38E8AA2F9049}" name="DT"/>
-    <tableColumn id="22" xr3:uid="{F37937B1-F618-9544-858E-9C385880A578}" name="CFL" dataDxfId="7">
+    <tableColumn id="22" xr3:uid="{F37937B1-F618-9544-858E-9C385880A578}" name="CFL" dataDxfId="17">
       <calculatedColumnFormula>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{57BAD542-64CC-254E-88F0-83BA2685E4ED}" name="URF" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{CF78813F-1FCF-E643-8377-72AF6325BEEE}" name="diverging_factor" dataDxfId="5"/>
-    <tableColumn id="25" xr3:uid="{B19A7E44-6A26-8B41-BA69-77F75344DEA3}" name="IT" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{57BAD542-64CC-254E-88F0-83BA2685E4ED}" name="URF" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{CF78813F-1FCF-E643-8377-72AF6325BEEE}" name="diverging_factor" dataDxfId="15"/>
+    <tableColumn id="25" xr3:uid="{B19A7E44-6A26-8B41-BA69-77F75344DEA3}" name="IT" dataDxfId="14"/>
     <tableColumn id="11" xr3:uid="{F124CBF0-B3EB-C444-B55D-C50EED146627}" name="clock_time"/>
     <tableColumn id="12" xr3:uid="{5F48E9FB-C4BC-024C-B991-90BE72C979E1}" name="colour"/>
-    <tableColumn id="13" xr3:uid="{DEF21282-AC7A-5545-B41D-E8A24B1E8319}" name="compare_diff" dataDxfId="3">
+    <tableColumn id="13" xr3:uid="{DEF21282-AC7A-5545-B41D-E8A24B1E8319}" name="compare_diff" dataDxfId="13">
       <calculatedColumnFormula>2.5/Table52[[#This Row],[DT]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{04DFDB2B-B2EB-2143-A2BD-C078D341F02C}" name="plot" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{2C94A75A-643C-AB4F-B973-F132BD67C52D}" name="Coldumn3" dataDxfId="1">
+    <tableColumn id="14" xr3:uid="{04DFDB2B-B2EB-2143-A2BD-C078D341F02C}" name="plot" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{2C94A75A-643C-AB4F-B973-F132BD67C52D}" name="Coldumn3" dataDxfId="11">
       <calculatedColumnFormula>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4E3C3F99-0854-E448-B822-ED1CAF3861A9}" name="Time (min)" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{4E3C3F99-0854-E448-B822-ED1CAF3861A9}" name="Time (min)" dataDxfId="10">
       <calculatedColumnFormula>Table52[[#This Row],[clock_time]]/60</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -409,29 +389,29 @@
     <tableColumn id="2" xr3:uid="{5CAB8637-6767-EF4F-AB30-8872A405584F}" name="conv_scheme"/>
     <tableColumn id="17" xr3:uid="{F7E8B8A5-B5C1-654E-BF6E-56FB97322E67}" name="RE"/>
     <tableColumn id="4" xr3:uid="{D0F235B2-EEA8-D14B-A9CC-E4901839BFD8}" name="N"/>
-    <tableColumn id="5" xr3:uid="{83BA6CEC-05CE-F148-8D33-78AB6664A553}" name="DX" dataDxfId="19">
+    <tableColumn id="5" xr3:uid="{83BA6CEC-05CE-F148-8D33-78AB6664A553}" name="DX" dataDxfId="9">
       <calculatedColumnFormula>1/Table523[[#This Row],[N]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{67B863EC-1E80-594A-8E8C-A8AB6A765A5B}" name="DT_MAX" dataDxfId="18">
+    <tableColumn id="6" xr3:uid="{67B863EC-1E80-594A-8E8C-A8AB6A765A5B}" name="DT_MAX" dataDxfId="8">
       <calculatedColumnFormula>Table523[[#This Row],[DX]]/1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{B6FA003B-6936-8041-9393-B2FBF938999E}" name="DT"/>
-    <tableColumn id="22" xr3:uid="{6AF97E91-5A09-0D4F-8AFB-1FA45DB53426}" name="CFL" dataDxfId="17">
+    <tableColumn id="22" xr3:uid="{6AF97E91-5A09-0D4F-8AFB-1FA45DB53426}" name="CFL" dataDxfId="7">
       <calculatedColumnFormula>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{18D7BD5A-213F-BD40-97BA-0D536A04F891}" name="URF" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{798FE19B-9189-494F-A3BB-310F03005E42}" name="diverging_factor" dataDxfId="15"/>
-    <tableColumn id="25" xr3:uid="{FDF5445A-F7EE-1F4D-9905-BD45A45BD22B}" name="IT" dataDxfId="14"/>
+    <tableColumn id="16" xr3:uid="{18D7BD5A-213F-BD40-97BA-0D536A04F891}" name="URF" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{798FE19B-9189-494F-A3BB-310F03005E42}" name="diverging_factor" dataDxfId="5"/>
+    <tableColumn id="25" xr3:uid="{FDF5445A-F7EE-1F4D-9905-BD45A45BD22B}" name="IT" dataDxfId="4"/>
     <tableColumn id="11" xr3:uid="{BEAE8ECD-6C05-B047-A51B-18671676A586}" name="clock_time"/>
     <tableColumn id="12" xr3:uid="{750E52A0-203C-CD4A-98C6-C1F65E42F542}" name="colour"/>
-    <tableColumn id="13" xr3:uid="{FDAC66DF-EEEF-4B40-9B2B-8468B1ABCB4F}" name="compare_diff" dataDxfId="13">
+    <tableColumn id="13" xr3:uid="{FDAC66DF-EEEF-4B40-9B2B-8468B1ABCB4F}" name="compare_diff" dataDxfId="3">
       <calculatedColumnFormula>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{25F9EF5E-5623-9348-AFD3-BE21DEB4A0B1}" name="plot" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{6C6DB161-08C1-8C41-8D04-DBB62D987A88}" name="Coldumn3" dataDxfId="11">
+    <tableColumn id="14" xr3:uid="{25F9EF5E-5623-9348-AFD3-BE21DEB4A0B1}" name="plot" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{6C6DB161-08C1-8C41-8D04-DBB62D987A88}" name="Coldumn3" dataDxfId="1">
       <calculatedColumnFormula>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8D89A138-3ECA-4F4F-8AE2-5ED05E63F0B1}" name="Coldumn4" dataDxfId="10">
+    <tableColumn id="3" xr3:uid="{8D89A138-3ECA-4F4F-8AE2-5ED05E63F0B1}" name="Coldumn4" dataDxfId="0">
       <calculatedColumnFormula>Table523[[#This Row],[clock_time]]/60</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -884,514 +864,513 @@
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>10.4</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>4.1241166499999997E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F3" s="8">
+      <c r="E3">
+        <v>1000</v>
+      </c>
+      <c r="F3">
         <v>32</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3">
         <v>0.05</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>1.6</v>
       </c>
-      <c r="K3" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L3" s="8">
+      <c r="K3">
+        <v>-1</v>
+      </c>
+      <c r="L3">
         <v>0.1</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3">
         <v>860</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="1">
         <v>3.8879101299999999</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="8">
+      <c r="P3">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>50</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q3">
         <v>100</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.6</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.4798502166666661E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F4" s="8">
+      <c r="E4">
+        <v>1000</v>
+      </c>
+      <c r="F4">
         <v>64</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K4" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L4" s="8">
+      <c r="K4">
+        <v>-1</v>
+      </c>
+      <c r="L4">
         <v>0.02</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4">
         <v>3322</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4">
         <v>44.980831100000003</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P4">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q4" s="8">
+      <c r="Q4">
         <v>250</v>
       </c>
-      <c r="R4" s="8">
+      <c r="R4">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>13.288</v>
       </c>
-      <c r="S4" s="17">
+      <c r="S4">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.74968051833333338</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F5" s="8">
+      <c r="E5">
+        <v>1000</v>
+      </c>
+      <c r="F5">
         <v>128</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
-      <c r="K5" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L5" s="8">
+      <c r="K5">
+        <v>-1</v>
+      </c>
+      <c r="L5">
         <v>0.01</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5">
         <v>11952</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="1">
         <v>377.19601399999999</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>500</v>
       </c>
-      <c r="Q5" s="8">
-        <v>1000</v>
-      </c>
-      <c r="R5" s="8">
+      <c r="Q5">
+        <v>1000</v>
+      </c>
+      <c r="R5">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>11.952</v>
       </c>
-      <c r="S5" s="17">
+      <c r="S5">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.2866002333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="E6">
+        <v>1000</v>
+      </c>
+      <c r="F6">
         <v>256</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6">
         <v>1.5E-3</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.38400000000000001</v>
       </c>
-      <c r="K6" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L6" s="8">
+      <c r="K6">
+        <v>-1</v>
+      </c>
+      <c r="L6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6">
         <v>43836</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="1">
         <v>3393.8759799999998</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="8">
+      <c r="P6">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>1666.6666666666667</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6">
         <v>5000</v>
       </c>
-      <c r="R6" s="8">
+      <c r="R6">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.7672000000000008</v>
       </c>
-      <c r="S6" s="17">
+      <c r="S6">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>56.564599666666666</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F7" s="8">
+      <c r="E7">
+        <v>1000</v>
+      </c>
+      <c r="F7">
         <v>16</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7">
         <v>0.1</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>1.6</v>
       </c>
-      <c r="K7" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L7" s="8">
+      <c r="K7">
+        <v>-1</v>
+      </c>
+      <c r="L7">
         <v>0.15</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7">
         <v>675</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="1">
         <v>0.43378701800000002</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" t="s">
         <v>15</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>25</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q7">
         <v>50</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>13.5</v>
       </c>
-      <c r="S7" s="17">
+      <c r="S7">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>7.2297836333333337E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F8" s="8">
+      <c r="E8">
+        <v>1000</v>
+      </c>
+      <c r="F8">
         <v>32</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.8</v>
       </c>
-      <c r="K8" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L8" s="8">
+      <c r="K8">
+        <v>-1</v>
+      </c>
+      <c r="L8">
         <v>0.05</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8">
         <v>1941</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="1">
         <v>4.5700812300000004</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="O8" t="s">
         <v>15</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>100</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q8">
         <v>250</v>
       </c>
-      <c r="R8" s="8">
+      <c r="R8">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.7640000000000002</v>
       </c>
-      <c r="S8" s="17">
+      <c r="S8">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>7.6168020500000003E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F9" s="8">
+      <c r="E9">
+        <v>1000</v>
+      </c>
+      <c r="F9">
         <v>64</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K9" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L9" s="8">
+      <c r="K9">
+        <v>-1</v>
+      </c>
+      <c r="L9">
         <v>0.02</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9">
         <v>4202</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="1">
         <v>61.105514499999998</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9">
         <v>500</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.4039999999999999</v>
       </c>
-      <c r="S9" s="17">
+      <c r="S9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.0184252416666666</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="8">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="E10">
+        <v>1000</v>
+      </c>
+      <c r="F10">
         <v>128</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K10" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8">
+      <c r="K10">
+        <v>-1</v>
+      </c>
+      <c r="M10">
         <v>11902</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="1">
         <v>567.30658000000005</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="O10" t="s">
         <v>17</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>333.33333333333337</v>
       </c>
@@ -1402,70 +1381,70 @@
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>11.901999999999999</v>
       </c>
-      <c r="S10" s="7">
+      <c r="S10">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>9.455109666666667</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="11" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+    <row r="11" spans="1:19" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
         <v>10</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="11">
         <v>1</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F11" s="15">
+      <c r="E11" s="11">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="11">
         <v>256</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="11">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="11">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="11">
         <v>2E-3</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="11">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.51200000000000001</v>
       </c>
-      <c r="K11" s="15">
-        <v>-1</v>
-      </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15">
+      <c r="K11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11">
         <v>42487</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="12">
         <v>3972.08862</v>
       </c>
-      <c r="O11" s="15" t="s">
+      <c r="O11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>1250</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11">
         <v>5000</v>
       </c>
-      <c r="R11" s="11">
+      <c r="R11" s="7">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.4974000000000007</v>
       </c>
-      <c r="S11" s="18">
+      <c r="S11" s="7">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>66.201476999999997</v>
       </c>
@@ -1530,7 +1509,7 @@
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>10.36</v>
       </c>
-      <c r="S12" s="7">
+      <c r="S12">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>3.9128502166666671E-3</v>
       </c>
@@ -1585,14 +1564,14 @@
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>50</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.57</v>
       </c>
-      <c r="S13" s="7">
+      <c r="S13">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.3228702499999997E-2</v>
       </c>
@@ -1616,22 +1595,22 @@
       <c r="F14">
         <v>64</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
       <c r="I14">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14" s="1"/>
@@ -1644,1239 +1623,1239 @@
       <c r="O14" t="s">
         <v>18</v>
       </c>
-      <c r="P14" s="7">
+      <c r="P14">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q14">
         <v>250</v>
       </c>
-      <c r="R14" s="7">
+      <c r="R14">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>1.3280000000000001</v>
       </c>
-      <c r="S14" s="7">
+      <c r="S14">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.72652683333333334</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="8">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15">
         <v>2</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F15" s="8">
+      <c r="E15">
+        <v>1000</v>
+      </c>
+      <c r="F15">
         <v>128</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
-      <c r="K15" s="8">
-        <v>-1</v>
-      </c>
-      <c r="M15" s="8">
+      <c r="K15">
+        <v>-1</v>
+      </c>
+      <c r="M15">
         <v>11952</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="1">
         <v>392.12469499999997</v>
       </c>
-      <c r="O15" s="8" t="s">
+      <c r="O15" t="s">
         <v>18</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>500</v>
       </c>
-      <c r="Q15" s="8">
-        <v>1000</v>
-      </c>
-      <c r="R15" s="8">
+      <c r="Q15">
+        <v>1000</v>
+      </c>
+      <c r="R15">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>11.952</v>
       </c>
-      <c r="S15" s="17">
+      <c r="S15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.5354115833333326</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="20" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
+    <row r="16" spans="1:19" s="13" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13">
         <v>15</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="13">
         <v>2</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="20">
-        <v>1000</v>
-      </c>
-      <c r="F16" s="20">
+      <c r="E16" s="13">
+        <v>1000</v>
+      </c>
+      <c r="F16" s="13">
         <v>256</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="13">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="13">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="13">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K16" s="20">
-        <v>-1</v>
-      </c>
-      <c r="N16" s="21"/>
-      <c r="O16" s="20" t="s">
+      <c r="K16" s="13">
+        <v>-1</v>
+      </c>
+      <c r="N16" s="14"/>
+      <c r="O16" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="P16" s="20" t="e">
+      <c r="P16" s="13" t="e">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="Q16">
         <v>5000</v>
       </c>
-      <c r="R16" s="20">
+      <c r="R16" s="13">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>0</v>
       </c>
-      <c r="S16" s="22">
+      <c r="S16" s="13">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="E17">
+        <v>1000</v>
+      </c>
+      <c r="F17">
         <v>64</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J17" s="26">
+      <c r="J17">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27">
+      <c r="L17" s="1"/>
+      <c r="M17" s="1">
         <v>4202</v>
       </c>
-      <c r="N17" s="27">
+      <c r="N17" s="1">
         <v>64.518783600000006</v>
       </c>
-      <c r="P17" s="26">
+      <c r="P17">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17">
         <v>500</v>
       </c>
-      <c r="R17" s="26">
+      <c r="R17">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.4039999999999999</v>
       </c>
-      <c r="S17" s="26">
+      <c r="S17">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.07531306</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18">
         <v>1</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F18" s="25">
+      <c r="E18">
+        <v>1000</v>
+      </c>
+      <c r="F18">
         <v>64</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18">
         <v>0.01</v>
       </c>
-      <c r="J18" s="26">
+      <c r="J18">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27">
+      <c r="L18" s="1"/>
+      <c r="M18" s="1">
         <v>5552</v>
       </c>
-      <c r="N18" s="27">
+      <c r="N18" s="1">
         <v>48.560310399999999</v>
       </c>
-      <c r="P18" s="26">
+      <c r="P18">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>250</v>
       </c>
-      <c r="Q18" s="26">
+      <c r="Q18">
         <v>750</v>
       </c>
-      <c r="R18" s="26">
+      <c r="R18">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.4026666666666667</v>
       </c>
-      <c r="S18" s="26">
+      <c r="S18">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.80933850666666662</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19">
         <v>1</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F19" s="25">
+      <c r="E19">
+        <v>1000</v>
+      </c>
+      <c r="F19">
         <v>64</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.32</v>
       </c>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27">
+      <c r="L19" s="1"/>
+      <c r="M19" s="1">
         <v>9328</v>
       </c>
-      <c r="N19" s="27">
+      <c r="N19" s="1">
         <v>34.663536100000002</v>
       </c>
-      <c r="P19" s="26">
+      <c r="P19">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>500</v>
       </c>
-      <c r="Q19" s="26">
-        <v>1000</v>
-      </c>
-      <c r="R19" s="26">
+      <c r="Q19">
+        <v>1000</v>
+      </c>
+      <c r="R19">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>9.3279999999999994</v>
       </c>
-      <c r="S19" s="26">
+      <c r="S19">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.57772560166666664</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20">
         <v>1</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F20" s="25">
+      <c r="E20">
+        <v>1000</v>
+      </c>
+      <c r="F20">
         <v>64</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20">
         <v>1E-3</v>
       </c>
-      <c r="J20" s="26">
+      <c r="J20">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27">
+      <c r="L20" s="1"/>
+      <c r="M20" s="1">
         <v>35260</v>
       </c>
-      <c r="N20" s="27">
+      <c r="N20" s="1">
         <v>47.817623099999999</v>
       </c>
-      <c r="P20" s="26">
+      <c r="P20">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>2500</v>
       </c>
-      <c r="Q20" s="26">
+      <c r="Q20">
         <v>5000</v>
       </c>
-      <c r="R20" s="26">
+      <c r="R20">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.0519999999999996</v>
       </c>
-      <c r="S20" s="26">
+      <c r="S20">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.79696038499999999</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="11" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
+    <row r="21" spans="1:19" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="7">
         <v>1</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="11">
-        <v>1000</v>
-      </c>
-      <c r="F21" s="11">
+      <c r="E21" s="7">
+        <v>1000</v>
+      </c>
+      <c r="F21" s="7">
         <v>64</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="7">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="7">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="7">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="7">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12">
+      <c r="L21" s="8"/>
+      <c r="M21" s="8">
         <v>63517</v>
       </c>
-      <c r="N21" s="12">
+      <c r="N21" s="8">
         <v>76.141212499999995</v>
       </c>
-      <c r="P21" s="26">
+      <c r="P21">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>5000</v>
       </c>
-      <c r="Q21" s="18">
+      <c r="Q21" s="7">
         <v>15000</v>
       </c>
-      <c r="R21" s="18">
+      <c r="R21" s="7">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>4.234466666666667</v>
       </c>
-      <c r="S21" s="18">
+      <c r="S21" s="7">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2690202083333333</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22">
         <v>2</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F22" s="25">
+      <c r="E22">
+        <v>1000</v>
+      </c>
+      <c r="F22">
         <v>64</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G22">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H22" s="26">
+      <c r="H22">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27">
+      <c r="L22" s="1"/>
+      <c r="M22" s="1">
         <v>4190</v>
       </c>
-      <c r="N22" s="27">
+      <c r="N22" s="1">
         <v>58.056365999999997</v>
       </c>
-      <c r="P22" s="26">
+      <c r="P22">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q22" s="17">
+      <c r="Q22">
         <v>500</v>
       </c>
-      <c r="R22" s="26">
+      <c r="R22">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.3800000000000008</v>
       </c>
-      <c r="S22" s="26">
+      <c r="S22">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.96760609999999991</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23">
         <v>2</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F23" s="25">
+      <c r="E23">
+        <v>1000</v>
+      </c>
+      <c r="F23">
         <v>64</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I23" s="25">
+      <c r="I23">
         <v>0.01</v>
       </c>
-      <c r="J23" s="26">
+      <c r="J23">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27">
+      <c r="L23" s="1"/>
+      <c r="M23" s="1">
         <v>5551</v>
       </c>
-      <c r="N23" s="27">
+      <c r="N23" s="1">
         <v>49.9791794</v>
       </c>
-      <c r="P23" s="26">
+      <c r="P23">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>250</v>
       </c>
-      <c r="Q23" s="26">
+      <c r="Q23">
         <v>750</v>
       </c>
-      <c r="R23" s="26">
+      <c r="R23">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.4013333333333335</v>
       </c>
-      <c r="S23" s="26">
+      <c r="S23">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.83298632333333333</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24">
         <v>2</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F24" s="25">
+      <c r="E24">
+        <v>1000</v>
+      </c>
+      <c r="F24">
         <v>64</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I24" s="25">
+      <c r="I24">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J24" s="26">
+      <c r="J24">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.32</v>
       </c>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27">
+      <c r="L24" s="1"/>
+      <c r="M24" s="1">
         <v>9339</v>
       </c>
-      <c r="N24" s="27">
+      <c r="N24" s="1">
         <v>35.158287000000001</v>
       </c>
-      <c r="P24" s="26">
+      <c r="P24">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>500</v>
       </c>
-      <c r="Q24" s="26">
-        <v>1000</v>
-      </c>
-      <c r="R24" s="26">
+      <c r="Q24">
+        <v>1000</v>
+      </c>
+      <c r="R24">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>9.3390000000000004</v>
       </c>
-      <c r="S24" s="26">
+      <c r="S24">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.58597145000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25">
         <v>2</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F25" s="28">
+      <c r="E25">
+        <v>1000</v>
+      </c>
+      <c r="F25">
         <v>64</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25">
         <v>1E-3</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="K25" s="28"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31">
+      <c r="L25" s="1"/>
+      <c r="M25" s="1">
         <v>35262</v>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="1">
         <v>46.530872299999999</v>
       </c>
-      <c r="O25" s="28"/>
-      <c r="P25" s="30">
+      <c r="P25">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>2500</v>
       </c>
-      <c r="Q25" s="26">
+      <c r="Q25">
         <v>5000</v>
       </c>
-      <c r="R25" s="30">
+      <c r="R25">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.0523999999999996</v>
       </c>
-      <c r="S25" s="30">
+      <c r="S25">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.77551453833333328</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="25" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
+    <row r="26" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26">
         <v>2</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F26" s="28">
+      <c r="E26">
+        <v>1000</v>
+      </c>
+      <c r="F26">
         <v>64</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G26">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H26">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="7">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J26">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="30">
+      <c r="L26" s="1"/>
+      <c r="M26" s="1">
+        <v>63500</v>
+      </c>
+      <c r="N26" s="1">
+        <v>77.783943199999996</v>
+      </c>
+      <c r="P26">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>5000</v>
       </c>
-      <c r="Q26" s="18">
+      <c r="Q26" s="7">
         <v>15000</v>
       </c>
-      <c r="R26" s="30">
+      <c r="R26">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>0</v>
-      </c>
-      <c r="S26" s="30">
+        <v>4.2333333333333334</v>
+      </c>
+      <c r="S26">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.2963990533333332</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="9">
+        <v>16</v>
+      </c>
+      <c r="G27" s="9">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-1</v>
+      </c>
+      <c r="I27" s="15">
+        <v>-1</v>
+      </c>
+      <c r="J27" s="15">
+        <v>-1</v>
+      </c>
+      <c r="N27" s="10"/>
+      <c r="O27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P27" s="9">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>-2.5</v>
+      </c>
+      <c r="R27" s="9" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S27" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="25">
-        <v>24</v>
-      </c>
-      <c r="B27" s="13" t="s">
+    <row r="28" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D27" s="13" t="s">
+      <c r="C28" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F27" s="13">
+      <c r="E28" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F28" s="9">
+        <v>32</v>
+      </c>
+      <c r="G28" s="9">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H28" s="16">
+        <v>-1</v>
+      </c>
+      <c r="I28" s="16">
+        <v>-1</v>
+      </c>
+      <c r="J28" s="16">
+        <v>-1</v>
+      </c>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="P28" s="9">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>-2.5</v>
+      </c>
+      <c r="R28" s="9" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S28" s="9">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F29" s="9">
+        <v>64</v>
+      </c>
+      <c r="G29" s="9">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-1</v>
+      </c>
+      <c r="I29" s="15">
+        <v>-1</v>
+      </c>
+      <c r="J29" s="15">
+        <v>-1</v>
+      </c>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="P29" s="9">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>-2.5</v>
+      </c>
+      <c r="R29" s="9" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S29" s="9">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F30" s="9">
+        <v>128</v>
+      </c>
+      <c r="G30" s="9">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="H30" s="16">
+        <v>-1</v>
+      </c>
+      <c r="I30" s="16">
+        <v>-1</v>
+      </c>
+      <c r="J30" s="16">
+        <v>-1</v>
+      </c>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="P30" s="9">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>-2.5</v>
+      </c>
+      <c r="R30" s="9" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S30" s="9">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F31" s="9">
+        <v>256</v>
+      </c>
+      <c r="G31" s="9">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>3.90625E-3</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-1</v>
+      </c>
+      <c r="I31" s="15">
+        <v>-1</v>
+      </c>
+      <c r="J31" s="15">
+        <v>-1</v>
+      </c>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="P31" s="9">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>-2.5</v>
+      </c>
+      <c r="R31" s="9" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S31" s="9">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="13">
+      <c r="E32" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F32" s="9">
+        <v>16</v>
+      </c>
+      <c r="G32" s="9">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H27" s="23">
-        <v>-1</v>
-      </c>
-      <c r="I27" s="23">
-        <v>-1</v>
-      </c>
-      <c r="J27" s="23">
-        <v>-1</v>
-      </c>
-      <c r="N27" s="14"/>
-      <c r="O27" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="P27" s="13">
+      <c r="H32" s="16">
+        <v>-1</v>
+      </c>
+      <c r="I32" s="16">
+        <v>-1</v>
+      </c>
+      <c r="J32" s="16">
+        <v>-1</v>
+      </c>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="P32" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R27" s="13" t="e">
+      <c r="R32" s="9" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S27" s="19">
+      <c r="S32" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="25">
-        <v>25</v>
-      </c>
-      <c r="B28" s="13" t="s">
+    <row r="33" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F28" s="13">
+      <c r="C33" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F33" s="9">
         <v>32</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G33" s="9">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H28" s="24">
-        <v>-1</v>
-      </c>
-      <c r="I28" s="24">
-        <v>-1</v>
-      </c>
-      <c r="J28" s="24">
-        <v>-1</v>
-      </c>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="P28" s="13">
+      <c r="H33" s="15">
+        <v>-1</v>
+      </c>
+      <c r="I33" s="15">
+        <v>-1</v>
+      </c>
+      <c r="J33" s="15">
+        <v>-1</v>
+      </c>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="P33" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R28" s="13" t="e">
+      <c r="R33" s="9" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S28" s="19">
+      <c r="S33" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="25">
-        <v>26</v>
-      </c>
-      <c r="B29" s="13" t="s">
+    <row r="34" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F29" s="13">
+      <c r="C34" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F34" s="9">
         <v>64</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G34" s="9">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H29" s="23">
-        <v>-1</v>
-      </c>
-      <c r="I29" s="23">
-        <v>-1</v>
-      </c>
-      <c r="J29" s="23">
-        <v>-1</v>
-      </c>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="P29" s="13">
+      <c r="H34" s="16">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="16">
+        <v>-1</v>
+      </c>
+      <c r="J34" s="16">
+        <v>-1</v>
+      </c>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="P34" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R29" s="13" t="e">
+      <c r="R34" s="9" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S29" s="19">
+      <c r="S34" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="25">
-        <v>27</v>
-      </c>
-      <c r="B30" s="13" t="s">
+    <row r="35" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F30" s="13">
+      <c r="C35" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F35" s="9">
         <v>128</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G35" s="9">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H30" s="24">
-        <v>-1</v>
-      </c>
-      <c r="I30" s="24">
-        <v>-1</v>
-      </c>
-      <c r="J30" s="24">
-        <v>-1</v>
-      </c>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="P30" s="13">
+      <c r="H35" s="15">
+        <v>-1</v>
+      </c>
+      <c r="I35" s="15">
+        <v>-1</v>
+      </c>
+      <c r="J35" s="15">
+        <v>-1</v>
+      </c>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="P35" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R30" s="13" t="e">
+      <c r="R35" s="9" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S30" s="19">
+      <c r="S35" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="25">
-        <v>28</v>
-      </c>
-      <c r="B31" s="13" t="s">
+    <row r="36" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F31" s="13">
+      <c r="C36" s="9">
+        <v>-1</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F36" s="9">
         <v>256</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G36" s="9">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H31" s="23">
-        <v>-1</v>
-      </c>
-      <c r="I31" s="23">
-        <v>-1</v>
-      </c>
-      <c r="J31" s="23">
-        <v>-1</v>
-      </c>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="P31" s="13">
+      <c r="H36" s="16">
+        <v>-1</v>
+      </c>
+      <c r="I36" s="16">
+        <v>-1</v>
+      </c>
+      <c r="J36" s="16">
+        <v>-1</v>
+      </c>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="P36" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R31" s="13" t="e">
+      <c r="R36" s="9" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S31" s="19">
+      <c r="S36" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="25">
-        <v>29</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D32" s="13" t="s">
+    <row r="37" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="11">
+        <v>1</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E32" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F32" s="13">
-        <v>16</v>
-      </c>
-      <c r="G32" s="13">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="H32" s="24">
-        <v>-1</v>
-      </c>
-      <c r="I32" s="24">
-        <v>-1</v>
-      </c>
-      <c r="J32" s="24">
-        <v>-1</v>
-      </c>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="P32" s="13">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>-2.5</v>
-      </c>
-      <c r="R32" s="13" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S32" s="19">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="25">
-        <v>30</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F33" s="13">
-        <v>32</v>
-      </c>
-      <c r="G33" s="13">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>3.125E-2</v>
-      </c>
-      <c r="H33" s="23">
-        <v>-1</v>
-      </c>
-      <c r="I33" s="23">
-        <v>-1</v>
-      </c>
-      <c r="J33" s="23">
-        <v>-1</v>
-      </c>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="P33" s="13">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>-2.5</v>
-      </c>
-      <c r="R33" s="13" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S33" s="19">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="25">
-        <v>31</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F34" s="13">
-        <v>64</v>
-      </c>
-      <c r="G34" s="13">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H34" s="24">
-        <v>-1</v>
-      </c>
-      <c r="I34" s="24">
-        <v>-1</v>
-      </c>
-      <c r="J34" s="24">
-        <v>-1</v>
-      </c>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="P34" s="13">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>-2.5</v>
-      </c>
-      <c r="R34" s="13" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S34" s="19">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="25">
-        <v>32</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F35" s="13">
-        <v>128</v>
-      </c>
-      <c r="G35" s="13">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>7.8125E-3</v>
-      </c>
-      <c r="H35" s="23">
-        <v>-1</v>
-      </c>
-      <c r="I35" s="23">
-        <v>-1</v>
-      </c>
-      <c r="J35" s="23">
-        <v>-1</v>
-      </c>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="P35" s="13">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>-2.5</v>
-      </c>
-      <c r="R35" s="13" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S35" s="19">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="25">
-        <v>33</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="13">
-        <v>-1</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F36" s="13">
+      <c r="E37" s="11">
+        <v>1000</v>
+      </c>
+      <c r="F37" s="11">
         <v>256</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G37" s="11">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H36" s="24">
-        <v>-1</v>
-      </c>
-      <c r="I36" s="24">
-        <v>-1</v>
-      </c>
-      <c r="J36" s="24">
-        <v>-1</v>
-      </c>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="P36" s="13">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>-2.5</v>
-      </c>
-      <c r="R36" s="13" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S36" s="19">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="25">
-        <v>34</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="15">
-        <v>1</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F37" s="15">
-        <v>256</v>
-      </c>
-      <c r="G37" s="15">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>3.90625E-3</v>
-      </c>
-      <c r="H37" s="15">
+      <c r="H37" s="11">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="I37" s="15">
+      <c r="I37" s="11">
         <v>2E-3</v>
       </c>
-      <c r="J37" s="15">
+      <c r="J37" s="11">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.51200000000000001</v>
       </c>
-      <c r="K37" s="15">
-        <v>-1</v>
-      </c>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15">
+      <c r="K37" s="11">
+        <v>-1</v>
+      </c>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11">
         <v>42487</v>
       </c>
-      <c r="N37" s="16">
+      <c r="N37" s="12">
         <v>3972.08862</v>
       </c>
-      <c r="O37" s="15" t="s">
+      <c r="O37" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="P37" s="13">
+      <c r="P37" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>1250</v>
       </c>
-      <c r="Q37" s="8">
+      <c r="Q37">
         <v>5000</v>
       </c>
-      <c r="R37" s="11">
+      <c r="R37" s="7">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.4974000000000007</v>
       </c>
-      <c r="S37" s="18">
+      <c r="S37" s="7">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>66.201476999999997</v>
       </c>
@@ -2900,22 +2879,22 @@
       <c r="F38">
         <v>64</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
       <c r="I38">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J38" s="7">
+      <c r="J38">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K38" s="8">
+      <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38" s="1"/>
@@ -2928,16 +2907,15 @@
       <c r="O38" t="s">
         <v>18</v>
       </c>
-      <c r="P38" s="7">
+      <c r="P38">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="7" t="e">
+      <c r="R38" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S38" s="7">
+      <c r="S38">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.60529174833333343</v>
       </c>
@@ -3084,321 +3062,321 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>10.4</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>4.1241166499999997E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F3" s="8">
+      <c r="E3">
+        <v>1000</v>
+      </c>
+      <c r="F3">
         <v>32</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3">
         <f>1/Table523[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3">
         <f>Table523[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3">
         <v>0.05</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3">
         <f>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</f>
         <v>1.6</v>
       </c>
-      <c r="K3" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L3" s="8">
+      <c r="K3">
+        <v>-1</v>
+      </c>
+      <c r="L3">
         <v>0.1</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3">
         <v>860</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="1">
         <v>3.8879101299999999</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="8">
+      <c r="P3">
         <f>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</f>
         <v>862.58019260874914</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q3">
         <v>100</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3">
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>8.6</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>6.4798502166666661E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F4" s="8">
+      <c r="E4">
+        <v>1000</v>
+      </c>
+      <c r="F4">
         <v>64</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4">
         <f>1/Table523[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4">
         <f>Table523[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4">
         <f>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K4" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L4" s="8">
+      <c r="K4">
+        <v>-1</v>
+      </c>
+      <c r="L4">
         <v>0.02</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4">
         <v>3322</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4">
         <v>44.980831100000003</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P4">
         <f>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</f>
         <v>3335.9807572485006</v>
       </c>
-      <c r="Q4" s="8">
+      <c r="Q4">
         <v>250</v>
       </c>
-      <c r="R4" s="8">
+      <c r="R4">
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>13.288</v>
       </c>
-      <c r="S4" s="17">
+      <c r="S4">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0.74968051833333338</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F5" s="8">
+      <c r="E5">
+        <v>1000</v>
+      </c>
+      <c r="F5">
         <v>128</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5">
         <f>1/Table523[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5">
         <f>Table523[[#This Row],[DX]]/1</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5">
         <f>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
-      <c r="K5" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L5" s="8">
+      <c r="K5">
+        <v>-1</v>
+      </c>
+      <c r="L5">
         <v>0.01</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5">
         <v>11952</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="1">
         <v>377.19601399999999</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5">
         <f>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</f>
         <v>12015.493545107956</v>
       </c>
-      <c r="Q5" s="8">
-        <v>1000</v>
-      </c>
-      <c r="R5" s="8">
+      <c r="Q5">
+        <v>1000</v>
+      </c>
+      <c r="R5">
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>11.952</v>
       </c>
-      <c r="S5" s="17">
+      <c r="S5">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>6.2866002333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="E6">
+        <v>1000</v>
+      </c>
+      <c r="F6">
         <v>256</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6">
         <f>1/Table523[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6">
         <f>Table523[[#This Row],[DX]]/1</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6">
         <v>1.5E-3</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6">
         <f>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</f>
         <v>0.38400000000000001</v>
       </c>
-      <c r="K6" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L6" s="8">
+      <c r="K6">
+        <v>-1</v>
+      </c>
+      <c r="L6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6">
         <v>43836</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="1">
         <v>3393.8759799999998</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="8">
+      <c r="P6">
         <f>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</f>
         <v>44121.96309189398</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6">
         <v>5000</v>
       </c>
-      <c r="R6" s="8">
+      <c r="R6">
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>8.7672000000000008</v>
       </c>
-      <c r="S6" s="17">
+      <c r="S6">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>56.564599666666666</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" s="13">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="9">
         <v>1</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="E7" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F7" s="9">
         <v>16</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="9">
         <f>1/Table523[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="9">
         <f>Table523[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="9">
         <v>0.1</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="9">
         <f>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</f>
         <v>1.6</v>
       </c>
-      <c r="K7" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L7" s="13">
+      <c r="K7" s="9">
+        <v>-1</v>
+      </c>
+      <c r="L7" s="9">
         <v>0.15</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="9">
         <v>660</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="10">
         <v>0.53302800699999997</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="O7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="P7" s="13">
+      <c r="P7" s="9">
         <f>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</f>
         <v>661.52145713141385</v>
       </c>
@@ -3406,61 +3384,61 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S7" s="7">
+      <c r="S7">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>8.8838001166666666E-3</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" s="13">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="9">
         <v>1</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F8" s="13">
+      <c r="E8" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F8" s="9">
         <v>32</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="9">
         <f>1/Table523[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="9">
         <f>Table523[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="9">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="9">
         <f>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</f>
         <v>0.8</v>
       </c>
-      <c r="K8" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L8" s="13">
+      <c r="K8" s="9">
+        <v>-1</v>
+      </c>
+      <c r="L8" s="9">
         <v>0.05</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="9">
         <v>1940</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="10">
         <v>5.9802618000000001</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="O8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="9">
         <f>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</f>
         <v>1947.1696419832119</v>
       </c>
@@ -3468,61 +3446,61 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S8" s="7">
+      <c r="S8">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>9.9671030000000008E-2</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" s="13">
+      <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="9">
         <v>1</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F9" s="13">
+      <c r="E9" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="9">
         <v>64</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="9">
         <f>1/Table523[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="9">
         <f>Table523[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="9">
         <f>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K9" s="13">
-        <v>-1</v>
-      </c>
-      <c r="L9" s="13">
+      <c r="K9" s="9">
+        <v>-1</v>
+      </c>
+      <c r="L9" s="9">
         <v>0.02</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="9">
         <v>4200</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="10">
         <v>79.461456299999995</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="13">
+      <c r="P9" s="9">
         <f>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</f>
         <v>4217.6758520300127</v>
       </c>
@@ -3530,59 +3508,58 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S9" s="7">
+      <c r="S9">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>1.3243576049999999</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="8">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="E10">
+        <v>1000</v>
+      </c>
+      <c r="F10">
         <v>128</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10">
         <f>1/Table523[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10">
         <f>Table523[[#This Row],[DX]]/1</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10">
         <f>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K10" s="8">
-        <v>-1</v>
-      </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8">
+      <c r="K10">
+        <v>-1</v>
+      </c>
+      <c r="M10">
         <v>11900</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="1">
         <v>573.28375200000005</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="O10" t="s">
         <v>17</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10">
         <f>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</f>
         <v>11958.367617496613</v>
       </c>
@@ -3593,70 +3570,70 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>11.9</v>
       </c>
-      <c r="S10" s="7">
+      <c r="S10">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>9.5547292000000006</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="11" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+    <row r="11" spans="1:19" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
         <v>10</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="11">
         <v>1</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F11" s="15">
+      <c r="E11" s="11">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="11">
         <v>256</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="11">
         <f>1/Table523[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="11">
         <f>Table523[[#This Row],[DX]]/1</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="11">
         <v>2E-3</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="11">
         <f>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</f>
         <v>0.51200000000000001</v>
       </c>
-      <c r="K11" s="15">
-        <v>-1</v>
-      </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15">
+      <c r="K11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11">
         <v>42487</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="12">
         <v>3972.08862</v>
       </c>
-      <c r="O11" s="15" t="s">
+      <c r="O11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="9">
         <f>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</f>
         <v>42751.862209248735</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11">
         <v>5000</v>
       </c>
-      <c r="R11" s="11">
+      <c r="R11" s="7">
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>8.4974000000000007</v>
       </c>
-      <c r="S11" s="18">
+      <c r="S11" s="7">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>66.201476999999997</v>
       </c>
@@ -3707,7 +3684,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S12" s="7">
+      <c r="S12">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -3758,7 +3735,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S13" s="7">
+      <c r="S13">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -3809,7 +3786,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S14" s="7">
+      <c r="S14">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -3860,7 +3837,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S15" s="7">
+      <c r="S15">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -3912,7 +3889,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S16" s="9">
+      <c r="S16" s="3">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -3961,7 +3938,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S17" s="7">
+      <c r="S17">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -4008,7 +3985,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S18" s="7">
+      <c r="S18">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -4055,7 +4032,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S19" s="7">
+      <c r="S19">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -4102,7 +4079,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S20" s="7">
+      <c r="S20">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -4149,7 +4126,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S21" s="7">
+      <c r="S21">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -4196,7 +4173,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S22" s="7">
+      <c r="S22">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -4243,7 +4220,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S23" s="7">
+      <c r="S23">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -4290,7 +4267,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S24" s="7">
+      <c r="S24">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -4337,7 +4314,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S25" s="7">
+      <c r="S25">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -4384,7 +4361,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S26" s="7">
+      <c r="S26">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
@@ -4401,7 +4378,7 @@
         <f>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S27" s="7">
+      <c r="S27">
         <f>Table523[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>

--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annashen/Desktop/code/ME663-project/postprocess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05523EA5-9B93-A840-9090-CBFD9100858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{62F2A2A3-FED6-4241-BF7C-386EC2465B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="700" windowWidth="25940" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
@@ -233,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -251,6 +251,9 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2325,152 +2328,176 @@
         <v>1.2963990533333332</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>24</v>
-      </c>
-      <c r="B27" s="9" t="s">
+    <row r="27" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="17">
+        <v>26</v>
+      </c>
+      <c r="B27" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D27" s="9" t="s">
+      <c r="C27" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D27" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F27" s="9">
+      <c r="E27" s="17">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="17">
         <v>16</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="17">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H27" s="15">
-        <v>-1</v>
-      </c>
-      <c r="I27" s="15">
-        <v>-1</v>
-      </c>
-      <c r="J27" s="15">
-        <v>-1</v>
-      </c>
-      <c r="N27" s="10"/>
-      <c r="O27" s="9" t="s">
+      <c r="H27" s="18">
+        <v>-1</v>
+      </c>
+      <c r="I27" s="18">
+        <v>-1</v>
+      </c>
+      <c r="J27" s="18">
+        <v>-1</v>
+      </c>
+      <c r="K27" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="M27" s="17">
+        <v>294</v>
+      </c>
+      <c r="N27" s="19">
+        <v>7.18609989E-2</v>
+      </c>
+      <c r="O27" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="P27" s="9">
+      <c r="P27" s="17">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R27" s="9" t="e">
+      <c r="R27" s="17" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S27" s="9">
+      <c r="S27" s="17">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>25</v>
-      </c>
-      <c r="B28" s="9" t="s">
+        <v>1.197683315E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="17">
+        <v>27</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="C28" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D28" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F28" s="9">
+      <c r="E28" s="17">
+        <v>1000</v>
+      </c>
+      <c r="F28" s="17">
         <v>32</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="17">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H28" s="16">
-        <v>-1</v>
-      </c>
-      <c r="I28" s="16">
-        <v>-1</v>
-      </c>
-      <c r="J28" s="16">
-        <v>-1</v>
-      </c>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="P28" s="9">
+      <c r="H28" s="18">
+        <v>-1</v>
+      </c>
+      <c r="I28" s="18">
+        <v>-1</v>
+      </c>
+      <c r="J28" s="18">
+        <v>-1</v>
+      </c>
+      <c r="K28" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19">
+        <v>460</v>
+      </c>
+      <c r="N28" s="17">
+        <v>0.33705398399999997</v>
+      </c>
+      <c r="P28" s="17">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R28" s="9" t="e">
+      <c r="R28" s="17" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S28" s="9">
+      <c r="S28" s="17">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>26</v>
-      </c>
-      <c r="B29" s="9" t="s">
+        <v>5.6175663999999993E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="17">
+        <v>28</v>
+      </c>
+      <c r="B29" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D29" s="9" t="s">
+      <c r="C29" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D29" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F29" s="9">
+      <c r="E29" s="17">
+        <v>1000</v>
+      </c>
+      <c r="F29" s="17">
         <v>64</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="17">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H29" s="15">
-        <v>-1</v>
-      </c>
-      <c r="I29" s="15">
-        <v>-1</v>
-      </c>
-      <c r="J29" s="15">
-        <v>-1</v>
-      </c>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="P29" s="9">
+      <c r="H29" s="18">
+        <v>-1</v>
+      </c>
+      <c r="I29" s="18">
+        <v>-1</v>
+      </c>
+      <c r="J29" s="18">
+        <v>-1</v>
+      </c>
+      <c r="K29" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19">
+        <v>955</v>
+      </c>
+      <c r="N29" s="17">
+        <v>2.6180739399999999</v>
+      </c>
+      <c r="P29" s="17">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R29" s="9" t="e">
+      <c r="R29" s="17" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S29" s="9">
+      <c r="S29" s="17">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>4.3634565666666666E-2</v>
       </c>
     </row>
     <row r="30" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>19</v>
@@ -2517,7 +2544,7 @@
     </row>
     <row r="31" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>19</v>
@@ -2564,7 +2591,7 @@
     </row>
     <row r="32" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>19</v>
@@ -2611,7 +2638,7 @@
     </row>
     <row r="33" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>19</v>
@@ -2658,7 +2685,7 @@
     </row>
     <row r="34" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>19</v>
@@ -2705,7 +2732,7 @@
     </row>
     <row r="35" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>19</v>
@@ -2752,7 +2779,7 @@
     </row>
     <row r="36" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>19</v>
@@ -2799,7 +2826,7 @@
     </row>
     <row r="37" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>12</v>

--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annashen/Desktop/code/ME663-project/postprocess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{62F2A2A3-FED6-4241-BF7C-386EC2465B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{9B10DABA-AC87-1644-94E9-AD62DFBDFD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="700" windowWidth="25940" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
+    <workbookView xWindow="1260" yWindow="500" windowWidth="25940" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="30">
   <si>
     <t>case</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t>Time (min)</t>
+  </si>
+  <si>
+    <t>URFU</t>
+  </si>
+  <si>
+    <t>URFP</t>
   </si>
 </sst>
 </file>
@@ -233,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -254,6 +260,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -343,9 +352,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:S38" totalsRowShown="0">
-  <autoFilter ref="A1:S38" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
-  <tableColumns count="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T38" totalsRowShown="0">
+  <autoFilter ref="A1:T38" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
+  <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{F042FD67-138A-3747-8F7D-92055EB26E1F}" name="case"/>
     <tableColumn id="19" xr3:uid="{6D3F4F6F-712A-EA45-8F90-560AA5EB3396}" name="solution_method"/>
     <tableColumn id="21" xr3:uid="{0FCB0505-3853-1D4B-812F-918F6E1D4857}" name="time_scheme"/>
@@ -362,7 +371,8 @@
     <tableColumn id="22" xr3:uid="{F37937B1-F618-9544-858E-9C385880A578}" name="CFL" dataDxfId="17">
       <calculatedColumnFormula>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{57BAD542-64CC-254E-88F0-83BA2685E4ED}" name="URF" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{CC46E7B8-FF0D-C94B-AE73-961311865B19}" name="URFP"/>
+    <tableColumn id="16" xr3:uid="{57BAD542-64CC-254E-88F0-83BA2685E4ED}" name="URFU" dataDxfId="16"/>
     <tableColumn id="9" xr3:uid="{CF78813F-1FCF-E643-8377-72AF6325BEEE}" name="diverging_factor" dataDxfId="15"/>
     <tableColumn id="25" xr3:uid="{B19A7E44-6A26-8B41-BA69-77F75344DEA3}" name="IT" dataDxfId="14"/>
     <tableColumn id="11" xr3:uid="{F124CBF0-B3EB-C444-B55D-C50EED146627}" name="clock_time"/>
@@ -739,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8141C424-3935-5946-8401-AC39630593AC}">
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="13.6640625" customWidth="1"/>
@@ -748,7 +758,7 @@
     <col min="8" max="8" width="11.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -780,34 +790,37 @@
         <v>23</v>
       </c>
       <c r="K1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>8</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>10</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>11</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -841,38 +854,38 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>2.4</v>
       </c>
-      <c r="K2">
-        <v>-1</v>
-      </c>
       <c r="L2">
+        <v>-1</v>
+      </c>
+      <c r="M2">
         <v>0.2</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>260</v>
       </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>0.247446999</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>14</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>16.666666666666668</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>25</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>10.4</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>4.1241166499999997E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -906,38 +919,38 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>1.6</v>
       </c>
-      <c r="K3">
-        <v>-1</v>
-      </c>
       <c r="L3">
+        <v>-1</v>
+      </c>
+      <c r="M3">
         <v>0.1</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>860</v>
       </c>
-      <c r="N3" s="1">
+      <c r="O3" s="1">
         <v>3.8879101299999999</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>14</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>50</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>100</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.6</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.4798502166666661E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -971,38 +984,38 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K4">
-        <v>-1</v>
-      </c>
       <c r="L4">
+        <v>-1</v>
+      </c>
+      <c r="M4">
         <v>0.02</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>3322</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>44.980831100000003</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>14</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>250</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>13.288</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.74968051833333338</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1036,38 +1049,38 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
-      <c r="K5">
-        <v>-1</v>
-      </c>
       <c r="L5">
+        <v>-1</v>
+      </c>
+      <c r="M5">
         <v>0.01</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>11952</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>377.19601399999999</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>14</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>500</v>
       </c>
-      <c r="Q5">
-        <v>1000</v>
-      </c>
       <c r="R5">
+        <v>1000</v>
+      </c>
+      <c r="S5">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>11.952</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.2866002333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1101,38 +1114,38 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.38400000000000001</v>
       </c>
-      <c r="K6">
-        <v>-1</v>
-      </c>
       <c r="L6">
+        <v>-1</v>
+      </c>
+      <c r="M6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>43836</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>3393.8759799999998</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>15</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>1666.6666666666667</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>5000</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.7672000000000008</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>56.564599666666666</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1166,38 +1179,38 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>1.6</v>
       </c>
-      <c r="K7">
-        <v>-1</v>
-      </c>
       <c r="L7">
+        <v>-1</v>
+      </c>
+      <c r="M7">
         <v>0.15</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>675</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>0.43378701800000002</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>15</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>25</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>50</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>13.5</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>7.2297836333333337E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1231,38 +1244,38 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.8</v>
       </c>
-      <c r="K8">
-        <v>-1</v>
-      </c>
       <c r="L8">
+        <v>-1</v>
+      </c>
+      <c r="M8">
         <v>0.05</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>1941</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>4.5700812300000004</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>15</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>100</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>250</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.7640000000000002</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>7.6168020500000003E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1296,38 +1309,38 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K9">
-        <v>-1</v>
-      </c>
       <c r="L9">
+        <v>-1</v>
+      </c>
+      <c r="M9">
         <v>0.02</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>4202</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>61.105514499999998</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>15</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>500</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.4039999999999999</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.0184252416666666</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1361,35 +1374,35 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K10">
-        <v>-1</v>
-      </c>
-      <c r="M10">
+      <c r="L10">
+        <v>-1</v>
+      </c>
+      <c r="N10">
         <v>11902</v>
       </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <v>567.30658000000005</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>17</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>333.33333333333337</v>
       </c>
-      <c r="Q10">
-        <v>1000</v>
-      </c>
       <c r="R10">
+        <v>1000</v>
+      </c>
+      <c r="S10">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>11.901999999999999</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>9.455109666666667</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>10</v>
       </c>
@@ -1423,36 +1436,37 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.51200000000000001</v>
       </c>
-      <c r="K11" s="11">
-        <v>-1</v>
-      </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11">
+      <c r="K11" s="11"/>
+      <c r="L11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11">
         <v>42487</v>
       </c>
-      <c r="N11" s="12">
+      <c r="O11" s="12">
         <v>3972.08862</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="P11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="P11" s="9">
+      <c r="Q11" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>1250</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>5000</v>
       </c>
-      <c r="R11" s="7">
+      <c r="S11" s="7">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.4974000000000007</v>
       </c>
-      <c r="S11" s="7">
+      <c r="T11" s="7">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>66.201476999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1486,38 +1500,38 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>2.4</v>
       </c>
-      <c r="K12">
-        <v>-1</v>
-      </c>
       <c r="L12">
+        <v>-1</v>
+      </c>
+      <c r="M12">
         <v>0.2</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>259</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <v>0.234771013</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>17</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>16.666666666666668</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>25</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>10.36</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>3.9128502166666671E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1551,35 +1565,35 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>1.6</v>
       </c>
-      <c r="K13">
-        <v>-1</v>
-      </c>
-      <c r="M13">
+      <c r="L13">
+        <v>-1</v>
+      </c>
+      <c r="N13">
         <v>857</v>
       </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
         <v>3.7937221499999998</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>17</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>50</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>100</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.57</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.3228702499999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1613,36 +1627,36 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K14">
-        <v>-1</v>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1">
+      <c r="L14">
+        <v>-1</v>
+      </c>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1">
         <v>332</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <v>43.591610000000003</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>18</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>250</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>1.3280000000000001</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.72652683333333334</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1676,35 +1690,35 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
-      <c r="K15">
-        <v>-1</v>
-      </c>
-      <c r="M15">
+      <c r="L15">
+        <v>-1</v>
+      </c>
+      <c r="N15">
         <v>11952</v>
       </c>
-      <c r="N15" s="1">
+      <c r="O15" s="1">
         <v>392.12469499999997</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>18</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>500</v>
       </c>
-      <c r="Q15">
-        <v>1000</v>
-      </c>
       <c r="R15">
+        <v>1000</v>
+      </c>
+      <c r="S15">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>11.952</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.5354115833333326</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="13" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" s="13" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -1735,30 +1749,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K16" s="13">
-        <v>-1</v>
-      </c>
-      <c r="N16" s="14"/>
-      <c r="O16" s="13" t="s">
+      <c r="L16" s="13">
+        <v>-1</v>
+      </c>
+      <c r="O16" s="14"/>
+      <c r="P16" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="P16" s="13" t="e">
+      <c r="Q16" s="13" t="e">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>5000</v>
       </c>
-      <c r="R16" s="13">
+      <c r="S16" s="13">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>0</v>
       </c>
-      <c r="S16" s="13">
+      <c r="T16" s="13">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1792,30 +1806,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1">
+      <c r="M17" s="1"/>
+      <c r="N17" s="1">
         <v>4202</v>
       </c>
-      <c r="N17" s="1">
+      <c r="O17" s="1">
         <v>64.518783600000006</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>500</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.4039999999999999</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.07531306</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1849,30 +1863,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1">
+      <c r="M18" s="1"/>
+      <c r="N18" s="1">
         <v>5552</v>
       </c>
-      <c r="N18" s="1">
+      <c r="O18" s="1">
         <v>48.560310399999999</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>250</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>750</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.4026666666666667</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.80933850666666662</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1906,30 +1920,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.32</v>
       </c>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1">
+      <c r="M19" s="1"/>
+      <c r="N19" s="1">
         <v>9328</v>
       </c>
-      <c r="N19" s="1">
+      <c r="O19" s="1">
         <v>34.663536100000002</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>500</v>
       </c>
-      <c r="Q19">
-        <v>1000</v>
-      </c>
       <c r="R19">
+        <v>1000</v>
+      </c>
+      <c r="S19">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>9.3279999999999994</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.57772560166666664</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1963,30 +1977,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1">
+      <c r="M20" s="1"/>
+      <c r="N20" s="1">
         <v>35260</v>
       </c>
-      <c r="N20" s="1">
+      <c r="O20" s="1">
         <v>47.817623099999999</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>2500</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>5000</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.0519999999999996</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.79696038499999999</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -2020,30 +2034,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8">
+      <c r="M21" s="8"/>
+      <c r="N21" s="8">
         <v>63517</v>
       </c>
-      <c r="N21" s="8">
+      <c r="O21" s="8">
         <v>76.141212499999995</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>5000</v>
       </c>
-      <c r="Q21" s="7">
+      <c r="R21" s="7">
         <v>15000</v>
       </c>
-      <c r="R21" s="7">
+      <c r="S21" s="7">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>4.234466666666667</v>
       </c>
-      <c r="S21" s="7">
+      <c r="T21" s="7">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2690202083333333</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2077,30 +2091,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1">
+      <c r="M22" s="1"/>
+      <c r="N22" s="1">
         <v>4190</v>
       </c>
-      <c r="N22" s="1">
+      <c r="O22" s="1">
         <v>58.056365999999997</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>500</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.3800000000000008</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.96760609999999991</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2134,30 +2148,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1">
+      <c r="M23" s="1"/>
+      <c r="N23" s="1">
         <v>5551</v>
       </c>
-      <c r="N23" s="1">
+      <c r="O23" s="1">
         <v>49.9791794</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>250</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>750</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.4013333333333335</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.83298632333333333</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2191,30 +2205,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.32</v>
       </c>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1">
+      <c r="M24" s="1"/>
+      <c r="N24" s="1">
         <v>9339</v>
       </c>
-      <c r="N24" s="1">
+      <c r="O24" s="1">
         <v>35.158287000000001</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>500</v>
       </c>
-      <c r="Q24">
-        <v>1000</v>
-      </c>
       <c r="R24">
+        <v>1000</v>
+      </c>
+      <c r="S24">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>9.3390000000000004</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.58597145000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2248,30 +2262,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1">
+      <c r="M25" s="1"/>
+      <c r="N25" s="1">
         <v>35262</v>
       </c>
-      <c r="N25" s="1">
+      <c r="O25" s="1">
         <v>46.530872299999999</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>2500</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>5000</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.0523999999999996</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.77551453833333328</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2305,30 +2319,30 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1">
+      <c r="M26" s="1"/>
+      <c r="N26" s="1">
         <v>63500</v>
       </c>
-      <c r="N26" s="1">
+      <c r="O26" s="1">
         <v>77.783943199999996</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>5000</v>
       </c>
-      <c r="Q26" s="7">
+      <c r="R26" s="7">
         <v>15000</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>4.2333333333333334</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2963990533333332</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="17">
         <v>26</v>
       </c>
@@ -2360,32 +2374,35 @@
       <c r="J27" s="18">
         <v>-1</v>
       </c>
-      <c r="K27" s="17">
+      <c r="K27" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="L27" s="17">
         <v>0.85</v>
       </c>
-      <c r="M27" s="17">
+      <c r="N27" s="17">
         <v>294</v>
       </c>
-      <c r="N27" s="19">
+      <c r="O27" s="19">
         <v>7.18609989E-2</v>
       </c>
-      <c r="O27" s="17" t="s">
+      <c r="P27" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="P27" s="17">
+      <c r="Q27" s="17">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R27" s="17" t="e">
+      <c r="S27" s="17" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S27" s="17">
+      <c r="T27" s="17">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.197683315E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="17">
         <v>27</v>
       </c>
@@ -2417,30 +2434,33 @@
       <c r="J28" s="18">
         <v>-1</v>
       </c>
-      <c r="K28" s="17">
+      <c r="K28" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="L28" s="17">
         <v>0.75</v>
       </c>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19">
+      <c r="M28" s="19"/>
+      <c r="N28" s="19">
         <v>460</v>
       </c>
-      <c r="N28" s="17">
+      <c r="O28" s="17">
         <v>0.33705398399999997</v>
       </c>
-      <c r="P28" s="17">
+      <c r="Q28" s="17">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R28" s="17" t="e">
+      <c r="S28" s="17" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S28" s="17">
+      <c r="T28" s="17">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.6175663999999993E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="17">
         <v>28</v>
       </c>
@@ -2472,124 +2492,149 @@
       <c r="J29" s="18">
         <v>-1</v>
       </c>
-      <c r="K29" s="17">
+      <c r="K29" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="L29" s="17">
         <v>0.7</v>
       </c>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19">
+      <c r="M29" s="19"/>
+      <c r="N29" s="19">
         <v>955</v>
       </c>
-      <c r="N29" s="17">
+      <c r="O29" s="17">
         <v>2.6180739399999999</v>
       </c>
-      <c r="P29" s="17">
+      <c r="Q29" s="17">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R29" s="17" t="e">
+      <c r="S29" s="17" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S29" s="17">
+      <c r="T29" s="17">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>4.3634565666666666E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30">
+    <row r="30" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="17">
         <v>29</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D30" s="9" t="s">
+      <c r="C30" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D30" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F30" s="9">
+      <c r="E30" s="17">
+        <v>1000</v>
+      </c>
+      <c r="F30" s="17">
         <v>128</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="17">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H30" s="16">
-        <v>-1</v>
-      </c>
-      <c r="I30" s="16">
-        <v>-1</v>
-      </c>
-      <c r="J30" s="16">
-        <v>-1</v>
-      </c>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="P30" s="9">
+      <c r="H30" s="18">
+        <v>-1</v>
+      </c>
+      <c r="I30" s="18">
+        <v>-1</v>
+      </c>
+      <c r="J30" s="18">
+        <v>-1</v>
+      </c>
+      <c r="K30" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="L30" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19">
+        <v>2808</v>
+      </c>
+      <c r="O30" s="17">
+        <v>31.147777600000001</v>
+      </c>
+      <c r="Q30" s="17">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R30" s="9" t="e">
+      <c r="S30" s="17" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S30" s="9">
+      <c r="T30" s="17">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31">
+        <v>0.51912962666666673</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="17">
         <v>30</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D31" s="9" t="s">
+      <c r="C31" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D31" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F31" s="9">
+      <c r="E31" s="17">
+        <v>1000</v>
+      </c>
+      <c r="F31" s="17">
         <v>256</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="17">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H31" s="15">
-        <v>-1</v>
-      </c>
-      <c r="I31" s="15">
-        <v>-1</v>
-      </c>
-      <c r="J31" s="15">
-        <v>-1</v>
-      </c>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="P31" s="9">
+      <c r="H31" s="18">
+        <v>-1</v>
+      </c>
+      <c r="I31" s="18">
+        <v>-1</v>
+      </c>
+      <c r="J31" s="18">
+        <v>-1</v>
+      </c>
+      <c r="K31" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="L31" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19">
+        <v>7290</v>
+      </c>
+      <c r="O31" s="17">
+        <v>421.73425300000002</v>
+      </c>
+      <c r="Q31" s="17">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R31" s="9" t="e">
+      <c r="S31" s="17" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S31" s="9">
+      <c r="T31" s="17">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>7.0289042166666666</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2621,22 +2666,23 @@
       <c r="J32" s="16">
         <v>-1</v>
       </c>
-      <c r="L32" s="10"/>
+      <c r="K32" s="21"/>
       <c r="M32" s="10"/>
-      <c r="P32" s="9">
+      <c r="N32" s="10"/>
+      <c r="Q32" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R32" s="9" t="e">
+      <c r="S32" s="9" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S32" s="9">
+      <c r="T32" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2668,22 +2714,23 @@
       <c r="J33" s="15">
         <v>-1</v>
       </c>
-      <c r="L33" s="10"/>
+      <c r="K33" s="22"/>
       <c r="M33" s="10"/>
-      <c r="P33" s="9">
+      <c r="N33" s="10"/>
+      <c r="Q33" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R33" s="9" t="e">
+      <c r="S33" s="9" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S33" s="9">
+      <c r="T33" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2715,22 +2762,23 @@
       <c r="J34" s="16">
         <v>-1</v>
       </c>
-      <c r="L34" s="10"/>
+      <c r="K34" s="21"/>
       <c r="M34" s="10"/>
-      <c r="P34" s="9">
+      <c r="N34" s="10"/>
+      <c r="Q34" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R34" s="9" t="e">
+      <c r="S34" s="9" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S34" s="9">
+      <c r="T34" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2762,22 +2810,23 @@
       <c r="J35" s="15">
         <v>-1</v>
       </c>
-      <c r="L35" s="10"/>
+      <c r="K35" s="22"/>
       <c r="M35" s="10"/>
-      <c r="P35" s="9">
+      <c r="N35" s="10"/>
+      <c r="Q35" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R35" s="9" t="e">
+      <c r="S35" s="9" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S35" s="9">
+      <c r="T35" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2809,22 +2858,23 @@
       <c r="J36" s="16">
         <v>-1</v>
       </c>
-      <c r="L36" s="10"/>
+      <c r="K36" s="21"/>
       <c r="M36" s="10"/>
-      <c r="P36" s="9">
+      <c r="N36" s="10"/>
+      <c r="Q36" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="R36" s="9" t="e">
+      <c r="S36" s="9" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S36" s="9">
+      <c r="T36" s="9">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2858,36 +2908,37 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.51200000000000001</v>
       </c>
-      <c r="K37" s="11">
-        <v>-1</v>
-      </c>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11">
+      <c r="K37" s="11"/>
+      <c r="L37" s="11">
+        <v>-1</v>
+      </c>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11">
         <v>42487</v>
       </c>
-      <c r="N37" s="12">
+      <c r="O37" s="12">
         <v>3972.08862</v>
       </c>
-      <c r="O37" s="11" t="s">
+      <c r="P37" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="P37" s="9">
+      <c r="Q37" s="9">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>1250</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>5000</v>
       </c>
-      <c r="R37" s="7">
+      <c r="S37" s="7">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>8.4974000000000007</v>
       </c>
-      <c r="S37" s="7">
+      <c r="T37" s="7">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>66.201476999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>13.1</v>
       </c>
@@ -2921,28 +2972,28 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="K38">
-        <v>-1</v>
-      </c>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1">
+      <c r="L38">
+        <v>-1</v>
+      </c>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1">
         <v>4576</v>
       </c>
-      <c r="N38" s="1">
+      <c r="O38" s="1">
         <v>36.317504900000003</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>18</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="R38" t="e">
+      <c r="S38" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S38">
+      <c r="T38">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.60529174833333343</v>
       </c>

--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annashen/Desktop/code/ME663-project/postprocess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{9B10DABA-AC87-1644-94E9-AD62DFBDFD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{74F324A3-25D9-0640-A921-253E875B9788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="500" windowWidth="25940" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
+    <workbookView xWindow="1240" yWindow="500" windowWidth="29120" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="30">
   <si>
     <t>case</t>
   </si>
@@ -191,12 +191,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -235,11 +235,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -255,14 +295,24 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -352,8 +402,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T38" totalsRowShown="0">
-  <autoFilter ref="A1:T38" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T45" totalsRowShown="0">
+  <autoFilter ref="A1:T45" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{F042FD67-138A-3747-8F7D-92055EB26E1F}" name="case"/>
     <tableColumn id="19" xr3:uid="{6D3F4F6F-712A-EA45-8F90-560AA5EB3396}" name="solution_method"/>
@@ -749,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8141C424-3935-5946-8401-AC39630593AC}">
-  <dimension ref="A1:T38"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="13.6640625" customWidth="1"/>
@@ -950,67 +1000,67 @@
         <v>6.4798502166666661E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row r="4" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="15">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="15">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E4">
-        <v>1000</v>
-      </c>
-      <c r="F4">
+      <c r="E4" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F4" s="15">
         <v>64</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="15">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="15">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="15">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="15">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="L4">
-        <v>-1</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="15">
+        <v>-1</v>
+      </c>
+      <c r="M4" s="15">
         <v>0.02</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="15">
         <v>3322</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="15">
         <v>44.980831100000003</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="15">
         <v>250</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="15">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>13.288</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.74968051833333338</v>
       </c>
@@ -2342,619 +2392,678 @@
         <v>1.2963990533333332</v>
       </c>
     </row>
-    <row r="27" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="17">
+    <row r="27" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="18">
         <v>26</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="17">
-        <v>-1</v>
-      </c>
-      <c r="D27" s="17" t="s">
+      <c r="C27" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D27" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="17">
-        <v>1000</v>
-      </c>
-      <c r="F27" s="17">
+      <c r="E27" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="18">
         <v>16</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="18">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H27" s="18">
-        <v>-1</v>
-      </c>
-      <c r="I27" s="18">
-        <v>-1</v>
-      </c>
-      <c r="J27" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K27" s="20">
+      <c r="H27" s="19">
+        <v>-1</v>
+      </c>
+      <c r="I27" s="19">
+        <v>-1</v>
+      </c>
+      <c r="J27" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K27" s="21">
         <v>0.3</v>
       </c>
-      <c r="L27" s="17">
+      <c r="L27" s="18">
         <v>0.85</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N27" s="18">
         <v>294</v>
       </c>
-      <c r="O27" s="19">
+      <c r="O27" s="20">
         <v>7.18609989E-2</v>
       </c>
-      <c r="P27" s="17" t="s">
+      <c r="P27" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="Q27" s="17">
+      <c r="Q27" s="18">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S27" s="17" t="e">
+      <c r="S27" s="18" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T27" s="17">
+      <c r="T27" s="18">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.197683315E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="17">
+    <row r="28" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="18">
         <v>27</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="17">
-        <v>-1</v>
-      </c>
-      <c r="D28" s="17" t="s">
+      <c r="C28" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D28" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="17">
-        <v>1000</v>
-      </c>
-      <c r="F28" s="17">
+      <c r="E28" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F28" s="18">
         <v>32</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="18">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H28" s="18">
-        <v>-1</v>
-      </c>
-      <c r="I28" s="18">
-        <v>-1</v>
-      </c>
-      <c r="J28" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K28" s="20">
+      <c r="H28" s="19">
+        <v>-1</v>
+      </c>
+      <c r="I28" s="19">
+        <v>-1</v>
+      </c>
+      <c r="J28" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K28" s="21">
         <v>0.3</v>
       </c>
-      <c r="L28" s="17">
+      <c r="L28" s="18">
         <v>0.75</v>
       </c>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19">
+      <c r="M28" s="20"/>
+      <c r="N28" s="20">
         <v>460</v>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="18">
         <v>0.33705398399999997</v>
       </c>
-      <c r="Q28" s="17">
+      <c r="Q28" s="18">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S28" s="17" t="e">
+      <c r="S28" s="18" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T28" s="17">
+      <c r="T28" s="18">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.6175663999999993E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="17">
+    <row r="29" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="18">
         <v>28</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="17">
-        <v>-1</v>
-      </c>
-      <c r="D29" s="17" t="s">
+      <c r="C29" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D29" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="17">
-        <v>1000</v>
-      </c>
-      <c r="F29" s="17">
+      <c r="E29" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F29" s="18">
         <v>64</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="18">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H29" s="18">
-        <v>-1</v>
-      </c>
-      <c r="I29" s="18">
-        <v>-1</v>
-      </c>
-      <c r="J29" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K29" s="20">
+      <c r="H29" s="19">
+        <v>-1</v>
+      </c>
+      <c r="I29" s="19">
+        <v>-1</v>
+      </c>
+      <c r="J29" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K29" s="21">
         <v>0.3</v>
       </c>
-      <c r="L29" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19">
-        <v>955</v>
-      </c>
-      <c r="O29" s="17">
-        <v>2.6180739399999999</v>
-      </c>
-      <c r="Q29" s="17">
+      <c r="L29" s="18">
+        <v>0.78</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20">
+        <v>1279</v>
+      </c>
+      <c r="O29" s="18">
+        <v>3.5678272199999999</v>
+      </c>
+      <c r="Q29" s="18">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S29" s="17" t="e">
+      <c r="S29" s="18" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T29" s="17">
+      <c r="T29" s="18">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>4.3634565666666666E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="17">
+        <v>5.9463786999999997E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="18">
         <v>29</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="17">
-        <v>-1</v>
-      </c>
-      <c r="D30" s="17" t="s">
+      <c r="C30" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D30" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="17">
-        <v>1000</v>
-      </c>
-      <c r="F30" s="17">
+      <c r="E30" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F30" s="18">
         <v>128</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="18">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H30" s="18">
-        <v>-1</v>
-      </c>
-      <c r="I30" s="18">
-        <v>-1</v>
-      </c>
-      <c r="J30" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K30" s="20">
+      <c r="H30" s="19">
+        <v>-1</v>
+      </c>
+      <c r="I30" s="19">
+        <v>-1</v>
+      </c>
+      <c r="J30" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K30" s="21">
         <v>0.3</v>
       </c>
-      <c r="L30" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19">
-        <v>2808</v>
-      </c>
-      <c r="O30" s="17">
-        <v>31.147777600000001</v>
-      </c>
-      <c r="Q30" s="17">
+      <c r="L30" s="18">
+        <v>0.99</v>
+      </c>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20">
+        <v>1882</v>
+      </c>
+      <c r="O30" s="18">
+        <v>20.745883899999999</v>
+      </c>
+      <c r="Q30" s="18">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S30" s="17" t="e">
+      <c r="S30" s="18" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T30" s="17">
+      <c r="T30" s="18">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0.51912962666666673</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="17">
+        <v>0.34576473166666666</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" s="22" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22">
         <v>30</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="17">
-        <v>-1</v>
-      </c>
-      <c r="D31" s="17" t="s">
+      <c r="C31" s="22">
+        <v>-1</v>
+      </c>
+      <c r="D31" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="17">
-        <v>1000</v>
-      </c>
-      <c r="F31" s="17">
+      <c r="E31" s="22">
+        <v>1000</v>
+      </c>
+      <c r="F31" s="22">
         <v>256</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="22">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H31" s="18">
-        <v>-1</v>
-      </c>
-      <c r="I31" s="18">
-        <v>-1</v>
-      </c>
-      <c r="J31" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K31" s="20">
+      <c r="H31" s="23">
+        <v>-1</v>
+      </c>
+      <c r="I31" s="23">
+        <v>-1</v>
+      </c>
+      <c r="J31" s="23">
+        <v>-1</v>
+      </c>
+      <c r="K31" s="24">
         <v>0.3</v>
       </c>
-      <c r="L31" s="17">
+      <c r="L31" s="22">
         <v>0.7</v>
       </c>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19">
+      <c r="M31" s="25"/>
+      <c r="N31" s="25">
         <v>7290</v>
       </c>
-      <c r="O31" s="17">
+      <c r="O31" s="22">
         <v>421.73425300000002</v>
       </c>
-      <c r="Q31" s="17">
+      <c r="Q31" s="22">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S31" s="17" t="e">
+      <c r="S31" s="22" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T31" s="17">
+      <c r="T31" s="22">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>7.0289042166666666</v>
       </c>
     </row>
-    <row r="32" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32">
+    <row r="32" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="15">
         <v>31</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F32" s="9">
-        <v>16</v>
-      </c>
-      <c r="G32" s="9">
+      <c r="B32" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="15">
+        <v>1</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F32" s="15">
+        <v>64</v>
+      </c>
+      <c r="G32" s="15">
         <f>1/Table52[[#This Row],[N]]</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="H32" s="16">
-        <v>-1</v>
-      </c>
-      <c r="I32" s="16">
-        <v>-1</v>
-      </c>
-      <c r="J32" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K32" s="21"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="Q32" s="9">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H32" s="26">
+        <v>-1</v>
+      </c>
+      <c r="I32" s="15">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="J32" s="26">
+        <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>1.0880000000000001</v>
+      </c>
+      <c r="K32" s="26">
+        <v>-1</v>
+      </c>
+      <c r="L32" s="26">
+        <v>-1</v>
+      </c>
+      <c r="M32" s="15">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="N32" s="16">
+        <v>4500</v>
+      </c>
+      <c r="O32" s="15">
+        <v>152.18124399999999</v>
+      </c>
+      <c r="Q32" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>-2.5</v>
-      </c>
-      <c r="S32" s="9" t="e">
+        <v>147.05882352941177</v>
+      </c>
+      <c r="R32" s="15">
+        <v>1000</v>
+      </c>
+      <c r="S32" s="15">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>4.5</v>
+      </c>
+      <c r="T32" s="15">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>2.5363540666666666</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="15">
+        <v>32</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="15">
+        <v>1</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F33" s="15">
+        <v>64</v>
+      </c>
+      <c r="G33" s="15">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H33" s="17">
+        <v>-1</v>
+      </c>
+      <c r="I33" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="J33" s="26">
+        <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="K33" s="17">
+        <v>-1</v>
+      </c>
+      <c r="L33" s="17">
+        <v>-1</v>
+      </c>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16">
+        <v>4530</v>
+      </c>
+      <c r="O33" s="15">
+        <v>113.157005</v>
+      </c>
+      <c r="Q33" s="15">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>2500</v>
+      </c>
+      <c r="S33" s="15" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T32" s="9">
+      <c r="T33" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F33" s="9">
-        <v>32</v>
-      </c>
-      <c r="G33" s="9">
+        <v>1.8859500833333334</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="15">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="15">
+        <v>1</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F34" s="15">
+        <v>64</v>
+      </c>
+      <c r="G34" s="15">
         <f>1/Table52[[#This Row],[N]]</f>
-        <v>3.125E-2</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-1</v>
-      </c>
-      <c r="I33" s="15">
-        <v>-1</v>
-      </c>
-      <c r="J33" s="15">
-        <v>-1</v>
-      </c>
-      <c r="K33" s="22"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="Q33" s="9">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H34" s="17">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="15">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J34" s="26">
+        <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0.32</v>
+      </c>
+      <c r="K34" s="17">
+        <v>-1</v>
+      </c>
+      <c r="L34" s="17">
+        <v>-1</v>
+      </c>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16">
+        <v>8051</v>
+      </c>
+      <c r="O34" s="15">
+        <v>77.035552999999993</v>
+      </c>
+      <c r="Q34" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>-2.5</v>
-      </c>
-      <c r="S33" s="9" t="e">
+        <v>500</v>
+      </c>
+      <c r="S34" s="15" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T33" s="9">
+      <c r="T34" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F34" s="9">
+        <v>1.2839258833333331</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="15">
+        <v>34</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="15">
+        <v>1</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F35" s="15">
         <v>64</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G35" s="15">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H34" s="16">
-        <v>-1</v>
-      </c>
-      <c r="I34" s="16">
-        <v>-1</v>
-      </c>
-      <c r="J34" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K34" s="21"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="Q34" s="9">
+      <c r="H35" s="17">
+        <v>-1</v>
+      </c>
+      <c r="I35" s="15">
+        <v>0.01</v>
+      </c>
+      <c r="J35" s="26">
+        <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0.64</v>
+      </c>
+      <c r="K35" s="17">
+        <v>-1</v>
+      </c>
+      <c r="L35" s="17">
+        <v>-1</v>
+      </c>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16">
+        <v>4530</v>
+      </c>
+      <c r="O35" s="15">
+        <v>113.239769</v>
+      </c>
+      <c r="Q35" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>-2.5</v>
-      </c>
-      <c r="S34" s="9" t="e">
+        <v>250</v>
+      </c>
+      <c r="S35" s="15" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T34" s="9">
+      <c r="T35" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F35" s="9">
-        <v>128</v>
-      </c>
-      <c r="G35" s="9">
+        <v>1.8873294833333332</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="15">
+        <v>35</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="15">
+        <v>1</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F36" s="15">
+        <v>64</v>
+      </c>
+      <c r="G36" s="15">
         <f>1/Table52[[#This Row],[N]]</f>
-        <v>7.8125E-3</v>
-      </c>
-      <c r="H35" s="15">
-        <v>-1</v>
-      </c>
-      <c r="I35" s="15">
-        <v>-1</v>
-      </c>
-      <c r="J35" s="15">
-        <v>-1</v>
-      </c>
-      <c r="K35" s="22"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="Q35" s="9">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H36" s="17">
+        <v>-1</v>
+      </c>
+      <c r="I36" s="15">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J36" s="26">
+        <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="K36" s="17">
+        <v>-1</v>
+      </c>
+      <c r="L36" s="17">
+        <v>-1</v>
+      </c>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16">
+        <v>53406</v>
+      </c>
+      <c r="O36" s="15">
+        <v>74.7314911</v>
+      </c>
+      <c r="Q36" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>-2.5</v>
-      </c>
-      <c r="S35" s="9" t="e">
+        <v>5000</v>
+      </c>
+      <c r="S36" s="15" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T35" s="9">
+      <c r="T36" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="9">
-        <v>-1</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F36" s="9">
-        <v>256</v>
-      </c>
-      <c r="G36" s="9">
+        <v>1.2455248516666666</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="15">
+        <v>36</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="15">
+        <v>1</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F37" s="15">
+        <v>64</v>
+      </c>
+      <c r="G37" s="28">
         <f>1/Table52[[#This Row],[N]]</f>
-        <v>3.90625E-3</v>
-      </c>
-      <c r="H36" s="16">
-        <v>-1</v>
-      </c>
-      <c r="I36" s="16">
-        <v>-1</v>
-      </c>
-      <c r="J36" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K36" s="21"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="Q36" s="9">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H37" s="28">
+        <v>-1</v>
+      </c>
+      <c r="I37" s="28">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="J37" s="28">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28">
+        <v>-1</v>
+      </c>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28">
+        <v>38422</v>
+      </c>
+      <c r="O37" s="29">
+        <v>59.427192699999999</v>
+      </c>
+      <c r="P37" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q37" s="30">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>-2.5</v>
-      </c>
-      <c r="S36" s="9" t="e">
+        <v>3333.3333333333335</v>
+      </c>
+      <c r="R37" s="27">
+        <v>5000</v>
+      </c>
+      <c r="S37" s="31">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T36" s="9">
+        <v>7.6844000000000001</v>
+      </c>
+      <c r="T37" s="31">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="11">
+        <v>0.99045321166666667</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A38" s="15">
+        <v>37</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="15">
         <v>1</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="11">
-        <v>1000</v>
-      </c>
-      <c r="F37" s="11">
-        <v>256</v>
-      </c>
-      <c r="G37" s="11">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>3.90625E-3</v>
-      </c>
-      <c r="H37" s="11">
-        <f>Table52[[#This Row],[DX]]/1</f>
-        <v>3.90625E-3</v>
-      </c>
-      <c r="I37" s="11">
-        <v>2E-3</v>
-      </c>
-      <c r="J37" s="11">
-        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>0.51200000000000001</v>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11">
-        <v>-1</v>
-      </c>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11">
-        <v>42487</v>
-      </c>
-      <c r="O37" s="12">
-        <v>3972.08862</v>
-      </c>
-      <c r="P37" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q37" s="9">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>1250</v>
-      </c>
-      <c r="R37">
-        <v>5000</v>
-      </c>
-      <c r="S37" s="7">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>8.4974000000000007</v>
-      </c>
-      <c r="T37" s="7">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>66.201476999999997</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>13.1</v>
-      </c>
-      <c r="B38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="D38" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E38">
-        <v>1000</v>
-      </c>
-      <c r="F38">
+      <c r="E38" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F38" s="15">
         <v>64</v>
       </c>
       <c r="G38">
@@ -2962,32 +3071,31 @@
         <v>1.5625E-2</v>
       </c>
       <c r="H38">
-        <f>Table52[[#This Row],[DX]]/1</f>
-        <v>1.5625E-2</v>
+        <v>-1</v>
       </c>
       <c r="I38">
-        <v>1.4999999999999999E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J38">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="L38">
         <v>-1</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1">
-        <v>4576</v>
+        <v>3717</v>
       </c>
       <c r="O38" s="1">
-        <v>36.317504900000003</v>
+        <v>128.21608000000001</v>
       </c>
       <c r="P38" t="s">
         <v>18</v>
       </c>
       <c r="Q38">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>166.66666666666669</v>
+        <v>200</v>
       </c>
       <c r="S38" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
@@ -2995,14 +3103,345 @@
       </c>
       <c r="T38">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0.60529174833333343</v>
+        <v>2.1369346666666669</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A39" s="15">
+        <v>38</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="15">
+        <v>1</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F39" s="15">
+        <v>64</v>
+      </c>
+      <c r="G39" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H39" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I39">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="J39">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0.48</v>
+      </c>
+      <c r="L39" s="18"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1">
+        <v>5759</v>
+      </c>
+      <c r="O39">
+        <v>95.118499799999995</v>
+      </c>
+      <c r="Q39" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>333.33333333333337</v>
+      </c>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T39" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.5853083299999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A40" s="15">
+        <v>39</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="15">
+        <v>1</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F40" s="15">
+        <v>64</v>
+      </c>
+      <c r="G40" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H40" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I40">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J40">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0.96</v>
+      </c>
+      <c r="L40" s="18"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1">
+        <v>3102</v>
+      </c>
+      <c r="O40">
+        <v>140.86225899999999</v>
+      </c>
+      <c r="Q40" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>166.66666666666669</v>
+      </c>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T40" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>2.3477043166666665</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A41" s="15">
+        <v>40</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="15">
+        <v>1</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F41" s="15">
+        <v>64</v>
+      </c>
+      <c r="G41" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H41" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J41">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="18"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="Q41" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R41" s="32"/>
+      <c r="S41" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T41" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A42" s="15">
+        <v>41</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="15">
+        <v>1</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F42" s="15">
+        <v>64</v>
+      </c>
+      <c r="G42" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H42" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J42">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="18"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="Q42" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T42" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A43" s="15">
+        <v>42</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="15">
+        <v>1</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F43" s="15">
+        <v>64</v>
+      </c>
+      <c r="G43" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H43" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J43" s="32">
+        <v>0.7</v>
+      </c>
+      <c r="L43" s="18"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="Q43" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R43" s="32"/>
+      <c r="S43" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T43" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A44" s="15">
+        <v>43</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="15">
+        <v>1</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="15">
+        <v>64</v>
+      </c>
+      <c r="G44" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H44" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J44" s="32">
+        <v>0.6</v>
+      </c>
+      <c r="L44" s="18"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="Q44" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R44" s="32"/>
+      <c r="S44" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T44" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="G45" s="32" t="e">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H45" s="32" t="e">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J45" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="L45" s="18"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="Q45" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T45" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="H27 H28:H36 J27:J36" calculatedColumn="1"/>
+    <ignoredError sqref="H27 H28:H36 J27:J31" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annashen/Desktop/code/ME663-project/postprocess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{74F324A3-25D9-0640-A921-253E875B9788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{DD04982F-5DD2-B044-91B9-58AA10734BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1240" yWindow="500" windowWidth="29120" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="30">
   <si>
     <t>case</t>
   </si>
@@ -279,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -313,6 +313,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,8 +405,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T45" totalsRowShown="0">
-  <autoFilter ref="A1:T45" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T48" totalsRowShown="0">
+  <autoFilter ref="A1:T48" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{F042FD67-138A-3747-8F7D-92055EB26E1F}" name="case"/>
     <tableColumn id="19" xr3:uid="{6D3F4F6F-712A-EA45-8F90-560AA5EB3396}" name="solution_method"/>
@@ -799,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8141C424-3935-5946-8401-AC39630593AC}">
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="13.6640625" customWidth="1"/>
@@ -3162,58 +3165,58 @@
         <v>1.5853083299999999</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A40" s="15">
+    <row r="40" spans="1:20" s="3" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="33">
         <v>39</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="15">
+      <c r="B40" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="33">
         <v>1</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F40" s="15">
+      <c r="E40" s="33">
+        <v>1000</v>
+      </c>
+      <c r="F40" s="33">
         <v>64</v>
       </c>
-      <c r="G40" s="32">
+      <c r="G40" s="34">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H40" s="32">
+      <c r="H40" s="34">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="3">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="L40" s="18"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1">
+      <c r="L40" s="22"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4">
         <v>3102</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="3">
         <v>140.86225899999999</v>
       </c>
-      <c r="Q40" s="32">
+      <c r="Q40" s="34">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="R40" s="32"/>
-      <c r="S40" s="32" t="e">
+      <c r="R40" s="34"/>
+      <c r="S40" s="34" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T40" s="32">
+      <c r="T40" s="34">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>2.3477043166666665</v>
       </c>
@@ -3245,16 +3248,24 @@
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
+      <c r="I41">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>1.5625E-4</v>
+      </c>
       <c r="J41">
-        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L41" s="18"/>
       <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="Q41" s="32" t="e">
+      <c r="N41" s="1">
+        <v>136659</v>
+      </c>
+      <c r="O41">
+        <v>175.09970100000001</v>
+      </c>
+      <c r="Q41" s="32">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
+        <v>16000</v>
       </c>
       <c r="R41" s="32"/>
       <c r="S41" s="32" t="e">
@@ -3263,7 +3274,7 @@
       </c>
       <c r="T41" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>2.9183283500000003</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
@@ -3293,16 +3304,24 @@
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
+      <c r="I42">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>7.8125000000000004E-4</v>
+      </c>
       <c r="J42">
-        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L42" s="18"/>
       <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="Q42" s="32" t="e">
+      <c r="N42" s="1">
+        <v>37155</v>
+      </c>
+      <c r="O42">
+        <v>58.603294400000003</v>
+      </c>
+      <c r="Q42" s="32">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
+        <v>3200</v>
       </c>
       <c r="R42" s="32"/>
       <c r="S42" s="32" t="e">
@@ -3311,10 +3330,10 @@
       </c>
       <c r="T42" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+        <v>0.97672157333333343</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="15">
         <v>42</v>
       </c>
@@ -3333,35 +3352,43 @@
       <c r="F43" s="15">
         <v>64</v>
       </c>
-      <c r="G43" s="32">
+      <c r="G43" s="35">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H43" s="32">
+      <c r="H43" s="35">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J43" s="32">
-        <v>0.7</v>
-      </c>
-      <c r="L43" s="18"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="Q43" s="32" t="e">
+      <c r="I43" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>3.1250000000000002E-3</v>
+      </c>
+      <c r="J43" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="M43" s="16"/>
+      <c r="N43" s="16">
+        <v>11825</v>
+      </c>
+      <c r="O43" s="15">
+        <v>60.159965499999998</v>
+      </c>
+      <c r="Q43" s="35">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R43" s="32"/>
-      <c r="S43" s="32" t="e">
+        <v>800</v>
+      </c>
+      <c r="R43" s="35"/>
+      <c r="S43" s="35" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T43" s="32">
+      <c r="T43" s="35">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
+        <v>1.0026660916666665</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="15">
         <v>43</v>
       </c>
@@ -3380,59 +3407,255 @@
       <c r="F44" s="15">
         <v>64</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="35">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="35">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J44" s="32">
-        <v>0.6</v>
-      </c>
-      <c r="L44" s="18"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="Q44" s="32" t="e">
+      <c r="I44" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="J44" s="35">
+        <v>0.4</v>
+      </c>
+      <c r="M44" s="16"/>
+      <c r="N44" s="16">
+        <v>6706</v>
+      </c>
+      <c r="O44" s="15">
+        <v>87.384323100000003</v>
+      </c>
+      <c r="Q44" s="35">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R44" s="32"/>
-      <c r="S44" s="32" t="e">
+        <v>400</v>
+      </c>
+      <c r="R44" s="35"/>
+      <c r="S44" s="35" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T44" s="32">
+      <c r="T44" s="35">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="G45" s="32" t="e">
+        <v>1.4564053850000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="15">
+        <v>44</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="15">
+        <v>1</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="15">
+        <v>64</v>
+      </c>
+      <c r="G45" s="35">
         <f>1/Table52[[#This Row],[N]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H45" s="32" t="e">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H45" s="35">
         <f>Table52[[#This Row],[DX]]/1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J45" s="32">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I45" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="J45" s="35">
         <v>0.5</v>
       </c>
-      <c r="L45" s="18"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="Q45" s="32" t="e">
+      <c r="M45" s="16"/>
+      <c r="N45" s="16">
+        <v>5560</v>
+      </c>
+      <c r="O45" s="15">
+        <v>97.289329499999994</v>
+      </c>
+      <c r="Q45" s="35">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R45" s="32"/>
-      <c r="S45" s="32" t="e">
+        <v>320</v>
+      </c>
+      <c r="R45" s="35"/>
+      <c r="S45" s="35" t="e">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T45" s="32">
+      <c r="T45" s="35">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.6214888249999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="15">
+        <v>45</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="15">
+        <v>1</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F46" s="15">
+        <v>64</v>
+      </c>
+      <c r="G46" s="35">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H46" s="35">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I46" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>9.3749999999999997E-3</v>
+      </c>
+      <c r="J46" s="35">
+        <v>0.6</v>
+      </c>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16">
+        <v>4791</v>
+      </c>
+      <c r="O46" s="15">
+        <v>107.397453</v>
+      </c>
+      <c r="Q46" s="35">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>266.66666666666669</v>
+      </c>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T46" s="35">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.78995755</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A47" s="15">
+        <v>46</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="15">
+        <v>1</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F47" s="15">
+        <v>64</v>
+      </c>
+      <c r="G47" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H47" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I47">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="J47" s="32">
+        <v>0.8</v>
+      </c>
+      <c r="L47" s="18"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1">
+        <v>3717</v>
+      </c>
+      <c r="O47">
+        <v>127.491776</v>
+      </c>
+      <c r="Q47" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>200</v>
+      </c>
+      <c r="R47" s="32"/>
+      <c r="S47" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T47" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>2.1248629333333335</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A48" s="15">
+        <v>47</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="15">
+        <v>1</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="15">
+        <v>64</v>
+      </c>
+      <c r="G48" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H48" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I48">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J48" s="32">
+        <v>1</v>
+      </c>
+      <c r="L48" s="18"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="Q48" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>160</v>
+      </c>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T48" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>

--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annashen/Desktop/code/ME663-project/postprocess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{DD04982F-5DD2-B044-91B9-58AA10734BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{93BBAE32-C701-A64E-A1C2-42F58C683E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1240" yWindow="500" windowWidth="29120" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="30">
   <si>
     <t>case</t>
   </si>
@@ -164,7 +164,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -192,6 +192,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -316,6 +322,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,8 +416,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T48" totalsRowShown="0">
-  <autoFilter ref="A1:T48" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T64" totalsRowShown="0">
+  <autoFilter ref="A1:T64" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{F042FD67-138A-3747-8F7D-92055EB26E1F}" name="case"/>
     <tableColumn id="19" xr3:uid="{6D3F4F6F-712A-EA45-8F90-560AA5EB3396}" name="solution_method"/>
@@ -414,30 +425,30 @@
     <tableColumn id="2" xr3:uid="{00DE4CFB-CE63-774C-9203-441FF3361859}" name="conv_scheme"/>
     <tableColumn id="17" xr3:uid="{47055424-3AAA-D24A-BA60-63AE4C6D6F5B}" name="RE"/>
     <tableColumn id="4" xr3:uid="{495CF2F5-C4F9-8F4D-AA38-DF0B3BD005AB}" name="N"/>
-    <tableColumn id="5" xr3:uid="{766BC887-C47B-5B4D-856A-DB7D9716FC41}" name="DX" dataDxfId="19">
+    <tableColumn id="5" xr3:uid="{766BC887-C47B-5B4D-856A-DB7D9716FC41}" name="DX" dataDxfId="9">
       <calculatedColumnFormula>1/Table52[[#This Row],[N]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{41134D54-A4BA-874E-976C-009F5555A5F2}" name="DT_MAX" dataDxfId="18">
+    <tableColumn id="6" xr3:uid="{41134D54-A4BA-874E-976C-009F5555A5F2}" name="DT_MAX" dataDxfId="8">
       <calculatedColumnFormula>Table52[[#This Row],[DX]]/1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{273D8EE8-DE95-664F-9350-38E8AA2F9049}" name="DT"/>
-    <tableColumn id="22" xr3:uid="{F37937B1-F618-9544-858E-9C385880A578}" name="CFL" dataDxfId="17">
+    <tableColumn id="22" xr3:uid="{F37937B1-F618-9544-858E-9C385880A578}" name="CFL" dataDxfId="7">
       <calculatedColumnFormula>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{CC46E7B8-FF0D-C94B-AE73-961311865B19}" name="URFP"/>
-    <tableColumn id="16" xr3:uid="{57BAD542-64CC-254E-88F0-83BA2685E4ED}" name="URFU" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{CF78813F-1FCF-E643-8377-72AF6325BEEE}" name="diverging_factor" dataDxfId="15"/>
-    <tableColumn id="25" xr3:uid="{B19A7E44-6A26-8B41-BA69-77F75344DEA3}" name="IT" dataDxfId="14"/>
+    <tableColumn id="16" xr3:uid="{57BAD542-64CC-254E-88F0-83BA2685E4ED}" name="URFU" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{CF78813F-1FCF-E643-8377-72AF6325BEEE}" name="diverging_factor" dataDxfId="5"/>
+    <tableColumn id="25" xr3:uid="{B19A7E44-6A26-8B41-BA69-77F75344DEA3}" name="IT" dataDxfId="4"/>
     <tableColumn id="11" xr3:uid="{F124CBF0-B3EB-C444-B55D-C50EED146627}" name="clock_time"/>
     <tableColumn id="12" xr3:uid="{5F48E9FB-C4BC-024C-B991-90BE72C979E1}" name="colour"/>
-    <tableColumn id="13" xr3:uid="{DEF21282-AC7A-5545-B41D-E8A24B1E8319}" name="compare_diff" dataDxfId="13">
+    <tableColumn id="13" xr3:uid="{DEF21282-AC7A-5545-B41D-E8A24B1E8319}" name="compare_diff" dataDxfId="3">
       <calculatedColumnFormula>2.5/Table52[[#This Row],[DT]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{04DFDB2B-B2EB-2143-A2BD-C078D341F02C}" name="plot" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{2C94A75A-643C-AB4F-B973-F132BD67C52D}" name="Coldumn3" dataDxfId="11">
+    <tableColumn id="14" xr3:uid="{04DFDB2B-B2EB-2143-A2BD-C078D341F02C}" name="plot" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{2C94A75A-643C-AB4F-B973-F132BD67C52D}" name="Coldumn3" dataDxfId="1">
       <calculatedColumnFormula>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4E3C3F99-0854-E448-B822-ED1CAF3861A9}" name="Time (min)" dataDxfId="10">
+    <tableColumn id="3" xr3:uid="{4E3C3F99-0854-E448-B822-ED1CAF3861A9}" name="Time (min)" dataDxfId="0">
       <calculatedColumnFormula>Table52[[#This Row],[clock_time]]/60</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -455,29 +466,29 @@
     <tableColumn id="2" xr3:uid="{5CAB8637-6767-EF4F-AB30-8872A405584F}" name="conv_scheme"/>
     <tableColumn id="17" xr3:uid="{F7E8B8A5-B5C1-654E-BF6E-56FB97322E67}" name="RE"/>
     <tableColumn id="4" xr3:uid="{D0F235B2-EEA8-D14B-A9CC-E4901839BFD8}" name="N"/>
-    <tableColumn id="5" xr3:uid="{83BA6CEC-05CE-F148-8D33-78AB6664A553}" name="DX" dataDxfId="9">
+    <tableColumn id="5" xr3:uid="{83BA6CEC-05CE-F148-8D33-78AB6664A553}" name="DX" dataDxfId="19">
       <calculatedColumnFormula>1/Table523[[#This Row],[N]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{67B863EC-1E80-594A-8E8C-A8AB6A765A5B}" name="DT_MAX" dataDxfId="8">
+    <tableColumn id="6" xr3:uid="{67B863EC-1E80-594A-8E8C-A8AB6A765A5B}" name="DT_MAX" dataDxfId="18">
       <calculatedColumnFormula>Table523[[#This Row],[DX]]/1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{B6FA003B-6936-8041-9393-B2FBF938999E}" name="DT"/>
-    <tableColumn id="22" xr3:uid="{6AF97E91-5A09-0D4F-8AFB-1FA45DB53426}" name="CFL" dataDxfId="7">
+    <tableColumn id="22" xr3:uid="{6AF97E91-5A09-0D4F-8AFB-1FA45DB53426}" name="CFL" dataDxfId="17">
       <calculatedColumnFormula>1*Table523[[#This Row],[DT]]/Table523[[#This Row],[DX]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{18D7BD5A-213F-BD40-97BA-0D536A04F891}" name="URF" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{798FE19B-9189-494F-A3BB-310F03005E42}" name="diverging_factor" dataDxfId="5"/>
-    <tableColumn id="25" xr3:uid="{FDF5445A-F7EE-1F4D-9905-BD45A45BD22B}" name="IT" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{18D7BD5A-213F-BD40-97BA-0D536A04F891}" name="URF" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{798FE19B-9189-494F-A3BB-310F03005E42}" name="diverging_factor" dataDxfId="15"/>
+    <tableColumn id="25" xr3:uid="{FDF5445A-F7EE-1F4D-9905-BD45A45BD22B}" name="IT" dataDxfId="14"/>
     <tableColumn id="11" xr3:uid="{BEAE8ECD-6C05-B047-A51B-18671676A586}" name="clock_time"/>
     <tableColumn id="12" xr3:uid="{750E52A0-203C-CD4A-98C6-C1F65E42F542}" name="colour"/>
-    <tableColumn id="13" xr3:uid="{FDAC66DF-EEEF-4B40-9B2B-8468B1ABCB4F}" name="compare_diff" dataDxfId="3">
+    <tableColumn id="13" xr3:uid="{FDAC66DF-EEEF-4B40-9B2B-8468B1ABCB4F}" name="compare_diff" dataDxfId="13">
       <calculatedColumnFormula>Table523[[#This Row],[IT]]/(Table523[[#This Row],[DT]]^(0.001))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{25F9EF5E-5623-9348-AFD3-BE21DEB4A0B1}" name="plot" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{6C6DB161-08C1-8C41-8D04-DBB62D987A88}" name="Coldumn3" dataDxfId="1">
+    <tableColumn id="14" xr3:uid="{25F9EF5E-5623-9348-AFD3-BE21DEB4A0B1}" name="plot" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{6C6DB161-08C1-8C41-8D04-DBB62D987A88}" name="Coldumn3" dataDxfId="11">
       <calculatedColumnFormula>Table523[[#This Row],[IT]]/Table523[[#This Row],[plot]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8D89A138-3ECA-4F4F-8AE2-5ED05E63F0B1}" name="Coldumn4" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{8D89A138-3ECA-4F4F-8AE2-5ED05E63F0B1}" name="Coldumn4" dataDxfId="10">
       <calculatedColumnFormula>Table523[[#This Row],[clock_time]]/60</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -802,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8141C424-3935-5946-8401-AC39630593AC}">
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:T64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="13.6640625" customWidth="1"/>
@@ -3016,10 +3027,7 @@
       <c r="I37" s="28">
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="J37" s="28">
-        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>4.8000000000000001E-2</v>
-      </c>
+      <c r="J37" s="28"/>
       <c r="K37" s="28"/>
       <c r="L37" s="28">
         <v>-1</v>
@@ -3221,7 +3229,7 @@
         <v>2.3477043166666665</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="15">
         <v>40</v>
       </c>
@@ -3240,44 +3248,43 @@
       <c r="F41" s="15">
         <v>64</v>
       </c>
-      <c r="G41" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H41" s="32">
+      <c r="G41" s="35">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H41" s="35">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="15">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.5625E-4</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="15">
         <v>0.01</v>
       </c>
-      <c r="L41" s="18"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1">
+      <c r="M41" s="16"/>
+      <c r="N41" s="16">
         <v>136659</v>
       </c>
-      <c r="O41">
+      <c r="O41" s="15">
         <v>175.09970100000001</v>
       </c>
-      <c r="Q41" s="32">
+      <c r="Q41" s="35">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>16000</v>
       </c>
-      <c r="R41" s="32"/>
-      <c r="S41" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T41" s="32">
+      <c r="R41" s="35"/>
+      <c r="S41" s="35" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T41" s="35">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>2.9183283500000003</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="15">
         <v>41</v>
       </c>
@@ -3296,39 +3303,38 @@
       <c r="F42" s="15">
         <v>64</v>
       </c>
-      <c r="G42" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H42" s="32">
+      <c r="G42" s="35">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H42" s="35">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="15">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>7.8125000000000004E-4</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="15">
         <v>0.05</v>
       </c>
-      <c r="L42" s="18"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1">
+      <c r="M42" s="16"/>
+      <c r="N42" s="16">
         <v>37155</v>
       </c>
-      <c r="O42">
+      <c r="O42" s="15">
         <v>58.603294400000003</v>
       </c>
-      <c r="Q42" s="32">
+      <c r="Q42" s="35">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>3200</v>
       </c>
-      <c r="R42" s="32"/>
-      <c r="S42" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T42" s="32">
+      <c r="R42" s="35"/>
+      <c r="S42" s="35" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T42" s="35">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.97672157333333343</v>
       </c>
@@ -3553,7 +3559,7 @@
         <v>1.78995755</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="15">
         <v>46</v>
       </c>
@@ -3572,90 +3578,949 @@
       <c r="F47" s="15">
         <v>64</v>
       </c>
-      <c r="G47" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H47" s="32">
+      <c r="G47" s="35">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H47" s="35">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="15">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="J47" s="32">
+      <c r="J47" s="35">
         <v>0.8</v>
       </c>
-      <c r="L47" s="18"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1">
+      <c r="M47" s="16"/>
+      <c r="N47" s="16">
         <v>3717</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="15">
         <v>127.491776</v>
       </c>
-      <c r="Q47" s="32">
+      <c r="Q47" s="35">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>200</v>
       </c>
-      <c r="R47" s="32"/>
-      <c r="S47" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T47" s="32">
+      <c r="R47" s="35"/>
+      <c r="S47" s="35" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T47" s="35">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>2.1248629333333335</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A48" s="15">
+    <row r="48" spans="1:20" s="33" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="33">
         <v>47</v>
       </c>
-      <c r="B48" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="15">
+      <c r="B48" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="33">
         <v>1</v>
       </c>
-      <c r="D48" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F48" s="15">
+      <c r="D48" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="33">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="33">
         <v>64</v>
       </c>
-      <c r="G48" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H48" s="32">
+      <c r="G48" s="36">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H48" s="36">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="33">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J48" s="32">
+      <c r="J48" s="36">
         <v>1</v>
       </c>
-      <c r="L48" s="18"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="Q48" s="32">
+      <c r="M48" s="37"/>
+      <c r="N48" s="37">
+        <v>2987</v>
+      </c>
+      <c r="O48" s="33">
+        <v>142.69487000000001</v>
+      </c>
+      <c r="Q48" s="36">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>160</v>
       </c>
-      <c r="R48" s="32"/>
-      <c r="S48" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T48" s="32">
+      <c r="R48" s="36"/>
+      <c r="S48" s="36" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T48" s="36">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>2.3782478333333334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="38">
+        <v>48</v>
+      </c>
+      <c r="B49" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="38">
+        <v>1</v>
+      </c>
+      <c r="D49" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F49" s="38">
+        <v>16</v>
+      </c>
+      <c r="G49" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H49" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I49" s="38">
+        <v>0.15</v>
+      </c>
+      <c r="J49" s="39">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>2.4</v>
+      </c>
+      <c r="M49" s="40"/>
+      <c r="N49" s="40">
+        <v>259</v>
+      </c>
+      <c r="O49" s="38">
+        <v>0.729385018</v>
+      </c>
+      <c r="Q49" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="R49" s="39"/>
+      <c r="S49" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T49" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.2156416966666667E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="38">
+        <v>49</v>
+      </c>
+      <c r="B50" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="38">
+        <v>1</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F50" s="38">
+        <v>16</v>
+      </c>
+      <c r="G50" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H50" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I50" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>0.15625</v>
+      </c>
+      <c r="J50" s="39">
+        <v>2.5</v>
+      </c>
+      <c r="M50" s="40"/>
+      <c r="N50" s="40">
+        <v>241</v>
+      </c>
+      <c r="O50" s="38">
+        <v>0.74937796599999995</v>
+      </c>
+      <c r="Q50" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>16</v>
+      </c>
+      <c r="R50" s="39"/>
+      <c r="S50" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T50" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.2489632766666666E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="38">
+        <v>50</v>
+      </c>
+      <c r="B51" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="38">
+        <v>1</v>
+      </c>
+      <c r="D51" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F51" s="38">
+        <v>16</v>
+      </c>
+      <c r="G51" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H51" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I51" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>0.140625</v>
+      </c>
+      <c r="J51" s="39">
+        <v>2.25</v>
+      </c>
+      <c r="M51" s="40"/>
+      <c r="N51" s="40">
+        <v>274</v>
+      </c>
+      <c r="O51" s="38">
+        <v>0.73873001299999996</v>
+      </c>
+      <c r="Q51" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>17.777777777777779</v>
+      </c>
+      <c r="R51" s="39"/>
+      <c r="S51" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T51" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.2312166883333333E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="38">
+        <v>51</v>
+      </c>
+      <c r="B52" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="38">
+        <v>1</v>
+      </c>
+      <c r="D52" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F52" s="38">
+        <v>16</v>
+      </c>
+      <c r="G52" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H52" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I52" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>0.125</v>
+      </c>
+      <c r="J52" s="39">
+        <v>2</v>
+      </c>
+      <c r="M52" s="40"/>
+      <c r="N52" s="40">
+        <v>304</v>
+      </c>
+      <c r="O52" s="38">
+        <v>0.72258299599999998</v>
+      </c>
+      <c r="Q52" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>20</v>
+      </c>
+      <c r="R52" s="39"/>
+      <c r="S52" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T52" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.2043049933333333E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="38">
+        <v>52</v>
+      </c>
+      <c r="B53" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="38">
+        <v>1</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F53" s="38">
+        <v>16</v>
+      </c>
+      <c r="G53" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H53" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I53" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>0.109375</v>
+      </c>
+      <c r="J53" s="39">
+        <v>1.75</v>
+      </c>
+      <c r="M53" s="40"/>
+      <c r="N53" s="40">
+        <v>341</v>
+      </c>
+      <c r="O53" s="38">
+        <v>0.73771297899999999</v>
+      </c>
+      <c r="Q53" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>22.857142857142858</v>
+      </c>
+      <c r="R53" s="39"/>
+      <c r="S53" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T53" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.2295216316666666E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="38">
+        <v>53</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="38">
+        <v>1</v>
+      </c>
+      <c r="D54" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F54" s="38">
+        <v>16</v>
+      </c>
+      <c r="G54" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H54" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I54" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>9.375E-2</v>
+      </c>
+      <c r="J54" s="39">
+        <v>1.5</v>
+      </c>
+      <c r="M54" s="40"/>
+      <c r="N54" s="40">
+        <v>390</v>
+      </c>
+      <c r="O54" s="38">
+        <v>0.72225296500000002</v>
+      </c>
+      <c r="Q54" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>26.666666666666668</v>
+      </c>
+      <c r="R54" s="39"/>
+      <c r="S54" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T54" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.2037549416666666E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="38">
+        <v>54</v>
+      </c>
+      <c r="B55" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="38">
+        <v>2</v>
+      </c>
+      <c r="D55" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F55" s="38">
+        <v>16</v>
+      </c>
+      <c r="G55" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H55" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I55" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>7.8125E-2</v>
+      </c>
+      <c r="J55" s="39">
+        <v>1.25</v>
+      </c>
+      <c r="M55" s="40"/>
+      <c r="N55" s="40">
+        <v>457</v>
+      </c>
+      <c r="O55" s="38">
+        <v>0.65907299500000005</v>
+      </c>
+      <c r="Q55" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>32</v>
+      </c>
+      <c r="R55" s="39"/>
+      <c r="S55" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T55" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.0984549916666668E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="38">
+        <v>55</v>
+      </c>
+      <c r="B56" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="38">
+        <v>3</v>
+      </c>
+      <c r="D56" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F56" s="38">
+        <v>16</v>
+      </c>
+      <c r="G56" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H56" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I56" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="J56" s="39">
+        <v>1</v>
+      </c>
+      <c r="M56" s="40"/>
+      <c r="N56" s="40">
+        <v>554</v>
+      </c>
+      <c r="O56" s="38">
+        <v>0.62351202999999999</v>
+      </c>
+      <c r="Q56" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>40</v>
+      </c>
+      <c r="R56" s="39"/>
+      <c r="S56" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T56" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.0391867166666667E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="38">
+        <v>56</v>
+      </c>
+      <c r="B57" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="38">
+        <v>4</v>
+      </c>
+      <c r="D57" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F57" s="38">
+        <v>16</v>
+      </c>
+      <c r="G57" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H57" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I57" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>4.6875E-2</v>
+      </c>
+      <c r="J57" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="M57" s="40"/>
+      <c r="N57" s="38">
+        <v>707</v>
+      </c>
+      <c r="O57" s="38">
+        <v>0.562693</v>
+      </c>
+      <c r="Q57" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>53.333333333333336</v>
+      </c>
+      <c r="R57" s="39"/>
+      <c r="S57" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T57" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>9.3782166666666663E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="38">
+        <v>57</v>
+      </c>
+      <c r="B58" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="38">
+        <v>5</v>
+      </c>
+      <c r="D58" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F58" s="38">
+        <v>16</v>
+      </c>
+      <c r="G58" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H58" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I58" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="J58" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="M58" s="40"/>
+      <c r="N58" s="40">
+        <v>996</v>
+      </c>
+      <c r="O58" s="38">
+        <v>0.46355798799999998</v>
+      </c>
+      <c r="Q58" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>80</v>
+      </c>
+      <c r="R58" s="39"/>
+      <c r="S58" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T58" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>7.7259664666666662E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="38">
+        <v>58</v>
+      </c>
+      <c r="B59" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="38">
+        <v>5</v>
+      </c>
+      <c r="D59" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="38">
+        <v>16</v>
+      </c>
+      <c r="G59" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H59" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I59" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J59" s="39">
+        <v>0.25</v>
+      </c>
+      <c r="M59" s="40"/>
+      <c r="N59" s="40"/>
+      <c r="Q59" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>160</v>
+      </c>
+      <c r="R59" s="39"/>
+      <c r="S59" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T59" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F60" s="18">
+        <v>64</v>
+      </c>
+      <c r="G60" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H60" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J60" s="32">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="L60" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="Q60" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R60" s="32"/>
+      <c r="S60" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T60" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F61" s="18">
+        <v>64</v>
+      </c>
+      <c r="G61" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H61" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J61" s="32">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="L61" s="18">
+        <v>0.6</v>
+      </c>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="Q61" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R61" s="32"/>
+      <c r="S61" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T61" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D62" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="18">
+        <v>1000</v>
+      </c>
+      <c r="G62" s="32" t="e">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H62" s="32" t="e">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J62" s="32" t="e">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K62" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="L62" s="18">
+        <v>0.7</v>
+      </c>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="Q62" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R62" s="32"/>
+      <c r="S62" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T62" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D63" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="18">
+        <v>1000</v>
+      </c>
+      <c r="G63" s="32" t="e">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H63" s="32" t="e">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J63" s="32" t="e">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K63" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="L63" s="18">
+        <v>0.8</v>
+      </c>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="Q63" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R63" s="32"/>
+      <c r="S63" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T63" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="18">
+        <v>1000</v>
+      </c>
+      <c r="G64" s="32" t="e">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H64" s="32" t="e">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J64" s="32" t="e">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K64" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="L64" s="18">
+        <v>0.78</v>
+      </c>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="Q64" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R64" s="32"/>
+      <c r="S64" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T64" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>

--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annashen/Desktop/code/ME663-project/postprocess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{93BBAE32-C701-A64E-A1C2-42F58C683E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{6B261AFC-3A1A-2F4A-8A9E-6EF113FD139E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1240" yWindow="500" windowWidth="29120" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="30">
   <si>
     <t>case</t>
   </si>
@@ -416,8 +416,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T64" totalsRowShown="0">
-  <autoFilter ref="A1:T64" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T72" totalsRowShown="0">
+  <autoFilter ref="A1:T72" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{F042FD67-138A-3747-8F7D-92055EB26E1F}" name="case"/>
     <tableColumn id="19" xr3:uid="{6D3F4F6F-712A-EA45-8F90-560AA5EB3396}" name="solution_method"/>
@@ -813,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8141C424-3935-5946-8401-AC39630593AC}">
-  <dimension ref="A1:T64"/>
+  <dimension ref="A1:T72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="13.6640625" customWidth="1"/>
@@ -4254,7 +4254,12 @@
         <v>0.25</v>
       </c>
       <c r="M59" s="40"/>
-      <c r="N59" s="40"/>
+      <c r="N59" s="40">
+        <v>1767</v>
+      </c>
+      <c r="O59" s="38">
+        <v>0.35058298700000001</v>
+      </c>
       <c r="Q59" s="39">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>160</v>
@@ -4266,7 +4271,7 @@
       </c>
       <c r="T59" s="39">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>5.8430497833333334E-3</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
@@ -4307,7 +4312,12 @@
         <v>0.5</v>
       </c>
       <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
+      <c r="N60" s="1">
+        <v>1317</v>
+      </c>
+      <c r="O60">
+        <v>3.6674129999999998</v>
+      </c>
       <c r="Q60" s="32" t="e">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>#DIV/0!</v>
@@ -4319,7 +4329,7 @@
       </c>
       <c r="T60" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>6.1123549999999999E-2</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
@@ -4360,7 +4370,12 @@
         <v>0.6</v>
       </c>
       <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
+      <c r="N61" s="1">
+        <v>1087</v>
+      </c>
+      <c r="O61">
+        <v>3.2093491599999999</v>
+      </c>
       <c r="Q61" s="32" t="e">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>#DIV/0!</v>
@@ -4372,7 +4387,7 @@
       </c>
       <c r="T61" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>5.3489152666666664E-2</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.2">
@@ -4391,17 +4406,20 @@
       <c r="E62" s="18">
         <v>1000</v>
       </c>
-      <c r="G62" s="32" t="e">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H62" s="32" t="e">
+      <c r="F62" s="18">
+        <v>64</v>
+      </c>
+      <c r="G62" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H62" s="32">
         <f>Table52[[#This Row],[DX]]/1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J62" s="32" t="e">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J62" s="32">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="K62" s="21">
         <v>0.3</v>
@@ -4410,7 +4428,12 @@
         <v>0.7</v>
       </c>
       <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
+      <c r="N62" s="1">
+        <v>955</v>
+      </c>
+      <c r="O62">
+        <v>2.6229457900000002</v>
+      </c>
       <c r="Q62" s="32" t="e">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>#DIV/0!</v>
@@ -4422,7 +4445,7 @@
       </c>
       <c r="T62" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>4.3715763166666671E-2</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
@@ -4441,17 +4464,20 @@
       <c r="E63" s="18">
         <v>1000</v>
       </c>
-      <c r="G63" s="32" t="e">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H63" s="32" t="e">
+      <c r="F63" s="18">
+        <v>64</v>
+      </c>
+      <c r="G63" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H63" s="32">
         <f>Table52[[#This Row],[DX]]/1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J63" s="32" t="e">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J63" s="32">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="K63" s="21">
         <v>0.3</v>
@@ -4460,7 +4486,12 @@
         <v>0.8</v>
       </c>
       <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
+      <c r="N63" s="1">
+        <v>2311</v>
+      </c>
+      <c r="O63">
+        <v>6.3866229099999998</v>
+      </c>
       <c r="Q63" s="32" t="e">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>#DIV/0!</v>
@@ -4472,7 +4503,7 @@
       </c>
       <c r="T63" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>0.10644371516666666</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
@@ -4491,26 +4522,34 @@
       <c r="E64" s="18">
         <v>1000</v>
       </c>
-      <c r="G64" s="32" t="e">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H64" s="32" t="e">
+      <c r="F64" s="18">
+        <v>64</v>
+      </c>
+      <c r="G64" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H64" s="32">
         <f>Table52[[#This Row],[DX]]/1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J64" s="32" t="e">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J64" s="32">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="K64" s="21">
         <v>0.3</v>
       </c>
       <c r="L64" s="18">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
+      <c r="N64" s="1">
+        <v>934</v>
+      </c>
+      <c r="O64">
+        <v>2.6197769599999998</v>
+      </c>
       <c r="Q64" s="32" t="e">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>#DIV/0!</v>
@@ -4521,6 +4560,435 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T64" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>4.3662949333333333E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F65" s="18">
+        <v>64</v>
+      </c>
+      <c r="G65" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H65" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J65" s="32">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0</v>
+      </c>
+      <c r="K65" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="L65" s="18">
+        <v>0.81</v>
+      </c>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1">
+        <v>3947</v>
+      </c>
+      <c r="O65">
+        <v>10.8955822</v>
+      </c>
+      <c r="Q65" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R65" s="32"/>
+      <c r="S65" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T65" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.18159303666666665</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="18">
+        <v>1000</v>
+      </c>
+      <c r="F66" s="18">
+        <v>64</v>
+      </c>
+      <c r="G66" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H66" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J66" s="32">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0</v>
+      </c>
+      <c r="K66" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="L66" s="18">
+        <v>0.4</v>
+      </c>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1">
+        <v>1584</v>
+      </c>
+      <c r="O66">
+        <v>4.5329389600000001</v>
+      </c>
+      <c r="Q66" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R66" s="32"/>
+      <c r="S66" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T66" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>7.5548982666666667E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" s="3" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>66</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67" s="22">
+        <v>-1</v>
+      </c>
+      <c r="D67" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="22">
+        <v>1000</v>
+      </c>
+      <c r="F67" s="22">
+        <v>64</v>
+      </c>
+      <c r="G67" s="34">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H67" s="34">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J67" s="34">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0</v>
+      </c>
+      <c r="K67" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="L67" s="22">
+        <v>0.78</v>
+      </c>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4">
+        <v>1279</v>
+      </c>
+      <c r="O67" s="3">
+        <v>3.5589289700000002</v>
+      </c>
+      <c r="Q67" s="34" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R67" s="34"/>
+      <c r="S67" s="34" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T67" s="34">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>5.9315482833333336E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68">
+        <v>1000</v>
+      </c>
+      <c r="F68">
+        <v>32</v>
+      </c>
+      <c r="G68" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H68" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="I68">
+        <v>0.05</v>
+      </c>
+      <c r="J68" s="32">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>1.6</v>
+      </c>
+      <c r="L68" s="18"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="Q68" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>50</v>
+      </c>
+      <c r="R68" s="32"/>
+      <c r="S68" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T68" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69">
+        <v>1000</v>
+      </c>
+      <c r="F69">
+        <v>32</v>
+      </c>
+      <c r="G69" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H69" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="I69">
+        <v>0.05</v>
+      </c>
+      <c r="J69" s="32">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>1.6</v>
+      </c>
+      <c r="L69" s="18"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="Q69" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>50</v>
+      </c>
+      <c r="R69" s="32"/>
+      <c r="S69" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T69" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70">
+        <v>1000</v>
+      </c>
+      <c r="F70">
+        <v>32</v>
+      </c>
+      <c r="G70" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H70" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="I70">
+        <v>0.05</v>
+      </c>
+      <c r="J70" s="32">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>1.6</v>
+      </c>
+      <c r="L70" s="18"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="Q70" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>50</v>
+      </c>
+      <c r="R70" s="32"/>
+      <c r="S70" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T70" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71">
+        <v>1000</v>
+      </c>
+      <c r="F71">
+        <v>32</v>
+      </c>
+      <c r="G71" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H71" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="I71">
+        <v>0.05</v>
+      </c>
+      <c r="J71" s="32">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>1.6</v>
+      </c>
+      <c r="L71" s="18"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="Q71" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>50</v>
+      </c>
+      <c r="R71" s="32"/>
+      <c r="S71" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T71" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72">
+        <v>1000</v>
+      </c>
+      <c r="F72">
+        <v>32</v>
+      </c>
+      <c r="G72" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H72" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="I72">
+        <v>0.05</v>
+      </c>
+      <c r="J72" s="32">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>1.6</v>
+      </c>
+      <c r="L72" s="18"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="Q72" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>50</v>
+      </c>
+      <c r="R72" s="32"/>
+      <c r="S72" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T72" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>

--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annashen/Desktop/code/ME663-project/postprocess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{6B261AFC-3A1A-2F4A-8A9E-6EF113FD139E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{1730DFB9-55E5-BC48-A846-4CF2FC93D49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="500" windowWidth="29120" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="27040" windowHeight="16880" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="30">
   <si>
     <t>case</t>
   </si>
@@ -202,7 +202,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -281,11 +281,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -327,6 +336,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,8 +429,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T72" totalsRowShown="0">
-  <autoFilter ref="A1:T72" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T83" totalsRowShown="0">
+  <autoFilter ref="A1:T83" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{F042FD67-138A-3747-8F7D-92055EB26E1F}" name="case"/>
     <tableColumn id="19" xr3:uid="{6D3F4F6F-712A-EA45-8F90-560AA5EB3396}" name="solution_method"/>
@@ -813,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8141C424-3935-5946-8401-AC39630593AC}">
-  <dimension ref="A1:T72"/>
+  <dimension ref="A1:T84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="13.6640625" customWidth="1"/>
@@ -4774,7 +4787,12 @@
       </c>
       <c r="L68" s="18"/>
       <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
+      <c r="N68" s="1">
+        <v>857</v>
+      </c>
+      <c r="O68">
+        <v>3.7602040799999998</v>
+      </c>
       <c r="Q68" s="32">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>50</v>
@@ -4786,7 +4804,7 @@
       </c>
       <c r="T68" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>6.2670067999999995E-2</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
@@ -4817,18 +4835,23 @@
         <v>3.125E-2</v>
       </c>
       <c r="I69">
-        <v>0.05</v>
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="J69" s="32">
-        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="L69" s="18"/>
       <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
+      <c r="N69" s="1">
+        <v>1098</v>
+      </c>
+      <c r="O69">
+        <v>3.5575039400000001</v>
+      </c>
       <c r="Q69" s="32">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>50</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="R69" s="32"/>
       <c r="S69" s="32" t="e">
@@ -4837,7 +4860,7 @@
       </c>
       <c r="T69" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>5.9291732333333333E-2</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.2">
@@ -4868,18 +4891,23 @@
         <v>3.125E-2</v>
       </c>
       <c r="I70">
-        <v>0.05</v>
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>3.125E-2</v>
       </c>
       <c r="J70" s="32">
-        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="L70" s="18"/>
       <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
+      <c r="N70" s="1">
+        <v>1282</v>
+      </c>
+      <c r="O70">
+        <v>3.1185360000000002</v>
+      </c>
       <c r="Q70" s="32">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R70" s="32"/>
       <c r="S70" s="32" t="e">
@@ -4888,7 +4916,7 @@
       </c>
       <c r="T70" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>5.1975600000000004E-2</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.2">
@@ -4919,18 +4947,23 @@
         <v>3.125E-2</v>
       </c>
       <c r="I71">
-        <v>0.05</v>
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>1.5625E-2</v>
       </c>
       <c r="J71" s="32">
-        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="L71" s="18"/>
       <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
+      <c r="N71" s="1">
+        <v>2309</v>
+      </c>
+      <c r="O71">
+        <v>2.5030021699999998</v>
+      </c>
       <c r="Q71" s="32">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="R71" s="32"/>
       <c r="S71" s="32" t="e">
@@ -4939,7 +4972,7 @@
       </c>
       <c r="T71" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>4.1716702833333327E-2</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">
@@ -4970,18 +5003,23 @@
         <v>3.125E-2</v>
       </c>
       <c r="I72">
-        <v>0.05</v>
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>7.8125E-3</v>
       </c>
       <c r="J72" s="32">
-        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
-        <v>1.6</v>
+        <v>0.25</v>
       </c>
       <c r="L72" s="18"/>
       <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
+      <c r="N72" s="1">
+        <v>4143</v>
+      </c>
+      <c r="O72">
+        <v>2.1527149699999999</v>
+      </c>
       <c r="Q72" s="32">
         <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="R72" s="32"/>
       <c r="S72" s="32" t="e">
@@ -4990,7 +5028,540 @@
       </c>
       <c r="T72" s="32">
         <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>3.5878582833333332E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73">
+        <v>1000</v>
+      </c>
+      <c r="F73">
+        <v>32</v>
+      </c>
+      <c r="G73" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H73" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="I73">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>5.4687499999999997E-3</v>
+      </c>
+      <c r="J73" s="32">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="L73" s="18"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1">
+        <v>5585</v>
+      </c>
+      <c r="O73">
+        <v>2.2835891199999998</v>
+      </c>
+      <c r="Q73" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>457.14285714285717</v>
+      </c>
+      <c r="R73" s="32"/>
+      <c r="S73" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T73" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>3.8059818666666662E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74">
+        <v>1000</v>
+      </c>
+      <c r="F74">
+        <v>32</v>
+      </c>
+      <c r="G74" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H74" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="I74">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>2.7343749999999998E-3</v>
+      </c>
+      <c r="J74" s="32">
+        <f>0.175/2</f>
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="L74" s="18"/>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1">
+        <v>9912</v>
+      </c>
+      <c r="O74">
+        <v>3.21408892</v>
+      </c>
+      <c r="Q74" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>914.28571428571433</v>
+      </c>
+      <c r="R74" s="32"/>
+      <c r="S74" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T74" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>5.3568148666666669E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" s="3" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="3">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F75" s="3">
+        <v>32</v>
+      </c>
+      <c r="G75" s="44">
+        <v>3.125E-2</v>
+      </c>
+      <c r="H75" s="44">
+        <v>3.125E-2</v>
+      </c>
+      <c r="I75" s="3">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>1.3671874999999999E-3</v>
+      </c>
+      <c r="J75" s="34">
+        <f>J74/2</f>
+        <v>4.3749999999999997E-2</v>
+      </c>
+      <c r="L75" s="22"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4">
+        <v>17360</v>
+      </c>
+      <c r="O75" s="3">
+        <v>5.3569212000000004</v>
+      </c>
+      <c r="Q75" s="34">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>1828.5714285714287</v>
+      </c>
+      <c r="R75" s="34"/>
+      <c r="S75" s="34" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T75" s="34">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>8.9282020000000004E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="42">
+        <v>1</v>
+      </c>
+      <c r="D76" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="42">
+        <v>1000</v>
+      </c>
+      <c r="F76">
+        <v>128</v>
+      </c>
+      <c r="G76" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="H76" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="I76">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J76" s="43">
+        <v>0.64</v>
+      </c>
+      <c r="L76" s="18"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1">
+        <v>11959</v>
+      </c>
+      <c r="O76">
+        <v>377.37094100000002</v>
+      </c>
+      <c r="Q76" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>500</v>
+      </c>
+      <c r="R76" s="32"/>
+      <c r="S76" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T76" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>6.2895156833333337</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77">
+        <v>1000</v>
+      </c>
+      <c r="F77">
+        <v>128</v>
+      </c>
+      <c r="G77" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="H77" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="I77">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>3.90625E-3</v>
+      </c>
+      <c r="J77">
+        <v>0.5</v>
+      </c>
+      <c r="L77" s="18"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1">
+        <v>14323</v>
+      </c>
+      <c r="O77">
+        <v>344.36364700000001</v>
+      </c>
+      <c r="Q77" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>640</v>
+      </c>
+      <c r="R77" s="32"/>
+      <c r="S77" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T77" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>5.7393941166666673</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="41">
+        <v>1</v>
+      </c>
+      <c r="D78" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F78">
+        <v>128</v>
+      </c>
+      <c r="G78" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="H78" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="I78">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>1.953125E-3</v>
+      </c>
+      <c r="J78" s="32">
+        <v>0.25</v>
+      </c>
+      <c r="L78" s="18"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1">
+        <v>24500</v>
+      </c>
+      <c r="O78">
+        <v>296.970123</v>
+      </c>
+      <c r="Q78" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>1280</v>
+      </c>
+      <c r="R78" s="32"/>
+      <c r="S78" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T78" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>4.9495020500000004</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79">
+        <v>1000</v>
+      </c>
+      <c r="F79">
+        <v>128</v>
+      </c>
+      <c r="G79" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="H79" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="I79">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>9.765625E-4</v>
+      </c>
+      <c r="J79" s="32">
+        <v>0.125</v>
+      </c>
+      <c r="L79" s="18"/>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1">
+        <v>42482</v>
+      </c>
+      <c r="O79">
+        <v>309.02886999999998</v>
+      </c>
+      <c r="Q79" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>2560</v>
+      </c>
+      <c r="R79" s="32"/>
+      <c r="S79" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T79" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>5.1504811666666663</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80">
+        <v>1000</v>
+      </c>
+      <c r="F80">
+        <v>128</v>
+      </c>
+      <c r="G80" s="32">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="H80" s="32">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="I80">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>4.8828125E-4</v>
+      </c>
+      <c r="J80" s="32">
+        <f>J79/2</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="L80" s="18"/>
+      <c r="M80" s="1"/>
+      <c r="N80" s="1"/>
+      <c r="Q80" s="32">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>5120</v>
+      </c>
+      <c r="R80" s="32"/>
+      <c r="S80" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T80" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+      <c r="J81" s="32"/>
+      <c r="L81" s="18"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="Q81" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R81" s="32"/>
+      <c r="S81" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T81" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="G82" s="32"/>
+      <c r="H82" s="32"/>
+      <c r="J82" s="32"/>
+      <c r="L82" s="18"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="Q82" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R82" s="32"/>
+      <c r="S82" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T82" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+      <c r="J83" s="32"/>
+      <c r="L83" s="18"/>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="Q83" s="32" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R83" s="32"/>
+      <c r="S83" s="32" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T83" s="32">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B84" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84">
+        <v>1000</v>
+      </c>
+      <c r="F84">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annashen/Desktop/code/ME663-project/postprocess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{1730DFB9-55E5-BC48-A846-4CF2FC93D49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578C7F68-1FD2-D14E-AA94-4DF9818C1BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="27040" windowHeight="16880" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="30">
   <si>
     <t>case</t>
   </si>
@@ -294,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -313,33 +312,37 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,8 +432,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T83" totalsRowShown="0">
-  <autoFilter ref="A1:T83" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T94" totalsRowShown="0">
+  <autoFilter ref="A1:T94" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{F042FD67-138A-3747-8F7D-92055EB26E1F}" name="case"/>
     <tableColumn id="19" xr3:uid="{6D3F4F6F-712A-EA45-8F90-560AA5EB3396}" name="solution_method"/>
@@ -826,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8141C424-3935-5946-8401-AC39630593AC}">
-  <dimension ref="A1:T84"/>
+  <dimension ref="A1:T94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="13.6640625" customWidth="1"/>
@@ -2419,294 +2422,294 @@
         <v>1.2963990533333332</v>
       </c>
     </row>
-    <row r="27" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F27" s="18">
+      <c r="C27">
+        <v>-1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27">
+        <v>1000</v>
+      </c>
+      <c r="F27">
         <v>16</v>
       </c>
-      <c r="G27" s="18">
+      <c r="G27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H27" s="19">
-        <v>-1</v>
-      </c>
-      <c r="I27" s="19">
-        <v>-1</v>
-      </c>
-      <c r="J27" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K27" s="21">
+      <c r="H27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K27" s="18">
         <v>0.3</v>
       </c>
-      <c r="L27" s="18">
+      <c r="L27">
         <v>0.85</v>
       </c>
-      <c r="N27" s="18">
+      <c r="N27">
         <v>294</v>
       </c>
-      <c r="O27" s="20">
+      <c r="O27" s="1">
         <v>7.18609989E-2</v>
       </c>
-      <c r="P27" s="18" t="s">
+      <c r="P27" t="s">
         <v>18</v>
       </c>
-      <c r="Q27" s="18">
+      <c r="Q27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S27" s="18" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T27" s="18">
+      <c r="S27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.197683315E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F28" s="18">
+      <c r="C28">
+        <v>-1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28">
+        <v>1000</v>
+      </c>
+      <c r="F28">
         <v>32</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H28" s="19">
-        <v>-1</v>
-      </c>
-      <c r="I28" s="19">
-        <v>-1</v>
-      </c>
-      <c r="J28" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K28" s="21">
+      <c r="H28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K28" s="18">
         <v>0.3</v>
       </c>
-      <c r="L28" s="18">
+      <c r="L28">
         <v>0.75</v>
       </c>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20">
+      <c r="M28" s="1"/>
+      <c r="N28" s="1">
         <v>460</v>
       </c>
-      <c r="O28" s="18">
+      <c r="O28">
         <v>0.33705398399999997</v>
       </c>
-      <c r="Q28" s="18">
+      <c r="Q28">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S28" s="18" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T28" s="18">
+      <c r="S28" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T28">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.6175663999999993E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F29" s="18">
+      <c r="C29">
+        <v>-1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29">
+        <v>1000</v>
+      </c>
+      <c r="F29">
         <v>64</v>
       </c>
-      <c r="G29" s="18">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H29" s="19">
-        <v>-1</v>
-      </c>
-      <c r="I29" s="19">
-        <v>-1</v>
-      </c>
-      <c r="J29" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K29" s="21">
+      <c r="G29">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K29" s="18">
         <v>0.3</v>
       </c>
-      <c r="L29" s="18">
+      <c r="L29">
         <v>0.78</v>
       </c>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20">
+      <c r="M29" s="1"/>
+      <c r="N29" s="1">
         <v>1279</v>
       </c>
-      <c r="O29" s="18">
+      <c r="O29">
         <v>3.5678272199999999</v>
       </c>
-      <c r="Q29" s="18">
+      <c r="Q29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S29" s="18" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T29" s="18">
+      <c r="S29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.9463786999999997E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="18">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F30" s="18">
+      <c r="C30">
+        <v>-1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30">
+        <v>1000</v>
+      </c>
+      <c r="F30">
         <v>128</v>
       </c>
-      <c r="G30" s="18">
+      <c r="G30">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H30" s="19">
-        <v>-1</v>
-      </c>
-      <c r="I30" s="19">
-        <v>-1</v>
-      </c>
-      <c r="J30" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K30" s="21">
+      <c r="H30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K30" s="18">
         <v>0.3</v>
       </c>
-      <c r="L30" s="18">
+      <c r="L30">
         <v>0.99</v>
       </c>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20">
+      <c r="M30" s="1"/>
+      <c r="N30" s="1">
         <v>1882</v>
       </c>
-      <c r="O30" s="18">
+      <c r="O30">
         <v>20.745883899999999</v>
       </c>
-      <c r="Q30" s="18">
+      <c r="Q30">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S30" s="18" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T30" s="18">
+      <c r="S30" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T30">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.34576473166666666</v>
       </c>
     </row>
-    <row r="31" spans="1:20" s="22" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="22">
+    <row r="31" spans="1:20" s="3" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="22">
-        <v>-1</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="22">
-        <v>1000</v>
-      </c>
-      <c r="F31" s="22">
+      <c r="C31" s="3">
+        <v>-1</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F31" s="3">
         <v>256</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="3">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H31" s="23">
-        <v>-1</v>
-      </c>
-      <c r="I31" s="23">
-        <v>-1</v>
-      </c>
-      <c r="J31" s="23">
-        <v>-1</v>
-      </c>
-      <c r="K31" s="24">
+      <c r="H31" s="19">
+        <v>-1</v>
+      </c>
+      <c r="I31" s="19">
+        <v>-1</v>
+      </c>
+      <c r="J31" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K31" s="20">
         <v>0.3</v>
       </c>
-      <c r="L31" s="22">
+      <c r="L31" s="3">
         <v>0.7</v>
       </c>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25">
+      <c r="M31" s="4"/>
+      <c r="N31" s="4">
         <v>7290</v>
       </c>
-      <c r="O31" s="22">
+      <c r="O31" s="3">
         <v>421.73425300000002</v>
       </c>
-      <c r="Q31" s="22">
+      <c r="Q31" s="3">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S31" s="22" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T31" s="22">
+      <c r="S31" s="3" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T31" s="3">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>7.0289042166666666</v>
       </c>
@@ -2719,7 +2722,7 @@
         <v>12</v>
       </c>
       <c r="C32" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>13</v>
@@ -2734,20 +2737,20 @@
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="21">
         <v>-1</v>
       </c>
       <c r="I32" s="15">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="J32" s="26">
+      <c r="J32" s="21">
         <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>1.0880000000000001</v>
       </c>
-      <c r="K32" s="26">
-        <v>-1</v>
-      </c>
-      <c r="L32" s="26">
+      <c r="K32" s="21">
+        <v>-1</v>
+      </c>
+      <c r="L32" s="21">
         <v>-1</v>
       </c>
       <c r="M32" s="15">
@@ -2783,7 +2786,7 @@
         <v>12</v>
       </c>
       <c r="C33" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>13</v>
@@ -2804,7 +2807,7 @@
       <c r="I33" s="15">
         <v>1E-3</v>
       </c>
-      <c r="J33" s="26">
+      <c r="J33" s="21">
         <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>6.4000000000000001E-2</v>
       </c>
@@ -2842,7 +2845,7 @@
         <v>12</v>
       </c>
       <c r="C34" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>13</v>
@@ -2863,7 +2866,7 @@
       <c r="I34" s="15">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J34" s="26">
+      <c r="J34" s="21">
         <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.32</v>
       </c>
@@ -2901,7 +2904,7 @@
         <v>12</v>
       </c>
       <c r="C35" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>13</v>
@@ -2922,7 +2925,7 @@
       <c r="I35" s="15">
         <v>0.01</v>
       </c>
-      <c r="J35" s="26">
+      <c r="J35" s="21">
         <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
@@ -2960,7 +2963,7 @@
         <v>12</v>
       </c>
       <c r="C36" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>13</v>
@@ -2981,7 +2984,7 @@
       <c r="I36" s="15">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="J36" s="26">
+      <c r="J36" s="21">
         <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>3.2000000000000001E-2</v>
       </c>
@@ -3011,7 +3014,7 @@
         <v>1.2455248516666666</v>
       </c>
     </row>
-    <row r="37" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15">
         <v>36</v>
       </c>
@@ -3019,7 +3022,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>13</v>
@@ -3030,43 +3033,43 @@
       <c r="F37" s="15">
         <v>64</v>
       </c>
-      <c r="G37" s="28">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H37" s="28">
-        <v>-1</v>
-      </c>
-      <c r="I37" s="28">
+      <c r="G37" s="23">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H37" s="23">
+        <v>-1</v>
+      </c>
+      <c r="I37" s="23">
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28">
-        <v>-1</v>
-      </c>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28">
+      <c r="J37" s="23"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="23">
+        <v>-1</v>
+      </c>
+      <c r="M37" s="23"/>
+      <c r="N37" s="23">
         <v>38422</v>
       </c>
-      <c r="O37" s="29">
+      <c r="O37" s="24">
         <v>59.427192699999999</v>
       </c>
-      <c r="P37" s="28" t="s">
+      <c r="P37" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="Q37" s="30">
+      <c r="Q37" s="25">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>3333.3333333333335</v>
       </c>
-      <c r="R37" s="27">
+      <c r="R37" s="22">
         <v>5000</v>
       </c>
-      <c r="S37" s="31">
+      <c r="S37" s="26">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.6844000000000001</v>
       </c>
-      <c r="T37" s="31">
+      <c r="T37" s="26">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.99045321166666667</v>
       </c>
@@ -3079,7 +3082,7 @@
         <v>12</v>
       </c>
       <c r="C38" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>13</v>
@@ -3138,7 +3141,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>13</v>
@@ -3149,11 +3152,11 @@
       <c r="F39" s="15">
         <v>64</v>
       </c>
-      <c r="G39" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H39" s="32">
+      <c r="G39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H39">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -3164,7 +3167,6 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.48</v>
       </c>
-      <c r="L39" s="18"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1">
         <v>5759</v>
@@ -3172,44 +3174,43 @@
       <c r="O39">
         <v>95.118499799999995</v>
       </c>
-      <c r="Q39" s="32">
+      <c r="Q39">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>333.33333333333337</v>
       </c>
-      <c r="R39" s="32"/>
-      <c r="S39" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T39" s="32">
+      <c r="S39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T39">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.5853083299999999</v>
       </c>
     </row>
     <row r="40" spans="1:20" s="3" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="33">
+      <c r="A40" s="27">
         <v>39</v>
       </c>
-      <c r="B40" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="33">
-        <v>1</v>
-      </c>
-      <c r="D40" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="33">
-        <v>1000</v>
-      </c>
-      <c r="F40" s="33">
+      <c r="B40" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="27">
+        <v>2</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F40" s="27">
         <v>64</v>
       </c>
-      <c r="G40" s="34">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H40" s="34">
+      <c r="G40" s="3">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H40" s="3">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -3220,7 +3221,6 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.96</v>
       </c>
-      <c r="L40" s="22"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4">
         <v>3102</v>
@@ -3228,16 +3228,15 @@
       <c r="O40" s="3">
         <v>140.86225899999999</v>
       </c>
-      <c r="Q40" s="34">
+      <c r="Q40" s="3">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T40" s="34">
+      <c r="S40" s="3" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T40" s="3">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>2.3477043166666665</v>
       </c>
@@ -3250,7 +3249,7 @@
         <v>12</v>
       </c>
       <c r="C41" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="15" t="s">
         <v>13</v>
@@ -3261,11 +3260,11 @@
       <c r="F41" s="15">
         <v>64</v>
       </c>
-      <c r="G41" s="35">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H41" s="35">
+      <c r="G41" s="15">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H41" s="15">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -3283,16 +3282,15 @@
       <c r="O41" s="15">
         <v>175.09970100000001</v>
       </c>
-      <c r="Q41" s="35">
+      <c r="Q41" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>16000</v>
       </c>
-      <c r="R41" s="35"/>
-      <c r="S41" s="35" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T41" s="35">
+      <c r="S41" s="15" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T41" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>2.9183283500000003</v>
       </c>
@@ -3305,7 +3303,7 @@
         <v>12</v>
       </c>
       <c r="C42" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>13</v>
@@ -3316,11 +3314,11 @@
       <c r="F42" s="15">
         <v>64</v>
       </c>
-      <c r="G42" s="35">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H42" s="35">
+      <c r="G42" s="15">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H42" s="15">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -3338,16 +3336,15 @@
       <c r="O42" s="15">
         <v>58.603294400000003</v>
       </c>
-      <c r="Q42" s="35">
+      <c r="Q42" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>3200</v>
       </c>
-      <c r="R42" s="35"/>
-      <c r="S42" s="35" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T42" s="35">
+      <c r="S42" s="15" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T42" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.97672157333333343</v>
       </c>
@@ -3360,7 +3357,7 @@
         <v>12</v>
       </c>
       <c r="C43" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" s="15" t="s">
         <v>13</v>
@@ -3371,11 +3368,11 @@
       <c r="F43" s="15">
         <v>64</v>
       </c>
-      <c r="G43" s="35">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H43" s="35">
+      <c r="G43" s="15">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H43" s="15">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -3383,7 +3380,7 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>3.1250000000000002E-3</v>
       </c>
-      <c r="J43" s="35">
+      <c r="J43" s="15">
         <v>0.2</v>
       </c>
       <c r="M43" s="16"/>
@@ -3393,16 +3390,15 @@
       <c r="O43" s="15">
         <v>60.159965499999998</v>
       </c>
-      <c r="Q43" s="35">
+      <c r="Q43" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>800</v>
       </c>
-      <c r="R43" s="35"/>
-      <c r="S43" s="35" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T43" s="35">
+      <c r="S43" s="15" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T43" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.0026660916666665</v>
       </c>
@@ -3415,7 +3411,7 @@
         <v>12</v>
       </c>
       <c r="C44" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>13</v>
@@ -3426,11 +3422,11 @@
       <c r="F44" s="15">
         <v>64</v>
       </c>
-      <c r="G44" s="35">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H44" s="35">
+      <c r="G44" s="15">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H44" s="15">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -3438,7 +3434,7 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>6.2500000000000003E-3</v>
       </c>
-      <c r="J44" s="35">
+      <c r="J44" s="15">
         <v>0.4</v>
       </c>
       <c r="M44" s="16"/>
@@ -3448,16 +3444,15 @@
       <c r="O44" s="15">
         <v>87.384323100000003</v>
       </c>
-      <c r="Q44" s="35">
+      <c r="Q44" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>400</v>
       </c>
-      <c r="R44" s="35"/>
-      <c r="S44" s="35" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T44" s="35">
+      <c r="S44" s="15" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T44" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.4564053850000001</v>
       </c>
@@ -3470,7 +3465,7 @@
         <v>12</v>
       </c>
       <c r="C45" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>13</v>
@@ -3481,11 +3476,11 @@
       <c r="F45" s="15">
         <v>64</v>
       </c>
-      <c r="G45" s="35">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H45" s="35">
+      <c r="G45" s="15">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H45" s="15">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -3493,7 +3488,7 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="J45" s="35">
+      <c r="J45" s="15">
         <v>0.5</v>
       </c>
       <c r="M45" s="16"/>
@@ -3503,16 +3498,15 @@
       <c r="O45" s="15">
         <v>97.289329499999994</v>
       </c>
-      <c r="Q45" s="35">
+      <c r="Q45" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>320</v>
       </c>
-      <c r="R45" s="35"/>
-      <c r="S45" s="35" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T45" s="35">
+      <c r="S45" s="15" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T45" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.6214888249999999</v>
       </c>
@@ -3525,7 +3519,7 @@
         <v>12</v>
       </c>
       <c r="C46" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>13</v>
@@ -3536,11 +3530,11 @@
       <c r="F46" s="15">
         <v>64</v>
       </c>
-      <c r="G46" s="35">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H46" s="35">
+      <c r="G46" s="15">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H46" s="15">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -3548,7 +3542,7 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>9.3749999999999997E-3</v>
       </c>
-      <c r="J46" s="35">
+      <c r="J46" s="15">
         <v>0.6</v>
       </c>
       <c r="M46" s="16"/>
@@ -3558,16 +3552,15 @@
       <c r="O46" s="15">
         <v>107.397453</v>
       </c>
-      <c r="Q46" s="35">
+      <c r="Q46" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>266.66666666666669</v>
       </c>
-      <c r="R46" s="35"/>
-      <c r="S46" s="35" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T46" s="35">
+      <c r="S46" s="15" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T46" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.78995755</v>
       </c>
@@ -3580,7 +3573,7 @@
         <v>12</v>
       </c>
       <c r="C47" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>13</v>
@@ -3591,11 +3584,11 @@
       <c r="F47" s="15">
         <v>64</v>
       </c>
-      <c r="G47" s="35">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H47" s="35">
+      <c r="G47" s="15">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H47" s="15">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -3603,7 +3596,7 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="J47" s="35">
+      <c r="J47" s="15">
         <v>0.8</v>
       </c>
       <c r="M47" s="16"/>
@@ -3613,676 +3606,663 @@
       <c r="O47" s="15">
         <v>127.491776</v>
       </c>
-      <c r="Q47" s="35">
+      <c r="Q47" s="15">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>200</v>
       </c>
-      <c r="R47" s="35"/>
-      <c r="S47" s="35" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T47" s="35">
+      <c r="S47" s="15" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T47" s="15">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>2.1248629333333335</v>
       </c>
     </row>
-    <row r="48" spans="1:20" s="33" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="33">
+    <row r="48" spans="1:20" s="27" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
         <v>47</v>
       </c>
-      <c r="B48" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="33">
+      <c r="B48" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="27">
+        <v>2</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="27">
+        <v>64</v>
+      </c>
+      <c r="G48" s="27">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H48" s="27">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I48" s="27">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J48" s="27">
         <v>1</v>
       </c>
-      <c r="D48" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="33">
-        <v>1000</v>
-      </c>
-      <c r="F48" s="33">
-        <v>64</v>
-      </c>
-      <c r="G48" s="36">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H48" s="36">
-        <f>Table52[[#This Row],[DX]]/1</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="I48" s="33">
-        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="J48" s="36">
+      <c r="M48" s="28"/>
+      <c r="N48" s="28">
+        <v>2987</v>
+      </c>
+      <c r="O48" s="27">
+        <v>142.69487000000001</v>
+      </c>
+      <c r="Q48" s="27">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>160</v>
+      </c>
+      <c r="S48" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T48" s="27">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>2.3782478333333334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="29">
+        <v>48</v>
+      </c>
+      <c r="B49" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="29">
         <v>1</v>
       </c>
-      <c r="M48" s="37"/>
-      <c r="N48" s="37">
-        <v>2987</v>
-      </c>
-      <c r="O48" s="33">
-        <v>142.69487000000001</v>
-      </c>
-      <c r="Q48" s="36">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>160</v>
-      </c>
-      <c r="R48" s="36"/>
-      <c r="S48" s="36" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T48" s="36">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>2.3782478333333334</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="38">
-        <v>48</v>
-      </c>
-      <c r="B49" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="38">
-        <v>1</v>
-      </c>
-      <c r="D49" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F49" s="38">
+      <c r="D49" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F49" s="29">
         <v>16</v>
       </c>
-      <c r="G49" s="39">
+      <c r="G49" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H49" s="39">
+      <c r="H49" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I49" s="38">
+      <c r="I49" s="29">
         <v>0.15</v>
       </c>
-      <c r="J49" s="39">
+      <c r="J49" s="29">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>2.4</v>
       </c>
-      <c r="M49" s="40"/>
-      <c r="N49" s="40">
+      <c r="M49" s="30"/>
+      <c r="N49" s="30">
         <v>259</v>
       </c>
-      <c r="O49" s="38">
+      <c r="O49" s="29">
         <v>0.729385018</v>
       </c>
-      <c r="Q49" s="39">
+      <c r="Q49" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>16.666666666666668</v>
       </c>
-      <c r="R49" s="39"/>
-      <c r="S49" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T49" s="39">
+      <c r="S49" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T49" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2156416966666667E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="38">
+    <row r="50" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="29">
         <v>49</v>
       </c>
-      <c r="B50" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="38">
+      <c r="B50" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="29">
         <v>1</v>
       </c>
-      <c r="D50" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F50" s="38">
+      <c r="D50" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F50" s="29">
         <v>16</v>
       </c>
-      <c r="G50" s="39">
+      <c r="G50" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H50" s="39">
+      <c r="H50" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I50" s="38">
+      <c r="I50" s="29">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>0.15625</v>
       </c>
-      <c r="J50" s="39">
+      <c r="J50" s="29">
         <v>2.5</v>
       </c>
-      <c r="M50" s="40"/>
-      <c r="N50" s="40">
+      <c r="M50" s="30"/>
+      <c r="N50" s="30">
         <v>241</v>
       </c>
-      <c r="O50" s="38">
+      <c r="O50" s="29">
         <v>0.74937796599999995</v>
       </c>
-      <c r="Q50" s="39">
+      <c r="Q50" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>16</v>
       </c>
-      <c r="R50" s="39"/>
-      <c r="S50" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T50" s="39">
+      <c r="S50" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T50" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2489632766666666E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="38">
+    <row r="51" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="29">
         <v>50</v>
       </c>
-      <c r="B51" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="38">
+      <c r="B51" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="29">
         <v>1</v>
       </c>
-      <c r="D51" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F51" s="38">
+      <c r="D51" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F51" s="29">
         <v>16</v>
       </c>
-      <c r="G51" s="39">
+      <c r="G51" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H51" s="39">
+      <c r="H51" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I51" s="38">
+      <c r="I51" s="29">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>0.140625</v>
       </c>
-      <c r="J51" s="39">
+      <c r="J51" s="29">
         <v>2.25</v>
       </c>
-      <c r="M51" s="40"/>
-      <c r="N51" s="40">
+      <c r="M51" s="30"/>
+      <c r="N51" s="30">
         <v>274</v>
       </c>
-      <c r="O51" s="38">
+      <c r="O51" s="29">
         <v>0.73873001299999996</v>
       </c>
-      <c r="Q51" s="39">
+      <c r="Q51" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>17.777777777777779</v>
       </c>
-      <c r="R51" s="39"/>
-      <c r="S51" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T51" s="39">
+      <c r="S51" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T51" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2312166883333333E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="38">
+    <row r="52" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="29">
         <v>51</v>
       </c>
-      <c r="B52" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="38">
+      <c r="B52" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="29">
         <v>1</v>
       </c>
-      <c r="D52" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F52" s="38">
+      <c r="D52" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F52" s="29">
         <v>16</v>
       </c>
-      <c r="G52" s="39">
+      <c r="G52" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H52" s="39">
+      <c r="H52" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I52" s="38">
+      <c r="I52" s="29">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>0.125</v>
       </c>
-      <c r="J52" s="39">
+      <c r="J52" s="29">
         <v>2</v>
       </c>
-      <c r="M52" s="40"/>
-      <c r="N52" s="40">
+      <c r="M52" s="30"/>
+      <c r="N52" s="30">
         <v>304</v>
       </c>
-      <c r="O52" s="38">
+      <c r="O52" s="29">
         <v>0.72258299599999998</v>
       </c>
-      <c r="Q52" s="39">
+      <c r="Q52" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>20</v>
       </c>
-      <c r="R52" s="39"/>
-      <c r="S52" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T52" s="39">
+      <c r="S52" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T52" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2043049933333333E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:20" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="38">
+    <row r="53" spans="1:20" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="29">
         <v>52</v>
       </c>
-      <c r="B53" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="38">
+      <c r="B53" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="29">
         <v>1</v>
       </c>
-      <c r="D53" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F53" s="38">
+      <c r="D53" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F53" s="29">
         <v>16</v>
       </c>
-      <c r="G53" s="39">
+      <c r="G53" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H53" s="39">
+      <c r="H53" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I53" s="38">
+      <c r="I53" s="29">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>0.109375</v>
       </c>
-      <c r="J53" s="39">
+      <c r="J53" s="29">
         <v>1.75</v>
       </c>
-      <c r="M53" s="40"/>
-      <c r="N53" s="40">
+      <c r="M53" s="30"/>
+      <c r="N53" s="30">
         <v>341</v>
       </c>
-      <c r="O53" s="38">
+      <c r="O53" s="29">
         <v>0.73771297899999999</v>
       </c>
-      <c r="Q53" s="39">
+      <c r="Q53" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>22.857142857142858</v>
       </c>
-      <c r="R53" s="39"/>
-      <c r="S53" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T53" s="39">
+      <c r="S53" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T53" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2295216316666666E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38">
+    <row r="54" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="29">
         <v>53</v>
       </c>
-      <c r="B54" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="38">
+      <c r="B54" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="29">
         <v>1</v>
       </c>
-      <c r="D54" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F54" s="38">
+      <c r="D54" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F54" s="29">
         <v>16</v>
       </c>
-      <c r="G54" s="39">
+      <c r="G54" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H54" s="39">
+      <c r="H54" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I54" s="38">
+      <c r="I54" s="29">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>9.375E-2</v>
       </c>
-      <c r="J54" s="39">
+      <c r="J54" s="29">
         <v>1.5</v>
       </c>
-      <c r="M54" s="40"/>
-      <c r="N54" s="40">
+      <c r="M54" s="30"/>
+      <c r="N54" s="30">
         <v>390</v>
       </c>
-      <c r="O54" s="38">
+      <c r="O54" s="29">
         <v>0.72225296500000002</v>
       </c>
-      <c r="Q54" s="39">
+      <c r="Q54" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>26.666666666666668</v>
       </c>
-      <c r="R54" s="39"/>
-      <c r="S54" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T54" s="39">
+      <c r="S54" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T54" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2037549416666666E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="38">
+    <row r="55" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="29">
         <v>54</v>
       </c>
-      <c r="B55" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="38">
+      <c r="B55" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="29">
         <v>2</v>
       </c>
-      <c r="D55" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F55" s="38">
+      <c r="D55" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F55" s="29">
         <v>16</v>
       </c>
-      <c r="G55" s="39">
+      <c r="G55" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H55" s="39">
+      <c r="H55" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I55" s="38">
+      <c r="I55" s="29">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>7.8125E-2</v>
       </c>
-      <c r="J55" s="39">
+      <c r="J55" s="29">
         <v>1.25</v>
       </c>
-      <c r="M55" s="40"/>
-      <c r="N55" s="40">
+      <c r="M55" s="30"/>
+      <c r="N55" s="30">
         <v>457</v>
       </c>
-      <c r="O55" s="38">
+      <c r="O55" s="29">
         <v>0.65907299500000005</v>
       </c>
-      <c r="Q55" s="39">
+      <c r="Q55" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>32</v>
       </c>
-      <c r="R55" s="39"/>
-      <c r="S55" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T55" s="39">
+      <c r="S55" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T55" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.0984549916666668E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="38">
+    <row r="56" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="29">
         <v>55</v>
       </c>
-      <c r="B56" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="38">
+      <c r="B56" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="29">
         <v>3</v>
       </c>
-      <c r="D56" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F56" s="38">
+      <c r="D56" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F56" s="29">
         <v>16</v>
       </c>
-      <c r="G56" s="39">
+      <c r="G56" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H56" s="39">
+      <c r="H56" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I56" s="38">
+      <c r="I56" s="29">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="J56" s="39">
+      <c r="J56" s="29">
         <v>1</v>
       </c>
-      <c r="M56" s="40"/>
-      <c r="N56" s="40">
+      <c r="M56" s="30"/>
+      <c r="N56" s="30">
         <v>554</v>
       </c>
-      <c r="O56" s="38">
+      <c r="O56" s="29">
         <v>0.62351202999999999</v>
       </c>
-      <c r="Q56" s="39">
+      <c r="Q56" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>40</v>
       </c>
-      <c r="R56" s="39"/>
-      <c r="S56" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T56" s="39">
+      <c r="S56" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T56" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.0391867166666667E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="38">
+    <row r="57" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="29">
         <v>56</v>
       </c>
-      <c r="B57" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="38">
+      <c r="B57" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="29">
         <v>4</v>
       </c>
-      <c r="D57" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F57" s="38">
+      <c r="D57" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F57" s="29">
         <v>16</v>
       </c>
-      <c r="G57" s="39">
+      <c r="G57" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H57" s="39">
+      <c r="H57" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I57" s="38">
+      <c r="I57" s="29">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>4.6875E-2</v>
       </c>
-      <c r="J57" s="39">
+      <c r="J57" s="29">
         <v>0.75</v>
       </c>
-      <c r="M57" s="40"/>
-      <c r="N57" s="38">
+      <c r="M57" s="30"/>
+      <c r="N57" s="29">
         <v>707</v>
       </c>
-      <c r="O57" s="38">
+      <c r="O57" s="29">
         <v>0.562693</v>
       </c>
-      <c r="Q57" s="39">
+      <c r="Q57" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>53.333333333333336</v>
       </c>
-      <c r="R57" s="39"/>
-      <c r="S57" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T57" s="39">
+      <c r="S57" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T57" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>9.3782166666666663E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="38">
+    <row r="58" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="29">
         <v>57</v>
       </c>
-      <c r="B58" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="38">
+      <c r="B58" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="29">
         <v>5</v>
       </c>
-      <c r="D58" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F58" s="38">
+      <c r="D58" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F58" s="29">
         <v>16</v>
       </c>
-      <c r="G58" s="39">
+      <c r="G58" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H58" s="39">
+      <c r="H58" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I58" s="38">
+      <c r="I58" s="29">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="J58" s="39">
+      <c r="J58" s="29">
         <v>0.5</v>
       </c>
-      <c r="M58" s="40"/>
-      <c r="N58" s="40">
+      <c r="M58" s="30"/>
+      <c r="N58" s="30">
         <v>996</v>
       </c>
-      <c r="O58" s="38">
+      <c r="O58" s="29">
         <v>0.46355798799999998</v>
       </c>
-      <c r="Q58" s="39">
+      <c r="Q58" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>80</v>
       </c>
-      <c r="R58" s="39"/>
-      <c r="S58" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T58" s="39">
+      <c r="S58" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T58" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>7.7259664666666662E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="38">
+    <row r="59" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="29">
         <v>58</v>
       </c>
-      <c r="B59" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="38">
+      <c r="B59" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="29">
         <v>5</v>
       </c>
-      <c r="D59" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F59" s="38">
+      <c r="D59" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="29">
         <v>16</v>
       </c>
-      <c r="G59" s="39">
+      <c r="G59" s="29">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H59" s="39">
+      <c r="H59" s="29">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I59" s="38">
+      <c r="I59" s="29">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J59" s="39">
+      <c r="J59" s="29">
         <v>0.25</v>
       </c>
-      <c r="M59" s="40"/>
-      <c r="N59" s="40">
+      <c r="M59" s="30"/>
+      <c r="N59" s="30">
         <v>1767</v>
       </c>
-      <c r="O59" s="38">
+      <c r="O59" s="29">
         <v>0.35058298700000001</v>
       </c>
-      <c r="Q59" s="39">
+      <c r="Q59" s="29">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>160</v>
       </c>
-      <c r="R59" s="39"/>
-      <c r="S59" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T59" s="39">
+      <c r="S59" s="29" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T59" s="29">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.8430497833333334E-3</v>
       </c>
@@ -4291,37 +4271,37 @@
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="18" t="s">
+      <c r="B60" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F60" s="18">
+      <c r="C60">
+        <v>-1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60">
+        <v>1000</v>
+      </c>
+      <c r="F60">
         <v>64</v>
       </c>
-      <c r="G60" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H60" s="32">
+      <c r="G60">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H60">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J60" s="32">
+      <c r="J60">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K60" s="21">
+      <c r="K60" s="18">
         <v>0.3</v>
       </c>
-      <c r="L60" s="18">
+      <c r="L60">
         <v>0.5</v>
       </c>
       <c r="M60" s="1"/>
@@ -4331,16 +4311,15 @@
       <c r="O60">
         <v>3.6674129999999998</v>
       </c>
-      <c r="Q60" s="32" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R60" s="32"/>
-      <c r="S60" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T60" s="32">
+      <c r="Q60" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S60" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T60">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.1123549999999999E-2</v>
       </c>
@@ -4349,37 +4328,37 @@
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="18" t="s">
+      <c r="B61" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F61" s="18">
+      <c r="C61">
+        <v>-1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61">
+        <v>1000</v>
+      </c>
+      <c r="F61">
         <v>64</v>
       </c>
-      <c r="G61" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H61" s="32">
+      <c r="G61">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H61">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J61" s="32">
+      <c r="J61">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K61" s="21">
+      <c r="K61" s="18">
         <v>0.3</v>
       </c>
-      <c r="L61" s="18">
+      <c r="L61">
         <v>0.6</v>
       </c>
       <c r="M61" s="1"/>
@@ -4389,16 +4368,15 @@
       <c r="O61">
         <v>3.2093491599999999</v>
       </c>
-      <c r="Q61" s="32" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R61" s="32"/>
-      <c r="S61" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T61" s="32">
+      <c r="Q61" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S61" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T61">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.3489152666666664E-2</v>
       </c>
@@ -4407,37 +4385,37 @@
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="B62" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F62" s="18">
+      <c r="C62">
+        <v>-1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62">
+        <v>1000</v>
+      </c>
+      <c r="F62">
         <v>64</v>
       </c>
-      <c r="G62" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H62" s="32">
+      <c r="G62">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H62">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K62" s="21">
+      <c r="K62" s="18">
         <v>0.3</v>
       </c>
-      <c r="L62" s="18">
+      <c r="L62">
         <v>0.7</v>
       </c>
       <c r="M62" s="1"/>
@@ -4447,16 +4425,15 @@
       <c r="O62">
         <v>2.6229457900000002</v>
       </c>
-      <c r="Q62" s="32" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R62" s="32"/>
-      <c r="S62" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T62" s="32">
+      <c r="Q62" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S62" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T62">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>4.3715763166666671E-2</v>
       </c>
@@ -4465,37 +4442,37 @@
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F63" s="18">
+      <c r="C63">
+        <v>-1</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63">
+        <v>1000</v>
+      </c>
+      <c r="F63">
         <v>64</v>
       </c>
-      <c r="G63" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H63" s="32">
+      <c r="G63">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H63">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J63" s="32">
+      <c r="J63">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K63" s="21">
+      <c r="K63" s="18">
         <v>0.3</v>
       </c>
-      <c r="L63" s="18">
+      <c r="L63">
         <v>0.8</v>
       </c>
       <c r="M63" s="1"/>
@@ -4505,16 +4482,15 @@
       <c r="O63">
         <v>6.3866229099999998</v>
       </c>
-      <c r="Q63" s="32" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R63" s="32"/>
-      <c r="S63" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T63" s="32">
+      <c r="Q63" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S63" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T63">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.10644371516666666</v>
       </c>
@@ -4523,37 +4499,37 @@
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B64" t="s">
         <v>19</v>
       </c>
-      <c r="C64" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F64" s="18">
+      <c r="C64">
+        <v>-1</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64">
+        <v>1000</v>
+      </c>
+      <c r="F64">
         <v>64</v>
       </c>
-      <c r="G64" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H64" s="32">
+      <c r="G64">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H64">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J64" s="32">
+      <c r="J64">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K64" s="21">
+      <c r="K64" s="18">
         <v>0.3</v>
       </c>
-      <c r="L64" s="18">
+      <c r="L64">
         <v>0.75</v>
       </c>
       <c r="M64" s="1"/>
@@ -4563,16 +4539,15 @@
       <c r="O64">
         <v>2.6197769599999998</v>
       </c>
-      <c r="Q64" s="32" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R64" s="32"/>
-      <c r="S64" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T64" s="32">
+      <c r="Q64" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S64" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T64">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>4.3662949333333333E-2</v>
       </c>
@@ -4581,37 +4556,37 @@
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="B65" t="s">
         <v>19</v>
       </c>
-      <c r="C65" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D65" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F65" s="18">
+      <c r="C65">
+        <v>-1</v>
+      </c>
+      <c r="D65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65">
+        <v>1000</v>
+      </c>
+      <c r="F65">
         <v>64</v>
       </c>
-      <c r="G65" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H65" s="32">
+      <c r="G65">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H65">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J65">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K65" s="21">
+      <c r="K65" s="18">
         <v>0.3</v>
       </c>
-      <c r="L65" s="18">
+      <c r="L65">
         <v>0.81</v>
       </c>
       <c r="M65" s="1"/>
@@ -4621,16 +4596,15 @@
       <c r="O65">
         <v>10.8955822</v>
       </c>
-      <c r="Q65" s="32" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R65" s="32"/>
-      <c r="S65" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T65" s="32">
+      <c r="Q65" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S65" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T65">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.18159303666666665</v>
       </c>
@@ -4639,37 +4613,37 @@
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="18" t="s">
+      <c r="B66" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="18">
-        <v>-1</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="18">
-        <v>1000</v>
-      </c>
-      <c r="F66" s="18">
+      <c r="C66">
+        <v>-1</v>
+      </c>
+      <c r="D66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66">
+        <v>1000</v>
+      </c>
+      <c r="F66">
         <v>64</v>
       </c>
-      <c r="G66" s="32">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H66" s="32">
+      <c r="G66">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H66">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J66" s="32">
+      <c r="J66">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K66" s="21">
+      <c r="K66" s="18">
         <v>0.3</v>
       </c>
-      <c r="L66" s="18">
+      <c r="L66">
         <v>0.4</v>
       </c>
       <c r="M66" s="1"/>
@@ -4679,16 +4653,15 @@
       <c r="O66">
         <v>4.5329389600000001</v>
       </c>
-      <c r="Q66" s="32" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R66" s="32"/>
-      <c r="S66" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T66" s="32">
+      <c r="Q66" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S66" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T66">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>7.5548982666666667E-2</v>
       </c>
@@ -4697,37 +4670,37 @@
       <c r="A67" s="3">
         <v>66</v>
       </c>
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="22">
-        <v>-1</v>
-      </c>
-      <c r="D67" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="22">
-        <v>1000</v>
-      </c>
-      <c r="F67" s="22">
+      <c r="C67" s="3">
+        <v>-1</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F67" s="3">
         <v>64</v>
       </c>
-      <c r="G67" s="34">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H67" s="34">
+      <c r="G67" s="3">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H67" s="3">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J67" s="34">
+      <c r="J67" s="3">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K67" s="24">
+      <c r="K67" s="20">
         <v>0.3</v>
       </c>
-      <c r="L67" s="22">
+      <c r="L67" s="3">
         <v>0.78</v>
       </c>
       <c r="M67" s="4"/>
@@ -4737,16 +4710,15 @@
       <c r="O67" s="3">
         <v>3.5589289700000002</v>
       </c>
-      <c r="Q67" s="34" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R67" s="34"/>
-      <c r="S67" s="34" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T67" s="34">
+      <c r="Q67" s="3" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S67" s="3" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T67" s="3">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.9315482833333336E-2</v>
       </c>
@@ -4770,22 +4742,21 @@
       <c r="F68">
         <v>32</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
       <c r="I68">
         <v>0.05</v>
       </c>
-      <c r="J68" s="32">
+      <c r="J68">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>1.6</v>
       </c>
-      <c r="L68" s="18"/>
       <c r="M68" s="1"/>
       <c r="N68" s="1">
         <v>857</v>
@@ -4793,16 +4764,15 @@
       <c r="O68">
         <v>3.7602040799999998</v>
       </c>
-      <c r="Q68" s="32">
+      <c r="Q68">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>50</v>
       </c>
-      <c r="R68" s="32"/>
-      <c r="S68" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T68" s="32">
+      <c r="S68" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T68">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.2670067999999995E-2</v>
       </c>
@@ -4826,11 +4796,11 @@
       <c r="F69">
         <v>32</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H69" s="32">
+      <c r="H69">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
@@ -4838,10 +4808,9 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="J69" s="32">
+      <c r="J69">
         <v>1.2</v>
       </c>
-      <c r="L69" s="18"/>
       <c r="M69" s="1"/>
       <c r="N69" s="1">
         <v>1098</v>
@@ -4849,16 +4818,15 @@
       <c r="O69">
         <v>3.5575039400000001</v>
       </c>
-      <c r="Q69" s="32">
+      <c r="Q69">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>66.666666666666671</v>
       </c>
-      <c r="R69" s="32"/>
-      <c r="S69" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T69" s="32">
+      <c r="S69" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T69">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.9291732333333333E-2</v>
       </c>
@@ -4882,11 +4850,11 @@
       <c r="F70">
         <v>32</v>
       </c>
-      <c r="G70" s="32">
+      <c r="G70">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H70" s="32">
+      <c r="H70">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
@@ -4894,10 +4862,9 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="J70" s="32">
+      <c r="J70">
         <v>1</v>
       </c>
-      <c r="L70" s="18"/>
       <c r="M70" s="1"/>
       <c r="N70" s="1">
         <v>1282</v>
@@ -4905,16 +4872,15 @@
       <c r="O70">
         <v>3.1185360000000002</v>
       </c>
-      <c r="Q70" s="32">
+      <c r="Q70">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>80</v>
       </c>
-      <c r="R70" s="32"/>
-      <c r="S70" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T70" s="32">
+      <c r="S70" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T70">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.1975600000000004E-2</v>
       </c>
@@ -4938,11 +4904,11 @@
       <c r="F71">
         <v>32</v>
       </c>
-      <c r="G71" s="32">
+      <c r="G71">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H71" s="32">
+      <c r="H71">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
@@ -4950,10 +4916,9 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J71" s="32">
+      <c r="J71">
         <v>0.5</v>
       </c>
-      <c r="L71" s="18"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1">
         <v>2309</v>
@@ -4961,16 +4926,15 @@
       <c r="O71">
         <v>2.5030021699999998</v>
       </c>
-      <c r="Q71" s="32">
+      <c r="Q71">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>160</v>
       </c>
-      <c r="R71" s="32"/>
-      <c r="S71" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T71" s="32">
+      <c r="S71" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T71">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>4.1716702833333327E-2</v>
       </c>
@@ -4994,11 +4958,11 @@
       <c r="F72">
         <v>32</v>
       </c>
-      <c r="G72" s="32">
+      <c r="G72">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H72" s="32">
+      <c r="H72">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
@@ -5006,10 +4970,9 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="J72" s="32">
+      <c r="J72">
         <v>0.25</v>
       </c>
-      <c r="L72" s="18"/>
       <c r="M72" s="1"/>
       <c r="N72" s="1">
         <v>4143</v>
@@ -5017,16 +4980,15 @@
       <c r="O72">
         <v>2.1527149699999999</v>
       </c>
-      <c r="Q72" s="32">
+      <c r="Q72">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>320</v>
       </c>
-      <c r="R72" s="32"/>
-      <c r="S72" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T72" s="32">
+      <c r="S72" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T72">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>3.5878582833333332E-2</v>
       </c>
@@ -5050,11 +5012,11 @@
       <c r="F73">
         <v>32</v>
       </c>
-      <c r="G73" s="32">
+      <c r="G73">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H73" s="32">
+      <c r="H73">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
@@ -5062,10 +5024,9 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>5.4687499999999997E-3</v>
       </c>
-      <c r="J73" s="32">
+      <c r="J73">
         <v>0.17499999999999999</v>
       </c>
-      <c r="L73" s="18"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1">
         <v>5585</v>
@@ -5073,16 +5034,15 @@
       <c r="O73">
         <v>2.2835891199999998</v>
       </c>
-      <c r="Q73" s="32">
+      <c r="Q73">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>457.14285714285717</v>
       </c>
-      <c r="R73" s="32"/>
-      <c r="S73" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T73" s="32">
+      <c r="S73" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T73">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>3.8059818666666662E-2</v>
       </c>
@@ -5106,11 +5066,11 @@
       <c r="F74">
         <v>32</v>
       </c>
-      <c r="G74" s="32">
+      <c r="G74">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H74" s="32">
+      <c r="H74">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>3.125E-2</v>
       </c>
@@ -5118,11 +5078,10 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>2.7343749999999998E-3</v>
       </c>
-      <c r="J74" s="32">
+      <c r="J74">
         <f>0.175/2</f>
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="L74" s="18"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1">
         <v>9912</v>
@@ -5130,16 +5089,15 @@
       <c r="O74">
         <v>3.21408892</v>
       </c>
-      <c r="Q74" s="32">
+      <c r="Q74">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>914.28571428571433</v>
       </c>
-      <c r="R74" s="32"/>
-      <c r="S74" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T74" s="32">
+      <c r="S74" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T74">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.3568148666666669E-2</v>
       </c>
@@ -5163,21 +5121,20 @@
       <c r="F75" s="3">
         <v>32</v>
       </c>
-      <c r="G75" s="44">
+      <c r="G75" s="34">
         <v>3.125E-2</v>
       </c>
-      <c r="H75" s="44">
+      <c r="H75" s="34">
         <v>3.125E-2</v>
       </c>
       <c r="I75" s="3">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.3671874999999999E-3</v>
       </c>
-      <c r="J75" s="34">
+      <c r="J75" s="3">
         <f>J74/2</f>
         <v>4.3749999999999997E-2</v>
       </c>
-      <c r="L75" s="22"/>
       <c r="M75" s="4"/>
       <c r="N75" s="4">
         <v>17360</v>
@@ -5185,16 +5142,15 @@
       <c r="O75" s="3">
         <v>5.3569212000000004</v>
       </c>
-      <c r="Q75" s="34">
+      <c r="Q75" s="3">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>1828.5714285714287</v>
       </c>
-      <c r="R75" s="34"/>
-      <c r="S75" s="34" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T75" s="34">
+      <c r="S75" s="3" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T75" s="3">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>8.9282020000000004E-2</v>
       </c>
@@ -5203,26 +5159,26 @@
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="42">
+      <c r="B76" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="32">
         <v>1</v>
       </c>
-      <c r="D76" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="42">
+      <c r="D76" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="32">
         <v>1000</v>
       </c>
       <c r="F76">
         <v>128</v>
       </c>
-      <c r="G76" s="32">
+      <c r="G76">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H76" s="32">
+      <c r="H76">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>7.8125E-3</v>
       </c>
@@ -5230,10 +5186,9 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J76" s="43">
+      <c r="J76" s="33">
         <v>0.64</v>
       </c>
-      <c r="L76" s="18"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1">
         <v>11959</v>
@@ -5241,16 +5196,15 @@
       <c r="O76">
         <v>377.37094100000002</v>
       </c>
-      <c r="Q76" s="32">
+      <c r="Q76">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>500</v>
       </c>
-      <c r="R76" s="32"/>
-      <c r="S76" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T76" s="32">
+      <c r="S76" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T76">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>6.2895156833333337</v>
       </c>
@@ -5274,11 +5228,11 @@
       <c r="F77">
         <v>128</v>
       </c>
-      <c r="G77" s="32">
+      <c r="G77">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H77" s="32">
+      <c r="H77">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>7.8125E-3</v>
       </c>
@@ -5289,7 +5243,6 @@
       <c r="J77">
         <v>0.5</v>
       </c>
-      <c r="L77" s="18"/>
       <c r="M77" s="1"/>
       <c r="N77" s="1">
         <v>14323</v>
@@ -5297,16 +5250,15 @@
       <c r="O77">
         <v>344.36364700000001</v>
       </c>
-      <c r="Q77" s="32">
+      <c r="Q77">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>640</v>
       </c>
-      <c r="R77" s="32"/>
-      <c r="S77" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T77" s="32">
+      <c r="S77" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T77">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.7393941166666673</v>
       </c>
@@ -5315,26 +5267,26 @@
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="41">
+      <c r="B78" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="31">
         <v>1</v>
       </c>
-      <c r="D78" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="41">
+      <c r="D78" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="31">
         <v>1000</v>
       </c>
       <c r="F78">
         <v>128</v>
       </c>
-      <c r="G78" s="32">
+      <c r="G78">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H78" s="32">
+      <c r="H78">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>7.8125E-3</v>
       </c>
@@ -5342,10 +5294,9 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>1.953125E-3</v>
       </c>
-      <c r="J78" s="32">
+      <c r="J78">
         <v>0.25</v>
       </c>
-      <c r="L78" s="18"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1">
         <v>24500</v>
@@ -5353,16 +5304,15 @@
       <c r="O78">
         <v>296.970123</v>
       </c>
-      <c r="Q78" s="32">
+      <c r="Q78">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>1280</v>
       </c>
-      <c r="R78" s="32"/>
-      <c r="S78" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T78" s="32">
+      <c r="S78" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T78">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>4.9495020500000004</v>
       </c>
@@ -5386,11 +5336,11 @@
       <c r="F79">
         <v>128</v>
       </c>
-      <c r="G79" s="32">
+      <c r="G79">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H79" s="32">
+      <c r="H79">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>7.8125E-3</v>
       </c>
@@ -5398,10 +5348,9 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>9.765625E-4</v>
       </c>
-      <c r="J79" s="32">
+      <c r="J79">
         <v>0.125</v>
       </c>
-      <c r="L79" s="18"/>
       <c r="M79" s="1"/>
       <c r="N79" s="1">
         <v>42482</v>
@@ -5409,16 +5358,15 @@
       <c r="O79">
         <v>309.02886999999998</v>
       </c>
-      <c r="Q79" s="32">
+      <c r="Q79">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>2560</v>
       </c>
-      <c r="R79" s="32"/>
-      <c r="S79" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T79" s="32">
+      <c r="S79" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T79">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.1504811666666663</v>
       </c>
@@ -5442,11 +5390,11 @@
       <c r="F80">
         <v>128</v>
       </c>
-      <c r="G80" s="32">
+      <c r="G80">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H80" s="32">
+      <c r="H80">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>7.8125E-3</v>
       </c>
@@ -5454,114 +5402,774 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>4.8828125E-4</v>
       </c>
-      <c r="J80" s="32">
+      <c r="J80">
         <f>J79/2</f>
         <v>6.25E-2</v>
       </c>
-      <c r="L80" s="18"/>
       <c r="M80" s="1"/>
-      <c r="N80" s="1"/>
-      <c r="Q80" s="32">
+      <c r="N80" s="1">
+        <v>73907</v>
+      </c>
+      <c r="O80">
+        <v>412.84127799999999</v>
+      </c>
+      <c r="Q80">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>5120</v>
       </c>
-      <c r="R80" s="32"/>
-      <c r="S80" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T80" s="32">
+      <c r="S80" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T80">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>6.8806879666666667</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" s="35" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="35">
+        <v>80</v>
+      </c>
+      <c r="B81" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="38">
+        <v>1</v>
+      </c>
+      <c r="D81" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F81" s="38">
+        <v>64</v>
+      </c>
+      <c r="G81" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H81" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I81" s="38">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>1.7187500000000001E-2</v>
+      </c>
+      <c r="J81" s="39">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M81" s="36"/>
+      <c r="N81" s="36">
+        <v>4100</v>
+      </c>
+      <c r="O81" s="35">
+        <v>49.978645299999997</v>
+      </c>
+      <c r="Q81" s="35">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>145.45454545454544</v>
+      </c>
+      <c r="S81" s="35" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T81" s="35">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.83297742166666666</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="15">
+        <v>81</v>
+      </c>
+      <c r="B82" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="41">
+        <v>1</v>
+      </c>
+      <c r="D82" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F82" s="41">
+        <v>64</v>
+      </c>
+      <c r="G82" s="42">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H82" s="42">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I82" s="41">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="J82" s="42">
+        <v>1</v>
+      </c>
+      <c r="M82" s="16"/>
+      <c r="N82" s="16">
+        <v>3218</v>
+      </c>
+      <c r="O82" s="15">
+        <v>46.724494900000003</v>
+      </c>
+      <c r="Q82" s="15">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>160</v>
+      </c>
+      <c r="S82" s="15" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T82" s="15">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.77874158166666674</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="35">
+        <v>82</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="15">
+        <v>1</v>
+      </c>
+      <c r="D83" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F83" s="15">
+        <v>64</v>
+      </c>
+      <c r="G83" s="42">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H83" s="40"/>
+      <c r="I83" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>1.40625E-2</v>
+      </c>
+      <c r="J83" s="40">
+        <v>0.9</v>
+      </c>
+      <c r="M83" s="16"/>
+      <c r="N83" s="16">
+        <v>3490</v>
+      </c>
+      <c r="O83" s="15">
+        <v>43.7563362</v>
+      </c>
+      <c r="Q83" s="15">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>177.77777777777777</v>
+      </c>
+      <c r="S83" s="15" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T83" s="15">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.72927226999999994</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="15">
+        <v>83</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" s="15">
+        <v>1</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F84" s="15">
+        <v>64</v>
+      </c>
+      <c r="G84" s="42">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H84" s="40"/>
+      <c r="I84" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="J84" s="40">
+        <v>0.8</v>
+      </c>
+      <c r="M84" s="16"/>
+      <c r="N84" s="16">
+        <v>3836</v>
+      </c>
+      <c r="O84" s="15">
+        <v>41.343074799999997</v>
+      </c>
+      <c r="Q84" s="40">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>200</v>
+      </c>
+      <c r="R84" s="40"/>
+      <c r="S84" s="40" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T84" s="40">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.68905124666666662</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="35">
+        <v>84</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85" s="15">
+        <v>1</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F85" s="15">
+        <v>64</v>
+      </c>
+      <c r="G85" s="42">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H85" s="40">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I85" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>1.0937499999999999E-2</v>
+      </c>
+      <c r="J85" s="40">
+        <v>0.7</v>
+      </c>
+      <c r="L85" s="37"/>
+      <c r="M85" s="16"/>
+      <c r="N85" s="16">
+        <v>4259</v>
+      </c>
+      <c r="O85" s="15">
+        <v>38.909770999999999</v>
+      </c>
+      <c r="Q85" s="40">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>228.57142857142858</v>
+      </c>
+      <c r="R85" s="40"/>
+      <c r="S85" s="40" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T85" s="40">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.64849618333333336</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="15">
+        <v>85</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86" s="15">
+        <v>1</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F86" s="15">
+        <v>64</v>
+      </c>
+      <c r="G86" s="42">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H86" s="40">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I86" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>9.3749999999999997E-3</v>
+      </c>
+      <c r="J86" s="44">
+        <v>0.6</v>
+      </c>
+      <c r="M86" s="16"/>
+      <c r="N86" s="16">
+        <v>4819</v>
+      </c>
+      <c r="O86" s="15">
+        <v>36.087799099999998</v>
+      </c>
+      <c r="Q86" s="40">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>266.66666666666669</v>
+      </c>
+      <c r="R86" s="40"/>
+      <c r="S86" s="40" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T86" s="40">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.60146331833333333</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" s="41" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="35">
+        <v>86</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" s="15">
+        <v>1</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F87" s="15">
+        <v>64</v>
+      </c>
+      <c r="G87" s="42">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H87" s="40">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I87" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="J87" s="42">
+        <v>0.5</v>
+      </c>
+      <c r="M87" s="47"/>
+      <c r="N87" s="16">
+        <v>5579</v>
+      </c>
+      <c r="O87" s="15">
+        <v>32.4874382</v>
+      </c>
+      <c r="Q87" s="42">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>320</v>
+      </c>
+      <c r="R87" s="42"/>
+      <c r="S87" s="42" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T87" s="42">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.54145730333333331</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="15">
+        <v>87</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" s="15">
+        <v>1</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F88" s="15">
+        <v>64</v>
+      </c>
+      <c r="G88" s="42">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H88" s="40">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I88" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="J88" s="40">
+        <v>0.4</v>
+      </c>
+      <c r="M88" s="16"/>
+      <c r="N88" s="16">
+        <v>6682</v>
+      </c>
+      <c r="O88" s="15">
+        <v>29.4673786</v>
+      </c>
+      <c r="Q88" s="40">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>400</v>
+      </c>
+      <c r="R88" s="40"/>
+      <c r="S88" s="40" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T88" s="40">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.49112297666666666</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="35">
+        <v>88</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="15">
+        <v>1</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F89" s="15">
+        <v>64</v>
+      </c>
+      <c r="G89" s="42">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H89" s="40"/>
+      <c r="I89" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>4.6874999999999998E-3</v>
+      </c>
+      <c r="J89" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="K89" s="38"/>
+      <c r="L89" s="38"/>
+      <c r="M89" s="48"/>
+      <c r="N89" s="48">
+        <v>8448</v>
+      </c>
+      <c r="O89" s="38">
+        <v>26.9822311</v>
+      </c>
+      <c r="P89" s="38"/>
+      <c r="Q89" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>533.33333333333337</v>
+      </c>
+      <c r="R89" s="39"/>
+      <c r="S89" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T89" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.44970385166666665</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="15">
+        <v>89</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" s="15">
+        <v>1</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F90" s="15">
+        <v>64</v>
+      </c>
+      <c r="G90" s="42">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H90" s="40">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I90" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>3.1250000000000002E-3</v>
+      </c>
+      <c r="J90" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="M90" s="16"/>
+      <c r="N90" s="16">
+        <v>11786</v>
+      </c>
+      <c r="O90" s="15">
+        <v>25.726079899999998</v>
+      </c>
+      <c r="Q90" s="40">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>800</v>
+      </c>
+      <c r="R90" s="40"/>
+      <c r="S90" s="40" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T90" s="40">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.42876799833333329</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="35">
+        <v>90</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" s="15">
+        <v>1</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F91" s="15">
+        <v>64</v>
+      </c>
+      <c r="G91" s="42">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H91" s="40"/>
+      <c r="I91" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>1.5625000000000001E-3</v>
+      </c>
+      <c r="J91" s="40">
+        <v>0.1</v>
+      </c>
+      <c r="M91" s="16"/>
+      <c r="N91" s="16">
+        <v>20868</v>
+      </c>
+      <c r="O91" s="15">
+        <v>31.387655299999999</v>
+      </c>
+      <c r="Q91" s="40">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>1600</v>
+      </c>
+      <c r="R91" s="40"/>
+      <c r="S91" s="40" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T91" s="40">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.52312758833333328</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" s="37" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="37">
+        <v>91</v>
+      </c>
+      <c r="B92" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" s="37">
+        <v>1</v>
+      </c>
+      <c r="D92" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="37">
+        <v>1000</v>
+      </c>
+      <c r="F92" s="37">
+        <v>64</v>
+      </c>
+      <c r="G92" s="44">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H92" s="45">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I92" s="15">
+        <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
+        <v>7.8125000000000004E-4</v>
+      </c>
+      <c r="J92" s="45">
+        <v>0.05</v>
+      </c>
+      <c r="M92" s="46"/>
+      <c r="N92" s="46">
+        <v>37135</v>
+      </c>
+      <c r="O92" s="37">
+        <v>49.025444</v>
+      </c>
+      <c r="Q92" s="45">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>3200</v>
+      </c>
+      <c r="R92" s="45"/>
+      <c r="S92" s="45" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T92" s="45">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.81709073333333337</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" s="37" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="43">
+        <v>92</v>
+      </c>
+      <c r="B93" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="37">
+        <v>1</v>
+      </c>
+      <c r="D93" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="37">
+        <v>1000</v>
+      </c>
+      <c r="F93" s="37">
+        <v>64</v>
+      </c>
+      <c r="G93" s="45">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H93" s="45">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I93" s="37">
+        <f>Table52[[#This Row],[DX]]*Table52[[#This Row],[CFL]]</f>
+        <v>3.9062500000000002E-4</v>
+      </c>
+      <c r="J93" s="45">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M93" s="46"/>
+      <c r="N93" s="46"/>
+      <c r="Q93" s="45">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>6400</v>
+      </c>
+      <c r="R93" s="45"/>
+      <c r="S93" s="45" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T93" s="45">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="J81" s="32"/>
-      <c r="L81" s="18"/>
-      <c r="M81" s="1"/>
-      <c r="N81" s="1"/>
-      <c r="Q81" s="32" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R81" s="32"/>
-      <c r="S81" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T81" s="32">
+    <row r="94" spans="1:20" s="37" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="37">
+        <v>93</v>
+      </c>
+      <c r="C94" s="37">
+        <v>1</v>
+      </c>
+      <c r="D94" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="37">
+        <v>1000</v>
+      </c>
+      <c r="F94" s="37">
+        <v>64</v>
+      </c>
+      <c r="G94" s="45">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H94" s="45">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I94" s="37">
+        <f>Table52[[#This Row],[DX]]*Table52[[#This Row],[CFL]]</f>
+        <v>1.8749999999999999E-2</v>
+      </c>
+      <c r="J94" s="45">
+        <v>1.2</v>
+      </c>
+      <c r="M94" s="46"/>
+      <c r="N94" s="46"/>
+      <c r="Q94" s="45">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="R94" s="45"/>
+      <c r="S94" s="45" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T94" s="45">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="G82" s="32"/>
-      <c r="H82" s="32"/>
-      <c r="J82" s="32"/>
-      <c r="L82" s="18"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="Q82" s="32" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R82" s="32"/>
-      <c r="S82" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T82" s="32">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="G83" s="32"/>
-      <c r="H83" s="32"/>
-      <c r="J83" s="32"/>
-      <c r="L83" s="18"/>
-      <c r="M83" s="1"/>
-      <c r="N83" s="1"/>
-      <c r="Q83" s="32" t="e">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R83" s="32"/>
-      <c r="S83" s="32" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T83" s="32">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B84" t="s">
-        <v>12</v>
-      </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84" t="s">
-        <v>13</v>
-      </c>
-      <c r="E84">
-        <v>1000</v>
-      </c>
-      <c r="F84">
-        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annashen/Desktop/code/ME663-project/postprocess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578C7F68-1FD2-D14E-AA94-4DF9818C1BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963FC6EC-1C53-5B45-ADF2-3AC042830E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="27040" windowHeight="16880" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
+    <workbookView xWindow="2640" yWindow="820" windowWidth="25980" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="30">
   <si>
     <t>case</t>
   </si>
@@ -163,7 +163,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,6 +197,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -313,7 +325,6 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -322,7 +333,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -332,17 +342,27 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,8 +452,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T94" totalsRowShown="0">
-  <autoFilter ref="A1:T94" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}" name="Table52" displayName="Table52" ref="A1:T96" totalsRowShown="0">
+  <autoFilter ref="A1:T96" xr:uid="{1262BF81-760A-7144-97B7-D76DB2B84840}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{F042FD67-138A-3747-8F7D-92055EB26E1F}" name="case"/>
     <tableColumn id="19" xr3:uid="{6D3F4F6F-712A-EA45-8F90-560AA5EB3396}" name="solution_method"/>
@@ -829,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8141C424-3935-5946-8401-AC39630593AC}">
-  <dimension ref="A1:T94"/>
+  <dimension ref="A1:T96"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="13.6640625" customWidth="1"/>
@@ -2422,296 +2442,296 @@
         <v>1.2963990533333332</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A27">
+    <row r="27" spans="1:20" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="48">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C27">
-        <v>-1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27">
-        <v>1000</v>
-      </c>
-      <c r="F27">
+      <c r="C27" s="48">
+        <v>-1</v>
+      </c>
+      <c r="D27" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="48">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="48">
         <v>16</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="48">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H27" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I27" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J27" s="2">
-        <v>-1</v>
-      </c>
-      <c r="K27" s="18">
+      <c r="H27" s="49">
+        <v>-1</v>
+      </c>
+      <c r="I27" s="49">
+        <v>-1</v>
+      </c>
+      <c r="J27" s="49">
+        <v>-1</v>
+      </c>
+      <c r="K27" s="50">
         <v>0.3</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="48">
         <v>0.85</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="48">
         <v>294</v>
       </c>
-      <c r="O27" s="1">
-        <v>7.18609989E-2</v>
-      </c>
-      <c r="P27" t="s">
+      <c r="O27" s="51">
+        <v>7.6143994899999998E-2</v>
+      </c>
+      <c r="P27" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="48">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S27" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T27">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>1.197683315E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="S27" s="48" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T27" s="48">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.2690665816666666E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="48">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C28">
-        <v>-1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28">
-        <v>1000</v>
-      </c>
-      <c r="F28">
+      <c r="C28" s="48">
+        <v>-1</v>
+      </c>
+      <c r="D28" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="48">
+        <v>1000</v>
+      </c>
+      <c r="F28" s="48">
         <v>32</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="48">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="H28" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I28" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J28" s="2">
-        <v>-1</v>
-      </c>
-      <c r="K28" s="18">
+      <c r="H28" s="49">
+        <v>-1</v>
+      </c>
+      <c r="I28" s="49">
+        <v>-1</v>
+      </c>
+      <c r="J28" s="49">
+        <v>-1</v>
+      </c>
+      <c r="K28" s="50">
         <v>0.3</v>
       </c>
-      <c r="L28">
-        <v>0.75</v>
-      </c>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1">
-        <v>460</v>
-      </c>
-      <c r="O28">
-        <v>0.33705398399999997</v>
-      </c>
-      <c r="Q28">
+      <c r="L28" s="48">
+        <v>0.73</v>
+      </c>
+      <c r="M28" s="51"/>
+      <c r="N28" s="51">
+        <v>427</v>
+      </c>
+      <c r="O28" s="48">
+        <v>0.31440100100000001</v>
+      </c>
+      <c r="Q28" s="48">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S28" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T28">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>5.6175663999999993E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A29">
+      <c r="S28" s="48" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T28" s="48">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>5.2400166833333336E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="48">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C29">
-        <v>-1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29">
-        <v>1000</v>
-      </c>
-      <c r="F29">
+      <c r="C29" s="48">
+        <v>-1</v>
+      </c>
+      <c r="D29" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="48">
+        <v>1000</v>
+      </c>
+      <c r="F29" s="48">
         <v>64</v>
       </c>
-      <c r="G29">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H29" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I29" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J29" s="2">
-        <v>-1</v>
-      </c>
-      <c r="K29" s="18">
+      <c r="G29" s="48">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H29" s="49">
+        <v>-1</v>
+      </c>
+      <c r="I29" s="49">
+        <v>-1</v>
+      </c>
+      <c r="J29" s="49">
+        <v>-1</v>
+      </c>
+      <c r="K29" s="50">
         <v>0.3</v>
       </c>
-      <c r="L29">
-        <v>0.78</v>
-      </c>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1">
-        <v>1279</v>
-      </c>
-      <c r="O29">
-        <v>3.5678272199999999</v>
-      </c>
-      <c r="Q29">
+      <c r="L29" s="48">
+        <v>0.74</v>
+      </c>
+      <c r="M29" s="51"/>
+      <c r="N29" s="51">
+        <v>933</v>
+      </c>
+      <c r="O29" s="48">
+        <v>2.71165514</v>
+      </c>
+      <c r="Q29" s="48">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T29">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>5.9463786999999997E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A30">
+      <c r="S29" s="48" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T29" s="48">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>4.519425233333333E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="48">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C30">
-        <v>-1</v>
-      </c>
-      <c r="D30" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30">
-        <v>1000</v>
-      </c>
-      <c r="F30">
+      <c r="C30" s="48">
+        <v>-1</v>
+      </c>
+      <c r="D30" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="48">
+        <v>1000</v>
+      </c>
+      <c r="F30" s="48">
         <v>128</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="48">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="H30" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I30" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J30" s="2">
-        <v>-1</v>
-      </c>
-      <c r="K30" s="18">
+      <c r="H30" s="49">
+        <v>-1</v>
+      </c>
+      <c r="I30" s="49">
+        <v>-1</v>
+      </c>
+      <c r="J30" s="49">
+        <v>-1</v>
+      </c>
+      <c r="K30" s="50">
         <v>0.3</v>
       </c>
-      <c r="L30">
-        <v>0.99</v>
-      </c>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1">
-        <v>1882</v>
-      </c>
-      <c r="O30">
-        <v>20.745883899999999</v>
-      </c>
-      <c r="Q30">
+      <c r="L30" s="48">
+        <v>0.999</v>
+      </c>
+      <c r="M30" s="51"/>
+      <c r="N30" s="51">
+        <v>1865</v>
+      </c>
+      <c r="O30" s="48">
+        <v>21.054307900000001</v>
+      </c>
+      <c r="Q30" s="48">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S30" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T30">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0.34576473166666666</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" s="3" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+      <c r="S30" s="48" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T30" s="48">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0.3509051316666667</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" s="52" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="52">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="3">
-        <v>-1</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F31" s="3">
+      <c r="C31" s="52">
+        <v>-1</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="52">
+        <v>1000</v>
+      </c>
+      <c r="F31" s="52">
         <v>256</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="52">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>3.90625E-3</v>
       </c>
-      <c r="H31" s="19">
-        <v>-1</v>
-      </c>
-      <c r="I31" s="19">
-        <v>-1</v>
-      </c>
-      <c r="J31" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K31" s="20">
+      <c r="H31" s="53">
+        <v>-1</v>
+      </c>
+      <c r="I31" s="53">
+        <v>-1</v>
+      </c>
+      <c r="J31" s="53">
+        <v>-1</v>
+      </c>
+      <c r="K31" s="54">
         <v>0.3</v>
       </c>
-      <c r="L31" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4">
-        <v>7290</v>
-      </c>
-      <c r="O31" s="3">
-        <v>421.73425300000002</v>
-      </c>
-      <c r="Q31" s="3">
+      <c r="L31" s="52">
+        <v>0.999</v>
+      </c>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55">
+        <v>4081</v>
+      </c>
+      <c r="O31" s="52">
+        <v>191.85878</v>
+      </c>
+      <c r="Q31" s="52">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>-2.5</v>
       </c>
-      <c r="S31" s="3" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T31" s="3">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>7.0289042166666666</v>
+      <c r="S31" s="52" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T31" s="52">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>3.1976463333333331</v>
       </c>
     </row>
     <row r="32" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
@@ -2737,20 +2757,20 @@
         <f>1/Table52[[#This Row],[N]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="H32" s="21">
+      <c r="H32" s="20">
         <v>-1</v>
       </c>
       <c r="I32" s="15">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="J32" s="21">
+      <c r="J32" s="20">
         <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>1.0880000000000001</v>
       </c>
-      <c r="K32" s="21">
-        <v>-1</v>
-      </c>
-      <c r="L32" s="21">
+      <c r="K32" s="20">
+        <v>-1</v>
+      </c>
+      <c r="L32" s="20">
         <v>-1</v>
       </c>
       <c r="M32" s="15">
@@ -2807,7 +2827,7 @@
       <c r="I33" s="15">
         <v>1E-3</v>
       </c>
-      <c r="J33" s="21">
+      <c r="J33" s="20">
         <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>6.4000000000000001E-2</v>
       </c>
@@ -2866,7 +2886,7 @@
       <c r="I34" s="15">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J34" s="21">
+      <c r="J34" s="20">
         <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.32</v>
       </c>
@@ -2925,7 +2945,7 @@
       <c r="I35" s="15">
         <v>0.01</v>
       </c>
-      <c r="J35" s="21">
+      <c r="J35" s="20">
         <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0.64</v>
       </c>
@@ -2984,7 +3004,7 @@
       <c r="I36" s="15">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="J36" s="21">
+      <c r="J36" s="20">
         <f>Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>3.2000000000000001E-2</v>
       </c>
@@ -3014,7 +3034,7 @@
         <v>1.2455248516666666</v>
       </c>
     </row>
-    <row r="37" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15">
         <v>36</v>
       </c>
@@ -3033,43 +3053,43 @@
       <c r="F37" s="15">
         <v>64</v>
       </c>
-      <c r="G37" s="23">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H37" s="23">
-        <v>-1</v>
-      </c>
-      <c r="I37" s="23">
+      <c r="G37" s="22">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H37" s="22">
+        <v>-1</v>
+      </c>
+      <c r="I37" s="22">
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23">
-        <v>-1</v>
-      </c>
-      <c r="M37" s="23"/>
-      <c r="N37" s="23">
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22">
+        <v>-1</v>
+      </c>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22">
         <v>38422</v>
       </c>
-      <c r="O37" s="24">
+      <c r="O37" s="23">
         <v>59.427192699999999</v>
       </c>
-      <c r="P37" s="23" t="s">
+      <c r="P37" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="Q37" s="25">
+      <c r="Q37" s="24">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>3333.3333333333335</v>
       </c>
-      <c r="R37" s="22">
+      <c r="R37" s="21">
         <v>5000</v>
       </c>
-      <c r="S37" s="26">
+      <c r="S37" s="25">
         <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
         <v>7.6844000000000001</v>
       </c>
-      <c r="T37" s="26">
+      <c r="T37" s="25">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.99045321166666667</v>
       </c>
@@ -3188,22 +3208,22 @@
       </c>
     </row>
     <row r="40" spans="1:20" s="3" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="27">
+      <c r="A40" s="26">
         <v>39</v>
       </c>
-      <c r="B40" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="27">
+      <c r="B40" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="26">
         <v>2</v>
       </c>
-      <c r="D40" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="27">
-        <v>1000</v>
-      </c>
-      <c r="F40" s="27">
+      <c r="D40" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="26">
+        <v>1000</v>
+      </c>
+      <c r="F40" s="26">
         <v>64</v>
       </c>
       <c r="G40" s="3">
@@ -3241,1028 +3261,1028 @@
         <v>2.3477043166666665</v>
       </c>
     </row>
-    <row r="41" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="15">
+    <row r="41" spans="1:20" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="44">
         <v>40</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="15">
+      <c r="B41" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="44">
         <v>2</v>
       </c>
-      <c r="D41" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F41" s="15">
+      <c r="D41" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="44">
+        <v>1000</v>
+      </c>
+      <c r="F41" s="44">
         <v>64</v>
       </c>
-      <c r="G41" s="15">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H41" s="15">
+      <c r="G41" s="44">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H41" s="44">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="44">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.5625E-4</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="44">
         <v>0.01</v>
       </c>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16">
+      <c r="M41" s="45"/>
+      <c r="N41" s="45">
         <v>136659</v>
       </c>
-      <c r="O41" s="15">
+      <c r="O41" s="44">
         <v>175.09970100000001</v>
       </c>
-      <c r="Q41" s="15">
+      <c r="Q41" s="44">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>16000</v>
       </c>
-      <c r="S41" s="15" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T41" s="15">
+      <c r="S41" s="44" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T41" s="44">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>2.9183283500000003</v>
       </c>
     </row>
-    <row r="42" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="15">
+    <row r="42" spans="1:20" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="44">
         <v>41</v>
       </c>
-      <c r="B42" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="15">
+      <c r="B42" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="44">
         <v>2</v>
       </c>
-      <c r="D42" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F42" s="15">
+      <c r="D42" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="44">
+        <v>1000</v>
+      </c>
+      <c r="F42" s="44">
         <v>64</v>
       </c>
-      <c r="G42" s="15">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H42" s="15">
+      <c r="G42" s="44">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H42" s="44">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="44">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>7.8125000000000004E-4</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="44">
         <v>0.05</v>
       </c>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16">
+      <c r="M42" s="45"/>
+      <c r="N42" s="45">
         <v>37155</v>
       </c>
-      <c r="O42" s="15">
+      <c r="O42" s="44">
         <v>58.603294400000003</v>
       </c>
-      <c r="Q42" s="15">
+      <c r="Q42" s="44">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>3200</v>
       </c>
-      <c r="S42" s="15" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T42" s="15">
+      <c r="S42" s="44" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T42" s="44">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.97672157333333343</v>
       </c>
     </row>
-    <row r="43" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="15">
+    <row r="43" spans="1:20" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="44">
         <v>42</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="15">
+      <c r="B43" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="44">
         <v>2</v>
       </c>
-      <c r="D43" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F43" s="15">
+      <c r="D43" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="44">
+        <v>1000</v>
+      </c>
+      <c r="F43" s="44">
         <v>64</v>
       </c>
-      <c r="G43" s="15">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H43" s="15">
+      <c r="G43" s="44">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H43" s="44">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="44">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>3.1250000000000002E-3</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="44">
         <v>0.2</v>
       </c>
-      <c r="M43" s="16"/>
-      <c r="N43" s="16">
+      <c r="M43" s="45"/>
+      <c r="N43" s="45">
         <v>11825</v>
       </c>
-      <c r="O43" s="15">
+      <c r="O43" s="44">
         <v>60.159965499999998</v>
       </c>
-      <c r="Q43" s="15">
+      <c r="Q43" s="44">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>800</v>
       </c>
-      <c r="S43" s="15" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T43" s="15">
+      <c r="S43" s="44" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T43" s="44">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.0026660916666665</v>
       </c>
     </row>
-    <row r="44" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="15">
+    <row r="44" spans="1:20" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="44">
         <v>43</v>
       </c>
-      <c r="B44" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="15">
+      <c r="B44" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="44">
         <v>2</v>
       </c>
-      <c r="D44" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F44" s="15">
+      <c r="D44" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="44">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="44">
         <v>64</v>
       </c>
-      <c r="G44" s="15">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H44" s="15">
+      <c r="G44" s="44">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H44" s="44">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="44">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>6.2500000000000003E-3</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="44">
         <v>0.4</v>
       </c>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16">
+      <c r="M44" s="45"/>
+      <c r="N44" s="45">
         <v>6706</v>
       </c>
-      <c r="O44" s="15">
+      <c r="O44" s="44">
         <v>87.384323100000003</v>
       </c>
-      <c r="Q44" s="15">
+      <c r="Q44" s="44">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>400</v>
       </c>
-      <c r="S44" s="15" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T44" s="15">
+      <c r="S44" s="44" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T44" s="44">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.4564053850000001</v>
       </c>
     </row>
-    <row r="45" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="15">
+    <row r="45" spans="1:20" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="44">
         <v>44</v>
       </c>
-      <c r="B45" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="15">
+      <c r="B45" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="44">
         <v>2</v>
       </c>
-      <c r="D45" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F45" s="15">
+      <c r="D45" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="44">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="44">
         <v>64</v>
       </c>
-      <c r="G45" s="15">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H45" s="15">
+      <c r="G45" s="44">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H45" s="44">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="44">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="44">
         <v>0.5</v>
       </c>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16">
+      <c r="M45" s="45"/>
+      <c r="N45" s="45">
         <v>5560</v>
       </c>
-      <c r="O45" s="15">
+      <c r="O45" s="44">
         <v>97.289329499999994</v>
       </c>
-      <c r="Q45" s="15">
+      <c r="Q45" s="44">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>320</v>
       </c>
-      <c r="S45" s="15" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T45" s="15">
+      <c r="S45" s="44" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T45" s="44">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.6214888249999999</v>
       </c>
     </row>
-    <row r="46" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="15">
+    <row r="46" spans="1:20" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="44">
         <v>45</v>
       </c>
-      <c r="B46" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="15">
+      <c r="B46" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="44">
         <v>2</v>
       </c>
-      <c r="D46" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F46" s="15">
+      <c r="D46" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="44">
+        <v>1000</v>
+      </c>
+      <c r="F46" s="44">
         <v>64</v>
       </c>
-      <c r="G46" s="15">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H46" s="15">
+      <c r="G46" s="44">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H46" s="44">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I46" s="15">
+      <c r="I46" s="44">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>9.3749999999999997E-3</v>
       </c>
-      <c r="J46" s="15">
+      <c r="J46" s="44">
         <v>0.6</v>
       </c>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16">
+      <c r="M46" s="45"/>
+      <c r="N46" s="45">
         <v>4791</v>
       </c>
-      <c r="O46" s="15">
+      <c r="O46" s="44">
         <v>107.397453</v>
       </c>
-      <c r="Q46" s="15">
+      <c r="Q46" s="44">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>266.66666666666669</v>
       </c>
-      <c r="S46" s="15" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T46" s="15">
+      <c r="S46" s="44" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T46" s="44">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.78995755</v>
       </c>
     </row>
-    <row r="47" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="15">
+    <row r="47" spans="1:20" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="44">
         <v>46</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="15">
+      <c r="B47" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="44">
         <v>2</v>
       </c>
-      <c r="D47" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="15">
-        <v>1000</v>
-      </c>
-      <c r="F47" s="15">
+      <c r="D47" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="44">
+        <v>1000</v>
+      </c>
+      <c r="F47" s="44">
         <v>64</v>
       </c>
-      <c r="G47" s="15">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H47" s="15">
+      <c r="G47" s="44">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H47" s="44">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I47" s="15">
+      <c r="I47" s="44">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="J47" s="15">
+      <c r="J47" s="44">
         <v>0.8</v>
       </c>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16">
+      <c r="M47" s="45"/>
+      <c r="N47" s="45">
         <v>3717</v>
       </c>
-      <c r="O47" s="15">
+      <c r="O47" s="44">
         <v>127.491776</v>
       </c>
-      <c r="Q47" s="15">
+      <c r="Q47" s="44">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>200</v>
       </c>
-      <c r="S47" s="15" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T47" s="15">
+      <c r="S47" s="44" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T47" s="44">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>2.1248629333333335</v>
       </c>
     </row>
-    <row r="48" spans="1:20" s="27" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="27">
+    <row r="48" spans="1:20" s="46" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="46">
         <v>47</v>
       </c>
-      <c r="B48" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="27">
+      <c r="B48" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="46">
         <v>2</v>
       </c>
-      <c r="D48" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="27">
-        <v>1000</v>
-      </c>
-      <c r="F48" s="27">
+      <c r="D48" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="46">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="46">
         <v>64</v>
       </c>
-      <c r="G48" s="27">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H48" s="27">
+      <c r="G48" s="46">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H48" s="46">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I48" s="27">
+      <c r="I48" s="46">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J48" s="27">
+      <c r="J48" s="46">
         <v>1</v>
       </c>
-      <c r="M48" s="28"/>
-      <c r="N48" s="28">
+      <c r="M48" s="47"/>
+      <c r="N48" s="47">
         <v>2987</v>
       </c>
-      <c r="O48" s="27">
+      <c r="O48" s="46">
         <v>142.69487000000001</v>
       </c>
-      <c r="Q48" s="27">
+      <c r="Q48" s="46">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>160</v>
       </c>
-      <c r="S48" s="27" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T48" s="27">
+      <c r="S48" s="46" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T48" s="46">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>2.3782478333333334</v>
       </c>
     </row>
-    <row r="49" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="29">
+    <row r="49" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="27">
         <v>48</v>
       </c>
-      <c r="B49" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="29">
+      <c r="B49" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="27">
         <v>1</v>
       </c>
-      <c r="D49" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F49" s="29">
+      <c r="D49" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F49" s="27">
         <v>16</v>
       </c>
-      <c r="G49" s="29">
+      <c r="G49" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H49" s="29">
+      <c r="H49" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I49" s="29">
+      <c r="I49" s="27">
         <v>0.15</v>
       </c>
-      <c r="J49" s="29">
+      <c r="J49" s="27">
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>2.4</v>
       </c>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30">
+      <c r="M49" s="28"/>
+      <c r="N49" s="28">
         <v>259</v>
       </c>
-      <c r="O49" s="29">
+      <c r="O49" s="27">
         <v>0.729385018</v>
       </c>
-      <c r="Q49" s="29">
+      <c r="Q49" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>16.666666666666668</v>
       </c>
-      <c r="S49" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T49" s="29">
+      <c r="S49" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T49" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2156416966666667E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29">
+    <row r="50" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="27">
         <v>49</v>
       </c>
-      <c r="B50" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="29">
+      <c r="B50" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="27">
         <v>1</v>
       </c>
-      <c r="D50" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F50" s="29">
+      <c r="D50" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F50" s="27">
         <v>16</v>
       </c>
-      <c r="G50" s="29">
+      <c r="G50" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H50" s="29">
+      <c r="H50" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I50" s="29">
+      <c r="I50" s="27">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>0.15625</v>
       </c>
-      <c r="J50" s="29">
+      <c r="J50" s="27">
         <v>2.5</v>
       </c>
-      <c r="M50" s="30"/>
-      <c r="N50" s="30">
+      <c r="M50" s="28"/>
+      <c r="N50" s="28">
         <v>241</v>
       </c>
-      <c r="O50" s="29">
+      <c r="O50" s="27">
         <v>0.74937796599999995</v>
       </c>
-      <c r="Q50" s="29">
+      <c r="Q50" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>16</v>
       </c>
-      <c r="S50" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T50" s="29">
+      <c r="S50" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T50" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2489632766666666E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29">
+    <row r="51" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="27">
         <v>50</v>
       </c>
-      <c r="B51" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="29">
+      <c r="B51" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="27">
         <v>1</v>
       </c>
-      <c r="D51" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F51" s="29">
+      <c r="D51" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F51" s="27">
         <v>16</v>
       </c>
-      <c r="G51" s="29">
+      <c r="G51" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H51" s="29">
+      <c r="H51" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I51" s="29">
+      <c r="I51" s="27">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>0.140625</v>
       </c>
-      <c r="J51" s="29">
+      <c r="J51" s="27">
         <v>2.25</v>
       </c>
-      <c r="M51" s="30"/>
-      <c r="N51" s="30">
+      <c r="M51" s="28"/>
+      <c r="N51" s="28">
         <v>274</v>
       </c>
-      <c r="O51" s="29">
+      <c r="O51" s="27">
         <v>0.73873001299999996</v>
       </c>
-      <c r="Q51" s="29">
+      <c r="Q51" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>17.777777777777779</v>
       </c>
-      <c r="S51" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T51" s="29">
+      <c r="S51" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T51" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2312166883333333E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29">
+    <row r="52" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="27">
         <v>51</v>
       </c>
-      <c r="B52" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="29">
+      <c r="B52" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="27">
         <v>1</v>
       </c>
-      <c r="D52" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F52" s="29">
+      <c r="D52" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F52" s="27">
         <v>16</v>
       </c>
-      <c r="G52" s="29">
+      <c r="G52" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H52" s="29">
+      <c r="H52" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I52" s="29">
+      <c r="I52" s="27">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>0.125</v>
       </c>
-      <c r="J52" s="29">
+      <c r="J52" s="27">
         <v>2</v>
       </c>
-      <c r="M52" s="30"/>
-      <c r="N52" s="30">
+      <c r="M52" s="28"/>
+      <c r="N52" s="28">
         <v>304</v>
       </c>
-      <c r="O52" s="29">
+      <c r="O52" s="27">
         <v>0.72258299599999998</v>
       </c>
-      <c r="Q52" s="29">
+      <c r="Q52" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>20</v>
       </c>
-      <c r="S52" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T52" s="29">
+      <c r="S52" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T52" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2043049933333333E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:20" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="29">
+    <row r="53" spans="1:20" s="27" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="27">
         <v>52</v>
       </c>
-      <c r="B53" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="29">
+      <c r="B53" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="27">
         <v>1</v>
       </c>
-      <c r="D53" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F53" s="29">
+      <c r="D53" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F53" s="27">
         <v>16</v>
       </c>
-      <c r="G53" s="29">
+      <c r="G53" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H53" s="29">
+      <c r="H53" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I53" s="29">
+      <c r="I53" s="27">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>0.109375</v>
       </c>
-      <c r="J53" s="29">
+      <c r="J53" s="27">
         <v>1.75</v>
       </c>
-      <c r="M53" s="30"/>
-      <c r="N53" s="30">
+      <c r="M53" s="28"/>
+      <c r="N53" s="28">
         <v>341</v>
       </c>
-      <c r="O53" s="29">
+      <c r="O53" s="27">
         <v>0.73771297899999999</v>
       </c>
-      <c r="Q53" s="29">
+      <c r="Q53" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>22.857142857142858</v>
       </c>
-      <c r="S53" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T53" s="29">
+      <c r="S53" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T53" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2295216316666666E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="29">
+    <row r="54" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="27">
         <v>53</v>
       </c>
-      <c r="B54" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="29">
+      <c r="B54" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="27">
         <v>1</v>
       </c>
-      <c r="D54" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F54" s="29">
+      <c r="D54" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F54" s="27">
         <v>16</v>
       </c>
-      <c r="G54" s="29">
+      <c r="G54" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H54" s="29">
+      <c r="H54" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I54" s="29">
+      <c r="I54" s="27">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>9.375E-2</v>
       </c>
-      <c r="J54" s="29">
+      <c r="J54" s="27">
         <v>1.5</v>
       </c>
-      <c r="M54" s="30"/>
-      <c r="N54" s="30">
+      <c r="M54" s="28"/>
+      <c r="N54" s="28">
         <v>390</v>
       </c>
-      <c r="O54" s="29">
+      <c r="O54" s="27">
         <v>0.72225296500000002</v>
       </c>
-      <c r="Q54" s="29">
+      <c r="Q54" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>26.666666666666668</v>
       </c>
-      <c r="S54" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T54" s="29">
+      <c r="S54" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T54" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.2037549416666666E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="29">
+    <row r="55" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="27">
         <v>54</v>
       </c>
-      <c r="B55" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="29">
+      <c r="B55" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="27">
         <v>2</v>
       </c>
-      <c r="D55" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F55" s="29">
+      <c r="D55" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F55" s="27">
         <v>16</v>
       </c>
-      <c r="G55" s="29">
+      <c r="G55" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H55" s="29">
+      <c r="H55" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I55" s="29">
+      <c r="I55" s="27">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>7.8125E-2</v>
       </c>
-      <c r="J55" s="29">
+      <c r="J55" s="27">
         <v>1.25</v>
       </c>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30">
+      <c r="M55" s="28"/>
+      <c r="N55" s="28">
         <v>457</v>
       </c>
-      <c r="O55" s="29">
+      <c r="O55" s="27">
         <v>0.65907299500000005</v>
       </c>
-      <c r="Q55" s="29">
+      <c r="Q55" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>32</v>
       </c>
-      <c r="S55" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T55" s="29">
+      <c r="S55" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T55" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.0984549916666668E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="29">
+    <row r="56" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="27">
         <v>55</v>
       </c>
-      <c r="B56" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="29">
+      <c r="B56" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="27">
         <v>3</v>
       </c>
-      <c r="D56" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F56" s="29">
+      <c r="D56" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F56" s="27">
         <v>16</v>
       </c>
-      <c r="G56" s="29">
+      <c r="G56" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H56" s="29">
+      <c r="H56" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I56" s="29">
+      <c r="I56" s="27">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="J56" s="29">
+      <c r="J56" s="27">
         <v>1</v>
       </c>
-      <c r="M56" s="30"/>
-      <c r="N56" s="30">
+      <c r="M56" s="28"/>
+      <c r="N56" s="28">
         <v>554</v>
       </c>
-      <c r="O56" s="29">
+      <c r="O56" s="27">
         <v>0.62351202999999999</v>
       </c>
-      <c r="Q56" s="29">
+      <c r="Q56" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>40</v>
       </c>
-      <c r="S56" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T56" s="29">
+      <c r="S56" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T56" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>1.0391867166666667E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="29">
+    <row r="57" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="27">
         <v>56</v>
       </c>
-      <c r="B57" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="29">
+      <c r="B57" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="27">
         <v>4</v>
       </c>
-      <c r="D57" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F57" s="29">
+      <c r="D57" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F57" s="27">
         <v>16</v>
       </c>
-      <c r="G57" s="29">
+      <c r="G57" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H57" s="29">
+      <c r="H57" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I57" s="29">
+      <c r="I57" s="27">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>4.6875E-2</v>
       </c>
-      <c r="J57" s="29">
+      <c r="J57" s="27">
         <v>0.75</v>
       </c>
-      <c r="M57" s="30"/>
-      <c r="N57" s="29">
+      <c r="M57" s="28"/>
+      <c r="N57" s="27">
         <v>707</v>
       </c>
-      <c r="O57" s="29">
+      <c r="O57" s="27">
         <v>0.562693</v>
       </c>
-      <c r="Q57" s="29">
+      <c r="Q57" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>53.333333333333336</v>
       </c>
-      <c r="S57" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T57" s="29">
+      <c r="S57" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T57" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>9.3782166666666663E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="29">
+    <row r="58" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="27">
         <v>57</v>
       </c>
-      <c r="B58" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="29">
+      <c r="B58" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="27">
         <v>5</v>
       </c>
-      <c r="D58" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F58" s="29">
+      <c r="D58" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F58" s="27">
         <v>16</v>
       </c>
-      <c r="G58" s="29">
+      <c r="G58" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H58" s="29">
+      <c r="H58" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I58" s="29">
+      <c r="I58" s="27">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>3.125E-2</v>
       </c>
-      <c r="J58" s="29">
+      <c r="J58" s="27">
         <v>0.5</v>
       </c>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30">
+      <c r="M58" s="28"/>
+      <c r="N58" s="28">
         <v>996</v>
       </c>
-      <c r="O58" s="29">
+      <c r="O58" s="27">
         <v>0.46355798799999998</v>
       </c>
-      <c r="Q58" s="29">
+      <c r="Q58" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>80</v>
       </c>
-      <c r="S58" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T58" s="29">
+      <c r="S58" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T58" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>7.7259664666666662E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="29">
+    <row r="59" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="27">
         <v>58</v>
       </c>
-      <c r="B59" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="29">
+      <c r="B59" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="27">
         <v>5</v>
       </c>
-      <c r="D59" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="29">
-        <v>1000</v>
-      </c>
-      <c r="F59" s="29">
+      <c r="D59" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="27">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="27">
         <v>16</v>
       </c>
-      <c r="G59" s="29">
+      <c r="G59" s="27">
         <f>1/Table52[[#This Row],[N]]</f>
         <v>6.25E-2</v>
       </c>
-      <c r="H59" s="29">
+      <c r="H59" s="27">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>6.25E-2</v>
       </c>
-      <c r="I59" s="29">
+      <c r="I59" s="27">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J59" s="29">
+      <c r="J59" s="27">
         <v>0.25</v>
       </c>
-      <c r="M59" s="30"/>
-      <c r="N59" s="30">
+      <c r="M59" s="28"/>
+      <c r="N59" s="28">
         <v>1767</v>
       </c>
-      <c r="O59" s="29">
+      <c r="O59" s="27">
         <v>0.35058298700000001</v>
       </c>
-      <c r="Q59" s="29">
+      <c r="Q59" s="27">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>160</v>
       </c>
-      <c r="S59" s="29" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T59" s="29">
+      <c r="S59" s="27" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T59" s="27">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>5.8430497833333334E-3</v>
       </c>
@@ -4697,7 +4717,7 @@
         <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-      <c r="K67" s="20">
+      <c r="K67" s="19">
         <v>0.3</v>
       </c>
       <c r="L67" s="3">
@@ -5121,10 +5141,10 @@
       <c r="F75" s="3">
         <v>32</v>
       </c>
-      <c r="G75" s="34">
+      <c r="G75" s="32">
         <v>3.125E-2</v>
       </c>
-      <c r="H75" s="34">
+      <c r="H75" s="32">
         <v>3.125E-2</v>
       </c>
       <c r="I75" s="3">
@@ -5159,16 +5179,16 @@
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="32">
+      <c r="B76" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="30">
         <v>1</v>
       </c>
-      <c r="D76" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="32">
+      <c r="D76" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="30">
         <v>1000</v>
       </c>
       <c r="F76">
@@ -5186,7 +5206,7 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J76" s="33">
+      <c r="J76" s="31">
         <v>0.64</v>
       </c>
       <c r="M76" s="1"/>
@@ -5267,16 +5287,16 @@
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="31">
+      <c r="B78" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="29">
         <v>1</v>
       </c>
-      <c r="D78" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="31">
+      <c r="D78" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="29">
         <v>1000</v>
       </c>
       <c r="F78">
@@ -5426,56 +5446,56 @@
         <v>6.8806879666666667</v>
       </c>
     </row>
-    <row r="81" spans="1:20" s="35" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="35">
+    <row r="81" spans="1:20" s="33" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="33">
         <v>80</v>
       </c>
-      <c r="B81" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C81" s="38">
+      <c r="B81" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="37">
         <v>1</v>
       </c>
-      <c r="D81" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="38">
-        <v>1000</v>
-      </c>
-      <c r="F81" s="38">
+      <c r="D81" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="37">
+        <v>1000</v>
+      </c>
+      <c r="F81" s="37">
         <v>64</v>
       </c>
-      <c r="G81" s="39">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H81" s="39">
+      <c r="G81" s="38">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H81" s="38">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I81" s="38">
+      <c r="I81" s="37">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.7187500000000001E-2</v>
       </c>
-      <c r="J81" s="39">
+      <c r="J81" s="38">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M81" s="36"/>
-      <c r="N81" s="36">
+      <c r="M81" s="34"/>
+      <c r="N81" s="34">
         <v>4100</v>
       </c>
-      <c r="O81" s="35">
+      <c r="O81" s="33">
         <v>49.978645299999997</v>
       </c>
-      <c r="Q81" s="35">
+      <c r="Q81" s="33">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>145.45454545454544</v>
       </c>
-      <c r="S81" s="35" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T81" s="35">
+      <c r="S81" s="33" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T81" s="33">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.83297742166666666</v>
       </c>
@@ -5484,34 +5504,34 @@
       <c r="A82" s="15">
         <v>81</v>
       </c>
-      <c r="B82" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" s="41">
+      <c r="B82" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="40">
         <v>1</v>
       </c>
-      <c r="D82" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="E82" s="41">
-        <v>1000</v>
-      </c>
-      <c r="F82" s="41">
+      <c r="D82" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="40">
+        <v>1000</v>
+      </c>
+      <c r="F82" s="40">
         <v>64</v>
       </c>
-      <c r="G82" s="42">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H82" s="42">
+      <c r="G82" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H82" s="41">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I82" s="41">
+      <c r="I82" s="40">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DT_MAX]]</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="J82" s="42">
+      <c r="J82" s="41">
         <v>1</v>
       </c>
       <c r="M82" s="16"/>
@@ -5535,7 +5555,7 @@
       </c>
     </row>
     <row r="83" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="35">
+      <c r="A83" s="33">
         <v>82</v>
       </c>
       <c r="B83" s="15" t="s">
@@ -5553,16 +5573,16 @@
       <c r="F83" s="15">
         <v>64</v>
       </c>
-      <c r="G83" s="42">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H83" s="40"/>
+      <c r="G83" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H83" s="39"/>
       <c r="I83" s="15">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>1.40625E-2</v>
       </c>
-      <c r="J83" s="40">
+      <c r="J83" s="39">
         <v>0.9</v>
       </c>
       <c r="M83" s="16"/>
@@ -5604,16 +5624,16 @@
       <c r="F84" s="15">
         <v>64</v>
       </c>
-      <c r="G84" s="42">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H84" s="40"/>
+      <c r="G84" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H84" s="39"/>
       <c r="I84" s="15">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="J84" s="40">
+      <c r="J84" s="39">
         <v>0.8</v>
       </c>
       <c r="M84" s="16"/>
@@ -5623,22 +5643,22 @@
       <c r="O84" s="15">
         <v>41.343074799999997</v>
       </c>
-      <c r="Q84" s="40">
+      <c r="Q84" s="39">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>200</v>
       </c>
-      <c r="R84" s="40"/>
-      <c r="S84" s="40" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T84" s="40">
+      <c r="R84" s="39"/>
+      <c r="S84" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T84" s="39">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.68905124666666662</v>
       </c>
     </row>
     <row r="85" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="35">
+      <c r="A85" s="33">
         <v>84</v>
       </c>
       <c r="B85" s="15" t="s">
@@ -5656,11 +5676,11 @@
       <c r="F85" s="15">
         <v>64</v>
       </c>
-      <c r="G85" s="42">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H85" s="40">
+      <c r="G85" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H85" s="39">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -5668,10 +5688,9 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>1.0937499999999999E-2</v>
       </c>
-      <c r="J85" s="40">
+      <c r="J85" s="39">
         <v>0.7</v>
       </c>
-      <c r="L85" s="37"/>
       <c r="M85" s="16"/>
       <c r="N85" s="16">
         <v>4259</v>
@@ -5679,16 +5698,16 @@
       <c r="O85" s="15">
         <v>38.909770999999999</v>
       </c>
-      <c r="Q85" s="40">
+      <c r="Q85" s="39">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>228.57142857142858</v>
       </c>
-      <c r="R85" s="40"/>
-      <c r="S85" s="40" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T85" s="40">
+      <c r="R85" s="39"/>
+      <c r="S85" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T85" s="39">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.64849618333333336</v>
       </c>
@@ -5712,11 +5731,11 @@
       <c r="F86" s="15">
         <v>64</v>
       </c>
-      <c r="G86" s="42">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H86" s="40">
+      <c r="G86" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H86" s="39">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -5724,7 +5743,7 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>9.3749999999999997E-3</v>
       </c>
-      <c r="J86" s="44">
+      <c r="J86" s="41">
         <v>0.6</v>
       </c>
       <c r="M86" s="16"/>
@@ -5734,22 +5753,22 @@
       <c r="O86" s="15">
         <v>36.087799099999998</v>
       </c>
-      <c r="Q86" s="40">
+      <c r="Q86" s="39">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>266.66666666666669</v>
       </c>
-      <c r="R86" s="40"/>
-      <c r="S86" s="40" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T86" s="40">
+      <c r="R86" s="39"/>
+      <c r="S86" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T86" s="39">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.60146331833333333</v>
       </c>
     </row>
-    <row r="87" spans="1:20" s="41" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="35">
+    <row r="87" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="33">
         <v>86</v>
       </c>
       <c r="B87" s="15" t="s">
@@ -5767,11 +5786,11 @@
       <c r="F87" s="15">
         <v>64</v>
       </c>
-      <c r="G87" s="42">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H87" s="40">
+      <c r="G87" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H87" s="39">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -5779,26 +5798,26 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>7.8125E-3</v>
       </c>
-      <c r="J87" s="42">
+      <c r="J87" s="41">
         <v>0.5</v>
       </c>
-      <c r="M87" s="47"/>
+      <c r="M87" s="42"/>
       <c r="N87" s="16">
         <v>5579</v>
       </c>
       <c r="O87" s="15">
         <v>32.4874382</v>
       </c>
-      <c r="Q87" s="42">
+      <c r="Q87" s="41">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>320</v>
       </c>
-      <c r="R87" s="42"/>
-      <c r="S87" s="42" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T87" s="42">
+      <c r="R87" s="41"/>
+      <c r="S87" s="41" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T87" s="41">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.54145730333333331</v>
       </c>
@@ -5822,11 +5841,11 @@
       <c r="F88" s="15">
         <v>64</v>
       </c>
-      <c r="G88" s="42">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H88" s="40">
+      <c r="G88" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H88" s="39">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -5834,7 +5853,7 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>6.2500000000000003E-3</v>
       </c>
-      <c r="J88" s="40">
+      <c r="J88" s="39">
         <v>0.4</v>
       </c>
       <c r="M88" s="16"/>
@@ -5844,22 +5863,22 @@
       <c r="O88" s="15">
         <v>29.4673786</v>
       </c>
-      <c r="Q88" s="40">
+      <c r="Q88" s="39">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>400</v>
       </c>
-      <c r="R88" s="40"/>
-      <c r="S88" s="40" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T88" s="40">
+      <c r="R88" s="39"/>
+      <c r="S88" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T88" s="39">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.49112297666666666</v>
       </c>
     </row>
     <row r="89" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="35">
+      <c r="A89" s="33">
         <v>88</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -5877,38 +5896,38 @@
       <c r="F89" s="15">
         <v>64</v>
       </c>
-      <c r="G89" s="42">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H89" s="40"/>
+      <c r="G89" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H89" s="39"/>
       <c r="I89" s="15">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>4.6874999999999998E-3</v>
       </c>
-      <c r="J89" s="40">
+      <c r="J89" s="39">
         <v>0.3</v>
       </c>
-      <c r="K89" s="38"/>
-      <c r="L89" s="38"/>
-      <c r="M89" s="48"/>
-      <c r="N89" s="48">
+      <c r="K89" s="37"/>
+      <c r="L89" s="37"/>
+      <c r="M89" s="43"/>
+      <c r="N89" s="43">
         <v>8448</v>
       </c>
-      <c r="O89" s="38">
+      <c r="O89" s="37">
         <v>26.9822311</v>
       </c>
-      <c r="P89" s="38"/>
-      <c r="Q89" s="39">
+      <c r="P89" s="37"/>
+      <c r="Q89" s="38">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>533.33333333333337</v>
       </c>
-      <c r="R89" s="39"/>
-      <c r="S89" s="39" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T89" s="39">
+      <c r="R89" s="38"/>
+      <c r="S89" s="38" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T89" s="38">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.44970385166666665</v>
       </c>
@@ -5932,11 +5951,11 @@
       <c r="F90" s="15">
         <v>64</v>
       </c>
-      <c r="G90" s="42">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H90" s="40">
+      <c r="G90" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H90" s="39">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -5944,7 +5963,7 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>3.1250000000000002E-3</v>
       </c>
-      <c r="J90" s="40">
+      <c r="J90" s="39">
         <v>0.2</v>
       </c>
       <c r="M90" s="16"/>
@@ -5954,22 +5973,22 @@
       <c r="O90" s="15">
         <v>25.726079899999998</v>
       </c>
-      <c r="Q90" s="40">
+      <c r="Q90" s="39">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>800</v>
       </c>
-      <c r="R90" s="40"/>
-      <c r="S90" s="40" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T90" s="40">
+      <c r="R90" s="39"/>
+      <c r="S90" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T90" s="39">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.42876799833333329</v>
       </c>
     </row>
     <row r="91" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="35">
+      <c r="A91" s="33">
         <v>90</v>
       </c>
       <c r="B91" s="15" t="s">
@@ -5987,16 +6006,16 @@
       <c r="F91" s="15">
         <v>64</v>
       </c>
-      <c r="G91" s="42">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H91" s="40"/>
+      <c r="G91" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H91" s="39"/>
       <c r="I91" s="15">
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>1.5625000000000001E-3</v>
       </c>
-      <c r="J91" s="40">
+      <c r="J91" s="39">
         <v>0.1</v>
       </c>
       <c r="M91" s="16"/>
@@ -6006,44 +6025,44 @@
       <c r="O91" s="15">
         <v>31.387655299999999</v>
       </c>
-      <c r="Q91" s="40">
+      <c r="Q91" s="39">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>1600</v>
       </c>
-      <c r="R91" s="40"/>
-      <c r="S91" s="40" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T91" s="40">
+      <c r="R91" s="39"/>
+      <c r="S91" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T91" s="39">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.52312758833333328</v>
       </c>
     </row>
-    <row r="92" spans="1:20" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="37">
+    <row r="92" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="15">
         <v>91</v>
       </c>
-      <c r="B92" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C92" s="37">
+      <c r="B92" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" s="15">
         <v>1</v>
       </c>
-      <c r="D92" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="37">
-        <v>1000</v>
-      </c>
-      <c r="F92" s="37">
+      <c r="D92" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F92" s="15">
         <v>64</v>
       </c>
-      <c r="G92" s="44">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H92" s="45">
+      <c r="G92" s="41">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H92" s="39">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
@@ -6051,130 +6070,247 @@
         <f>Table52[[#This Row],[CFL]]*Table52[[#This Row],[DX]]</f>
         <v>7.8125000000000004E-4</v>
       </c>
-      <c r="J92" s="45">
+      <c r="J92" s="39">
         <v>0.05</v>
       </c>
-      <c r="M92" s="46"/>
-      <c r="N92" s="46">
+      <c r="M92" s="16"/>
+      <c r="N92" s="16">
         <v>37135</v>
       </c>
-      <c r="O92" s="37">
+      <c r="O92" s="15">
         <v>49.025444</v>
       </c>
-      <c r="Q92" s="45">
+      <c r="Q92" s="39">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>3200</v>
       </c>
-      <c r="R92" s="45"/>
-      <c r="S92" s="45" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T92" s="45">
+      <c r="R92" s="39"/>
+      <c r="S92" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T92" s="39">
         <f>Table52[[#This Row],[clock_time]]/60</f>
         <v>0.81709073333333337</v>
       </c>
     </row>
-    <row r="93" spans="1:20" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="43">
+    <row r="93" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="33">
         <v>92</v>
       </c>
-      <c r="B93" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C93" s="37">
+      <c r="B93" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="15">
         <v>1</v>
       </c>
-      <c r="D93" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="37">
-        <v>1000</v>
-      </c>
-      <c r="F93" s="37">
+      <c r="D93" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F93" s="15">
         <v>64</v>
       </c>
-      <c r="G93" s="45">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H93" s="45">
+      <c r="G93" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H93" s="39">
         <f>Table52[[#This Row],[DX]]/1</f>
         <v>1.5625E-2</v>
       </c>
-      <c r="I93" s="37">
+      <c r="I93" s="15">
         <f>Table52[[#This Row],[DX]]*Table52[[#This Row],[CFL]]</f>
         <v>3.9062500000000002E-4</v>
       </c>
-      <c r="J93" s="45">
+      <c r="J93" s="39">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M93" s="46"/>
-      <c r="N93" s="46"/>
-      <c r="Q93" s="45">
+      <c r="M93" s="16"/>
+      <c r="N93" s="16">
+        <v>65212</v>
+      </c>
+      <c r="O93" s="15">
+        <v>81.488029499999996</v>
+      </c>
+      <c r="Q93" s="39">
         <f>2.5/Table52[[#This Row],[DT]]</f>
         <v>6400</v>
       </c>
-      <c r="R93" s="45"/>
-      <c r="S93" s="45" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T93" s="45">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
+      <c r="R93" s="39"/>
+      <c r="S93" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T93" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.3581338249999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="15">
+        <v>93</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" s="15">
+        <v>1</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="15">
+        <v>1000</v>
+      </c>
+      <c r="F94" s="15">
+        <v>64</v>
+      </c>
+      <c r="G94" s="39">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H94" s="39">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I94" s="15">
+        <f>Table52[[#This Row],[DX]]*Table52[[#This Row],[CFL]]</f>
+        <v>1.7968749999999999E-2</v>
+      </c>
+      <c r="J94" s="39">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M94" s="16"/>
+      <c r="N94" s="16">
+        <v>23411</v>
+      </c>
+      <c r="O94" s="15">
+        <v>78.201164199999994</v>
+      </c>
+      <c r="Q94" s="39">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>139.13043478260872</v>
+      </c>
+      <c r="R94" s="39"/>
+      <c r="S94" s="39" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T94" s="39">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>1.3033527366666666</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95">
+        <v>1000</v>
+      </c>
+      <c r="F95">
+        <v>128</v>
+      </c>
+      <c r="G95" s="36">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="H95" s="36">
+        <f>Table52[[#This Row],[DX]]/1</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="J95" s="36">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="37">
-        <v>93</v>
-      </c>
-      <c r="C94" s="37">
-        <v>1</v>
-      </c>
-      <c r="D94" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" s="37">
-        <v>1000</v>
-      </c>
-      <c r="F94" s="37">
-        <v>64</v>
-      </c>
-      <c r="G94" s="45">
-        <f>1/Table52[[#This Row],[N]]</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="H94" s="45">
+      <c r="K95">
+        <v>0.3</v>
+      </c>
+      <c r="L95" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+      <c r="Q95" s="36" t="e">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R95" s="36"/>
+      <c r="S95" s="36" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T95" s="36">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>12</v>
+      </c>
+      <c r="D96" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96">
+        <v>1000</v>
+      </c>
+      <c r="F96">
+        <v>128</v>
+      </c>
+      <c r="G96" s="36">
+        <f>1/Table52[[#This Row],[N]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="H96" s="36">
         <f>Table52[[#This Row],[DX]]/1</f>
-        <v>1.5625E-2</v>
-      </c>
-      <c r="I94" s="37">
-        <f>Table52[[#This Row],[DX]]*Table52[[#This Row],[CFL]]</f>
-        <v>1.8749999999999999E-2</v>
-      </c>
-      <c r="J94" s="45">
-        <v>1.2</v>
-      </c>
-      <c r="M94" s="46"/>
-      <c r="N94" s="46"/>
-      <c r="Q94" s="45">
-        <f>2.5/Table52[[#This Row],[DT]]</f>
-        <v>133.33333333333334</v>
-      </c>
-      <c r="R94" s="45"/>
-      <c r="S94" s="45" t="e">
-        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T94" s="45">
-        <f>Table52[[#This Row],[clock_time]]/60</f>
-        <v>0</v>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="I96" s="56">
+        <v>7.4999998300000004E-3</v>
+      </c>
+      <c r="J96" s="36">
+        <f>1*Table52[[#This Row],[DT]]/Table52[[#This Row],[DX]]</f>
+        <v>0.95999997824000005</v>
+      </c>
+      <c r="L96" s="35"/>
+      <c r="M96" s="1"/>
+      <c r="N96" s="1">
+        <v>11902</v>
+      </c>
+      <c r="O96">
+        <v>572.64324999999997</v>
+      </c>
+      <c r="Q96" s="36">
+        <f>2.5/Table52[[#This Row],[DT]]</f>
+        <v>333.33334088888904</v>
+      </c>
+      <c r="R96" s="36"/>
+      <c r="S96" s="36" t="e">
+        <f>Table52[[#This Row],[IT]]/Table52[[#This Row],[plot]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T96" s="36">
+        <f>Table52[[#This Row],[clock_time]]/60</f>
+        <v>9.5440541666666654</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
     <ignoredError sqref="H27 H28:H36 J27:J31" calculatedColumn="1"/>
   </ignoredErrors>

--- a/postprocess/cases.xlsx
+++ b/postprocess/cases.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963FC6EC-1C53-5B45-ADF2-3AC042830E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="820" windowWidth="25980" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
+    <workbookView xWindow="31720" yWindow="-1340" windowWidth="25980" windowHeight="16860" xr2:uid="{4FFFDDBB-3764-044A-A563-7130C269BFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
